--- a/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
+++ b/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
@@ -24500,10 +24500,10 @@
         <v>เริ่มฝึกเขียนโค้ดด้วยตนเอง (Python/Scratch) ลองทำโปรเจกต์เล็ก ๆ เก็บเป็นผลงาน</v>
       </c>
       <c r="C17" t="str">
-        <v>เริ่มฝึกเขียนโค้ดด้วยตนเอง (Python/Scratch) | ลองทำโปรเจกต์เล็ก ๆ | เก็บเป็นผลงาน</v>
+        <v>เริ่มฝึกเขียนโค้ดด้วยตนเอง (Python/Scratch) | ลองทำโปรเจกต์เล็ก ๆ เก็บเป็นผลงาน</v>
       </c>
       <c r="D17" t="str">
-        <v>ลองทำโปรเจกต์เล็ก ๆ</v>
+        <v>ลองทำโปรเจกต์เล็ก ๆ เก็บเป็นผลงาน</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -24661,10 +24661,10 @@
         <v>ลองผลิตผลงานวิดีโอ/คอนเทนต์สั้น ๆ ด้วยตนเอง เก็บเป็นผลงานนำเสนอ</v>
       </c>
       <c r="C24" t="str">
-        <v>ลองผลิตผลงานวิดีโอ/คอนเทนต์สั้น ๆ ด้วยตนเอง | เก็บเป็นผลงานนำเสนอ</v>
+        <v>ลองผลิตผลงานวิดีโอ/คอนเทนต์สั้น ๆ ด้วยตนเอง เก็บเป็นผลงานนำเสนอ</v>
       </c>
       <c r="D24" t="str">
-        <v>ลองผลิตผลงานวิดีโอ/คอนเทนต์สั้น ๆ ด้วยตนเอง</v>
+        <v>ลองผลิตผลงานวิดีโอ/คอนเทนต์สั้น ๆ ด้วยตนเอง เก็บเป็นผลงานนำเสนอ</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -24776,10 +24776,10 @@
         <v>ลองผลิตหนังสั้นหรือคลิปวิดีโอด้วยตนเอง เก็บผลงานเป็นพอร์ตโฟลิโอ</v>
       </c>
       <c r="C29" t="str">
-        <v>ลองผลิตหนังสั้นหรือคลิปวิดีโอด้วยตนเอง | เก็บผลงานเป็นพอร์ตโฟลิโอ</v>
+        <v>ลองผลิตหนังสั้นหรือคลิปวิดีโอด้วยตนเอง เก็บผลงานเป็นพอร์ตโฟลิโอ</v>
       </c>
       <c r="D29" t="str">
-        <v>ลองผลิตหนังสั้นหรือคลิปวิดีโอด้วยตนเอง</v>
+        <v>ลองผลิตหนังสั้นหรือคลิปวิดีโอด้วยตนเอง เก็บผลงานเป็นพอร์ตโฟลิโอ</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -25328,10 +25328,10 @@
         <v>ฝึกสเก็ตช์และทำโมเดลต้นแบบ ลองใช้โปรแกรม 3 มิติ เก็บผลงานเป็น Portfolio</v>
       </c>
       <c r="C53" t="str">
-        <v>ฝึกสเก็ตช์และทำโมเดลต้นแบบ | ลองใช้โปรแกรม 3 มิติ | เก็บผลงานเป็น Portfolio</v>
+        <v>ฝึกสเก็ตช์และทำโมเดลต้นแบบ | ลองใช้โปรแกรม 3 มิติ เก็บผลงานเป็น Portfolio</v>
       </c>
       <c r="D53" t="str">
-        <v>ฝึกสเก็ตช์และทำโมเดลต้นแบบ | ลองใช้โปรแกรม 3 มิติ</v>
+        <v>ฝึกสเก็ตช์และทำโมเดลต้นแบบ | ลองใช้โปรแกรม 3 มิติ เก็บผลงานเป็น Portfolio</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -25397,7 +25397,7 @@
         <v>เริ่มฝึกเขียนโปรแกรมและทำเว็บ/แอปเล็ก ๆ เก็บเป็นผลงาน</v>
       </c>
       <c r="C56" t="str">
-        <v>เริ่มฝึกเขียนโปรแกรมและทำเว็บ/แอปเล็ก ๆ | เก็บเป็นผลงาน</v>
+        <v>เริ่มฝึกเขียนโปรแกรมและทำเว็บ/แอปเล็ก ๆ เก็บเป็นผลงาน</v>
       </c>
       <c r="D56" t="str">
         <v/>
@@ -25443,10 +25443,10 @@
         <v>ฝึกวาดทัศนียภาพและจัดพื้นที่ห้องจริง เก็บผลงานออกแบบเป็น Portfolio</v>
       </c>
       <c r="C58" t="str">
-        <v>ฝึกวาดทัศนียภาพและจัดพื้นที่ห้องจริง | เก็บผลงานออกแบบเป็น Portfolio</v>
+        <v>ฝึกวาดทัศนียภาพและจัดพื้นที่ห้องจริง เก็บผลงานออกแบบเป็น Portfolio</v>
       </c>
       <c r="D58" t="str">
-        <v>ฝึกวาดทัศนียภาพและจัดพื้นที่ห้องจริง</v>
+        <v>ฝึกวาดทัศนียภาพและจัดพื้นที่ห้องจริง เก็บผลงานออกแบบเป็น Portfolio</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -25949,10 +25949,10 @@
         <v>ฝึกออกแบบโปสเตอร์และสื่อต่าง ๆ จริง เก็บเป็น Portfolio</v>
       </c>
       <c r="C80" t="str">
-        <v>ฝึกออกแบบโปสเตอร์และสื่อต่าง ๆ จริง | เก็บเป็น Portfolio</v>
+        <v>ฝึกออกแบบโปสเตอร์และสื่อต่าง ๆ จริง เก็บเป็น Portfolio</v>
       </c>
       <c r="D80" t="str">
-        <v>ฝึกออกแบบโปสเตอร์และสื่อต่าง ๆ จริง</v>
+        <v>ฝึกออกแบบโปสเตอร์และสื่อต่าง ๆ จริง เก็บเป็น Portfolio</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -25972,10 +25972,10 @@
         <v>ลองทำเกมเล็ก ๆ ด้วย Scratch/Unity เก็บเป็นผลงาน</v>
       </c>
       <c r="C81" t="str">
-        <v>ลองทำเกมเล็ก ๆ ด้วย Scratch/Unity | เก็บเป็นผลงาน</v>
+        <v>ลองทำเกมเล็ก ๆ ด้วย Scratch/Unity เก็บเป็นผลงาน</v>
       </c>
       <c r="D81" t="str">
-        <v>ลองทำเกมเล็ก ๆ ด้วย Scratch/Unity</v>
+        <v>ลองทำเกมเล็ก ๆ ด้วย Scratch/Unity เก็บเป็นผลงาน</v>
       </c>
       <c r="E81" t="str">
         <v/>

--- a/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
+++ b/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
@@ -3775,7 +3775,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -3943,9 +3943,35 @@
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Twemoji 16.0.1 (Twitter, Inc. และผู้ร่วมพัฒนา)</v>
+      </c>
+      <c r="B7" t="str">
+        <v>https://github.com/jdecked/twemoji</v>
+      </c>
+      <c r="C7" t="str">
+        <v>รูปประกอบอาชีพ (เก็บไว้ในเว็บที่ public/emoji/twemoji — กราฟิก CC BY 4.0)</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9883,7 +9909,7 @@
         <v>วิธีลงมือทำ</v>
       </c>
       <c r="D3" t="str">
-        <v>ลองซ่อมของใช้ที่ชำรุดเล็กน้อย ประกอบชุดโมเดล หรือทำชิ้นงานง่าย ๆ ให้เสร็จ 1 ชิ้น แล้วจดว่าติดปัญหาตรงไหน</v>
+        <v>ลองประกอบชุดโมเดล ซ่อมของใช้ชิ้นเล็ก ๆ หรือสร้างชิ้นงานง่าย ๆ ให้เสร็จหนึ่งชิ้น</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -9929,7 +9955,7 @@
         <v>คำถามทบทวนตัวเอง</v>
       </c>
       <c r="D5" t="str">
-        <v>คุณรู้สึกอย่างไรเมื่อได้ลงมือทำจนเห็นผลงานเป็นชิ้นเป็นอัน?</v>
+        <v>คุณรู้สึกอย่างไรเมื่อได้ลงมือทำจนเห็นผลงานเป็นชิ้นเป็นอัน และรู้สึกสนุกกับการแก้ปัญหาระหว่างทำหรือไม่?</v>
       </c>
       <c r="E5" t="str">
         <v/>

--- a/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
+++ b/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
@@ -490,7 +490,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="str">
-        <v>ชีต 4-ข้อความที่ระบบเขียน: กิจกรรมทั่วไป 6 ด้าน คำถามทบทวนตัวเอง และประโยคแม่แบบ — เขียนโดยระบบ ยังไม่ผ่านครู</v>
+        <v>ชีต 4-ข้อความที่ระบบเขียน: กิจกรรมทั่วไป 6 ด้าน คำถามทบทวนตัวเอง ประโยคแม่แบบ และคำอธิบายทักษะ 216 ข้อ — เขียนโดยระบบ ยังไม่ผ่านครู</v>
       </c>
     </row>
     <row r="11">
@@ -9841,7 +9841,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G263"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" customWidth="1"/>
@@ -10797,16 +10797,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ประโยคแม่แบบ</v>
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>ประโยคสรุปความสนใจ</v>
+        <v>คณิตศาสตร์-ฟิสิกส์ประยุกต์</v>
       </c>
       <c r="D42" t="str">
-        <v>คุณมีความสนใจเด่นด้าน{ด้านอันดับ 1–2}[ในระดับใกล้เคียงกัน] + ขณะเดียวกันก็มีความสนใจด้าน{ด้านที่เหลือ}ในระดับใกล้เคียงกัน / รองลงมาคือด้าน{…}</v>
+        <v>ใช้คณิตศาสตร์และฟิสิกส์คำนวณแรงและโครงสร้างในงานจริง</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -10820,16 +10820,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ประโยคแม่แบบ</v>
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>เหตุผลสาขาที่ควรสำรวจ</v>
+        <v>การอ่านแบบก่อสร้าง</v>
       </c>
       <c r="D43" t="str">
-        <v>สาขานี้อาจเป็นทางเลือกที่น่าสำรวจสำหรับคุณ เนื่องจากเกี่ยวข้องกับ{วลีของสาขา} ซึ่งเชื่อมโยงกับความสนใจด้าน{…}ของคุณ</v>
+        <v>อ่านแบบแปลน รูปตัด และสัญลักษณ์ในแบบก่อสร้าง</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -10843,16 +10843,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ประโยคแม่แบบ</v>
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>การ์ดเป้าหมาย</v>
+        <v>การใช้โปรแกรม CAD</v>
       </c>
       <c r="D44" t="str">
-        <v>สาขานี้เน้น{วลีของสาขา} ซึ่งเชื่อมโยงกับความสนใจด้าน{…}ของคุณ ลองทำกิจกรรมจริงตามข้อด้านล่าง แล้วสังเกตว่าคุณสนุกกับงานลักษณะนี้มากน้อยเพียงใด</v>
+        <v>เขียนแบบและออกแบบชิ้นงานด้วยคอมพิวเตอร์</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -10866,16 +10866,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ประโยคแม่แบบ</v>
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>กรณีระดับต่ำ</v>
+        <v>กลศาสตร์</v>
       </c>
       <c r="D45" t="str">
-        <v>ความสนใจที่โดดเด่นของคุณอาจแตกต่างจากลักษณะการเรียนหรือการทำงานบางส่วนของสาขานี้ แต่ไม่ได้หมายความว่าคุณเรียนสาขานี้ไม่ได้ หากสาขานี้ยังเป็นเป้าหมาย ลองศึกษารายวิชาและลักษณะการเรียนจริง และทดลองกิจกรรมด้าน{…} เพื่อสำรวจว่าคุณชอบและอยากพัฒนาทักษะด้านใดเพิ่ม</v>
+        <v>เข้าใจแรง การเคลื่อนที่ และการรับน้ำหนักของวัตถุ</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -10889,16 +10889,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ประโยคแม่แบบ</v>
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>ข้อจำกัดของผล</v>
+        <v>การออกแบบเชิงกล</v>
       </c>
       <c r="D46" t="str">
-        <v>การเชื่อมโยงนี้สะท้อนความสนใจ ไม่ใช่การยืนยันความพร้อมในการเรียนหรือโอกาสสอบติด</v>
+        <v>ออกแบบชิ้นส่วนเครื่องจักรให้ทำงานได้และแข็งแรงพอ</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -10912,30 +10912,4998 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v>การใช้ซอฟต์แวร์จำลอง (CAE)</v>
+      </c>
+      <c r="D47" t="str">
+        <v>ใช้โปรแกรมทดสอบชิ้นงานในคอมพิวเตอร์ก่อนสร้างจริง</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v>วงจรไฟฟ้า</v>
+      </c>
+      <c r="D48" t="str">
+        <v>เข้าใจการไหลของกระแสไฟฟ้าและการต่อวงจร</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49" t="str">
+        <v>ระบบควบคุมอัตโนมัติ</v>
+      </c>
+      <c r="D49" t="str">
+        <v>ทำให้เครื่องจักรหรือระบบทำงานเองตามเงื่อนไขที่ตั้งไว้</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v>การเขียนโปรแกรมไมโครคอนโทรลเลอร์</v>
+      </c>
+      <c r="D50" t="str">
+        <v>เขียนโปรแกรมสั่งงานบอร์ดควบคุมขนาดเล็ก เช่น Arduino</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v>การบริหารกระบวนการผลิต</v>
+      </c>
+      <c r="D51" t="str">
+        <v>วางลำดับขั้นตอนการผลิตให้เร็ว ประหยัด และได้คุณภาพ</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v>สถิติเชิงคุณภาพ</v>
+      </c>
+      <c r="D52" t="str">
+        <v>ใช้สถิติตรวจว่าสินค้าหรือกระบวนการได้มาตรฐานหรือไม่</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v>การจัดการโลจิสติกส์</v>
+      </c>
+      <c r="D53" t="str">
+        <v>วางแผนการขนส่ง การเก็บ และการกระจายสินค้า</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+      <c r="C54" t="str">
+        <v>ชีววิทยาพืช/สัตว์</v>
+      </c>
+      <c r="D54" t="str">
+        <v>เข้าใจโครงสร้าง การเจริญเติบโต และการดำรงชีวิตของพืชและสัตว์</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v>การจัดการดินและน้ำ</v>
+      </c>
+      <c r="D55" t="str">
+        <v>ดูแลดินและน้ำให้เหมาะกับการเพาะปลูก</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v>เทคโนโลยีการเกษตรสมัยใหม่</v>
+      </c>
+      <c r="D56" t="str">
+        <v>ใช้เครื่องมือ เซนเซอร์ และข้อมูลช่วยทำการเกษตร</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v>กายวิภาคสัตว์</v>
+      </c>
+      <c r="D57" t="str">
+        <v>รู้จักโครงสร้างและอวัยวะในร่างกายของสัตว์</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v>ชีวเคมี</v>
+      </c>
+      <c r="D58" t="str">
+        <v>เข้าใจปฏิกิริยาเคมีที่เกิดขึ้นในสิ่งมีชีวิต</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v>ทักษะการดูแลสัตว์</v>
+      </c>
+      <c r="D59" t="str">
+        <v>จับ เลี้ยง และสังเกตอาการสัตว์อย่างปลอดภัย</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B60" t="str">
+        <v/>
+      </c>
+      <c r="C60" t="str">
+        <v>ชีววิทยาทางน้ำ</v>
+      </c>
+      <c r="D60" t="str">
+        <v>เข้าใจสิ่งมีชีวิตและระบบนิเวศในน้ำ</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61" t="str">
+        <v>การจัดการคุณภาพน้ำ</v>
+      </c>
+      <c r="D61" t="str">
+        <v>ตรวจและปรับค่าน้ำให้เหมาะกับสัตว์น้ำหรือการใช้งาน</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B62" t="str">
+        <v/>
+      </c>
+      <c r="C62" t="str">
+        <v>เทคโนโลยีการเพาะเลี้ยง</v>
+      </c>
+      <c r="D62" t="str">
+        <v>ใช้วิธีและอุปกรณ์เลี้ยงสัตว์น้ำให้เติบโตได้ดี</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B63" t="str">
+        <v/>
+      </c>
+      <c r="C63" t="str">
+        <v>นิเวศวิทยาป่าไม้</v>
+      </c>
+      <c r="D63" t="str">
+        <v>เข้าใจความสัมพันธ์ของพืช สัตว์ และสภาพแวดล้อมในป่า</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64" t="str">
+        <v>การสำรวจภาคสนาม</v>
+      </c>
+      <c r="D64" t="str">
+        <v>ออกไปเก็บข้อมูลในพื้นที่จริงอย่างเป็นระบบ</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B65" t="str">
+        <v/>
+      </c>
+      <c r="C65" t="str">
+        <v>GIS เบื้องต้น</v>
+      </c>
+      <c r="D65" t="str">
+        <v>ใช้แผนที่และข้อมูลตำแหน่งบนคอมพิวเตอร์วิเคราะห์พื้นที่</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+      <c r="C66" t="str">
+        <v>ฟิสิกส์การบิน</v>
+      </c>
+      <c r="D66" t="str">
+        <v>เข้าใจแรงยกและหลักการที่ทำให้อากาศยานบินได้</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B67" t="str">
+        <v/>
+      </c>
+      <c r="C67" t="str">
+        <v>ภาษาอังกฤษเชิงเทคนิค</v>
+      </c>
+      <c r="D67" t="str">
+        <v>อ่านคู่มือและใช้ศัพท์เฉพาะทางเป็นภาษาอังกฤษ</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B68" t="str">
+        <v/>
+      </c>
+      <c r="C68" t="str">
+        <v>การทำงานภายใต้กฎระเบียบเข้มงวด</v>
+      </c>
+      <c r="D68" t="str">
+        <v>ทำตามขั้นตอนความปลอดภัยอย่างเคร่งครัดทุกครั้ง</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B69" t="str">
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v>สรีรวิทยาการออกกำลังกาย</v>
+      </c>
+      <c r="D69" t="str">
+        <v>เข้าใจการทำงานของร่างกายขณะออกกำลังกาย</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+      <c r="C70" t="str">
+        <v>โภชนาการนักกีฬา</v>
+      </c>
+      <c r="D70" t="str">
+        <v>วางแผนอาหารให้เหมาะกับการฝึกและการแข่งขัน</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B71" t="str">
+        <v/>
+      </c>
+      <c r="C71" t="str">
+        <v>การวิเคราะห์การเคลื่อนไหว</v>
+      </c>
+      <c r="D71" t="str">
+        <v>สังเกตและวัดท่าทางเพื่อปรับปรุงการเคลื่อนไหว</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B72" t="str">
+        <v/>
+      </c>
+      <c r="C72" t="str">
+        <v>ชีววิทยา-เคมีขั้นสูง</v>
+      </c>
+      <c r="D72" t="str">
+        <v>ความรู้ชีววิทยาและเคมีในระดับลึกที่ใช้ในวิชาการแพทย์</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B73" t="str">
+        <v/>
+      </c>
+      <c r="C73" t="str">
+        <v>การคิดวิเคราะห์เชิงเหตุผล</v>
+      </c>
+      <c r="D73" t="str">
+        <v>ไล่เหตุและผลจากข้อมูลเพื่อหาข้อสรุปที่น่าเชื่อถือ</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B74" t="str">
+        <v/>
+      </c>
+      <c r="C74" t="str">
+        <v>ความอดทนต่อความกดดัน</v>
+      </c>
+      <c r="D74" t="str">
+        <v>ทำงานได้ดีแม้มีเวลาจำกัดหรือมีความรับผิดชอบสูง</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B75" t="str">
+        <v/>
+      </c>
+      <c r="C75" t="str">
+        <v>ความละเอียดในการใช้มือ (fine motor skills)</v>
+      </c>
+      <c r="D75" t="str">
+        <v>ใช้มือทำงานชิ้นเล็กอย่างแม่นยำ</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B76" t="str">
+        <v/>
+      </c>
+      <c r="C76" t="str">
+        <v>ชีววิทยา-เคมี</v>
+      </c>
+      <c r="D76" t="str">
+        <v>ความรู้พื้นฐานเรื่องสิ่งมีชีวิตและสารเคมี</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B77" t="str">
+        <v/>
+      </c>
+      <c r="C77" t="str">
+        <v>ทักษะการสื่อสารกับผู้ป่วย</v>
+      </c>
+      <c r="D77" t="str">
+        <v>อธิบายและรับฟังผู้ป่วยด้วยภาษาที่เข้าใจง่าย</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B78" t="str">
+        <v/>
+      </c>
+      <c r="C78" t="str">
+        <v>เคมีขั้นสูง</v>
+      </c>
+      <c r="D78" t="str">
+        <v>ความรู้เรื่องสารและปฏิกิริยาเคมีในระดับลึก</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B79" t="str">
+        <v/>
+      </c>
+      <c r="C79" t="str">
+        <v>ความละเอียดรอบคอบ</v>
+      </c>
+      <c r="D79" t="str">
+        <v>ตรวจงานทีละขั้นเพื่อไม่ให้ผิดพลาด</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B80" t="str">
+        <v/>
+      </c>
+      <c r="C80" t="str">
+        <v>ความรู้ด้านกฎหมายยา</v>
+      </c>
+      <c r="D80" t="str">
+        <v>รู้กฎหมายเกี่ยวกับการผลิต การจ่าย และการขายยา</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+      <c r="C81" t="str">
+        <v>การทดลองในห้องปฏิบัติการ</v>
+      </c>
+      <c r="D81" t="str">
+        <v>ทำการทดลองตามขั้นตอนและบันทึกผลอย่างถูกต้อง</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B82" t="str">
+        <v/>
+      </c>
+      <c r="C82" t="str">
+        <v>การวิเคราะห์ข้อมูลเชิงปริมาณ</v>
+      </c>
+      <c r="D82" t="str">
+        <v>ใช้ตัวเลขและสถิติหาข้อสรุปจากข้อมูล</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B83" t="str">
+        <v/>
+      </c>
+      <c r="C83" t="str">
+        <v>ชีววิทยาระดับเซลล์/โมเลกุล</v>
+      </c>
+      <c r="D83" t="str">
+        <v>เข้าใจการทำงานของเซลล์ ยีน และ DNA</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B84" t="str">
+        <v/>
+      </c>
+      <c r="C84" t="str">
+        <v>การใช้กล้องจุลทรรศน์และเครื่องมือแล็บ</v>
+      </c>
+      <c r="D84" t="str">
+        <v>ใช้อุปกรณ์ในห้องปฏิบัติการได้ถูกวิธีและปลอดภัย</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B85" t="str">
+        <v/>
+      </c>
+      <c r="C85" t="str">
+        <v>การเขียนโปรแกรม</v>
+      </c>
+      <c r="D85" t="str">
+        <v>เขียนคำสั่งให้คอมพิวเตอร์ทำงานตามที่ต้องการ</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B86" t="str">
+        <v/>
+      </c>
+      <c r="C86" t="str">
+        <v>ตรรกะและคณิตศาสตร์ไม่ต่อเนื่อง</v>
+      </c>
+      <c r="D86" t="str">
+        <v>คณิตศาสตร์ที่ใช้คิดเชิงตรรกะและออกแบบโปรแกรม</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B87" t="str">
+        <v/>
+      </c>
+      <c r="C87" t="str">
+        <v>การวิเคราะห์ข้อมูล</v>
+      </c>
+      <c r="D87" t="str">
+        <v>จัดระเบียบและตีความข้อมูลเพื่อตอบคำถาม</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B88" t="str">
+        <v/>
+      </c>
+      <c r="C88" t="str">
+        <v>การตรวจวิเคราะห์ทางห้องปฏิบัติการ</v>
+      </c>
+      <c r="D88" t="str">
+        <v>ตรวจตัวอย่าง เช่น เลือดหรือปัสสาวะ ด้วยเครื่องมือแล็บ</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B89" t="str">
+        <v/>
+      </c>
+      <c r="C89" t="str">
+        <v>สถิติพื้นฐาน</v>
+      </c>
+      <c r="D89" t="str">
+        <v>ค่าเฉลี่ย ร้อยละ และการอ่านกราฟเบื้องต้น</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B90" t="str">
+        <v/>
+      </c>
+      <c r="C90" t="str">
+        <v>การวิเคราะห์ข้อมูลสุขภาพประชากร</v>
+      </c>
+      <c r="D90" t="str">
+        <v>ดูแนวโน้มโรคและสุขภาพของคนจำนวนมากจากข้อมูล</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B91" t="str">
+        <v/>
+      </c>
+      <c r="C91" t="str">
+        <v>คณิตศาสตร์ขั้นสูง</v>
+      </c>
+      <c r="D91" t="str">
+        <v>แคลคูลัส พีชคณิต และการแก้โจทย์ที่ซับซ้อน</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B92" t="str">
+        <v/>
+      </c>
+      <c r="C92" t="str">
+        <v>การเขียนโปรแกรมเพื่อการวิเคราะห์ข้อมูล</v>
+      </c>
+      <c r="D92" t="str">
+        <v>ใช้โปรแกรมจัดการและคำนวณข้อมูลจำนวนมาก</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v>เทคนิคการวาด/ระบายสี</v>
+      </c>
+      <c r="D93" t="str">
+        <v>ใช้เส้น แสงเงา และสีถ่ายทอดภาพ</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
+        <v>การสร้างสรรค์แนวคิด (concept art)</v>
+      </c>
+      <c r="D94" t="str">
+        <v>ร่างภาพไอเดียตัวละคร ฉาก หรือผลงานก่อนลงมือจริง</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
+        <v>การออกแบบเชิงพื้นที่</v>
+      </c>
+      <c r="D95" t="str">
+        <v>จัดวางพื้นที่ให้ใช้งานได้ดีและสวยงาม</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v>โปรแกรมออกแบบ 3 มิติ</v>
+      </c>
+      <c r="D96" t="str">
+        <v>สร้างแบบจำลองสามมิติด้วยคอมพิวเตอร์</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v>คณิตศาสตร์เชิงเรขาคณิต</v>
+      </c>
+      <c r="D97" t="str">
+        <v>คำนวณรูปทรง มุม และระยะ</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
+        <v>ความคิดสร้างสรรค์เชิงพื้นที่</v>
+      </c>
+      <c r="D98" t="str">
+        <v>นึกภาพพื้นที่และรูปทรงสามมิติในหัวได้</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B99" t="str">
+        <v/>
+      </c>
+      <c r="C99" t="str">
+        <v>การเลือกใช้วัสดุและสี</v>
+      </c>
+      <c r="D99" t="str">
+        <v>เลือกวัสดุและสีให้เหมาะกับการใช้งานและบรรยากาศ</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v>การเล่าเรื่อง (storytelling)</v>
+      </c>
+      <c r="D100" t="str">
+        <v>เรียงเรื่องราวให้น่าติดตามและเข้าใจง่าย</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>การถ่ายภาพ/วิดีโอเบื้องต้น</v>
+      </c>
+      <c r="D101" t="str">
+        <v>จัดมุมกล้อง แสง และองค์ประกอบภาพ</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
+        <v>ทักษะเครื่องดนตรี/การขับร้อง</v>
+      </c>
+      <c r="D102" t="str">
+        <v>เล่นดนตรีหรือร้องเพลงได้อย่างมีคุณภาพ</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
+        <v>ทฤษฎีดนตรี</v>
+      </c>
+      <c r="D103" t="str">
+        <v>เข้าใจโน้ต จังหวะ และการประสานเสียง</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
+        <v>การออกแบบลวดลาย</v>
+      </c>
+      <c r="D104" t="str">
+        <v>สร้างลายสำหรับผ้า สินค้า หรือของตกแต่ง</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B105" t="str">
+        <v/>
+      </c>
+      <c r="C105" t="str">
+        <v>การตัดเย็บเบื้องต้น</v>
+      </c>
+      <c r="D105" t="str">
+        <v>วัดตัว ตัดผ้า และเย็บชิ้นงานพื้นฐาน</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B106" t="str">
+        <v/>
+      </c>
+      <c r="C106" t="str">
+        <v>แนวโน้มแฟชั่น</v>
+      </c>
+      <c r="D106" t="str">
+        <v>ติดตามสไตล์และกระแสการแต่งกาย</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B107" t="str">
+        <v/>
+      </c>
+      <c r="C107" t="str">
+        <v>การร่างแบบ</v>
+      </c>
+      <c r="D107" t="str">
+        <v>สเก็ตช์ไอเดียออกมาเป็นภาพอย่างรวดเร็ว</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B108" t="str">
+        <v/>
+      </c>
+      <c r="C108" t="str">
+        <v>การใช้โปรแกรมออกแบบ 3 มิติ</v>
+      </c>
+      <c r="D108" t="str">
+        <v>สร้างแบบจำลองสามมิติด้วยคอมพิวเตอร์</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B109" t="str">
+        <v/>
+      </c>
+      <c r="C109" t="str">
+        <v>ความเข้าใจวัสดุ</v>
+      </c>
+      <c r="D109" t="str">
+        <v>รู้คุณสมบัติของวัสดุแต่ละชนิดและเลือกใช้ให้เหมาะ</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B110" t="str">
+        <v/>
+      </c>
+      <c r="C110" t="str">
+        <v>การเขียนเชิงสร้างสรรค์</v>
+      </c>
+      <c r="D110" t="str">
+        <v>เขียนเรื่อง บทกวี หรือบทความให้มีชีวิตชีวา</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B111" t="str">
+        <v/>
+      </c>
+      <c r="C111" t="str">
+        <v>ทักษะภาษาไทย/ภาษาต่างประเทศ</v>
+      </c>
+      <c r="D111" t="str">
+        <v>อ่าน เขียน และสื่อสารได้ถูกต้องและสละสลวย</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B112" t="str">
+        <v/>
+      </c>
+      <c r="C112" t="str">
+        <v>การตัดต่อวิดีโอ</v>
+      </c>
+      <c r="D112" t="str">
+        <v>เรียงภาพและเสียงให้เป็นเรื่องราวที่ลื่นไหล</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B113" t="str">
+        <v/>
+      </c>
+      <c r="C113" t="str">
+        <v>การเล่าเรื่องด้วยภาพ</v>
+      </c>
+      <c r="D113" t="str">
+        <v>ใช้ภาพหรือฉากสื่อความหมายแทนคำพูด</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B114" t="str">
+        <v/>
+      </c>
+      <c r="C114" t="str">
+        <v>ซอฟต์แวร์ตัดต่อ/แอนิเมชัน</v>
+      </c>
+      <c r="D114" t="str">
+        <v>ใช้โปรแกรมตัดต่อวิดีโอหรือทำภาพเคลื่อนไหว</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B115" t="str">
+        <v/>
+      </c>
+      <c r="C115" t="str">
+        <v>การสื่อสารกับเด็ก/เยาวชน</v>
+      </c>
+      <c r="D115" t="str">
+        <v>พูดและอธิบายให้เด็กเข้าใจและไว้ใจ</v>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B116" t="str">
+        <v/>
+      </c>
+      <c r="C116" t="str">
+        <v>การจัดการชั้นเรียน</v>
+      </c>
+      <c r="D116" t="str">
+        <v>ดูแลผู้เรียนทั้งห้องให้เรียนได้อย่างราบรื่น</v>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B117" t="str">
+        <v/>
+      </c>
+      <c r="C117" t="str">
+        <v>ความรู้ทางการพยาบาล</v>
+      </c>
+      <c r="D117" t="str">
+        <v>การดูแลผู้ป่วยและหลักการรักษาพยาบาลเบื้องต้น</v>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B118" t="str">
+        <v/>
+      </c>
+      <c r="C118" t="str">
+        <v>ความเห็นอกเห็นใจ</v>
+      </c>
+      <c r="D118" t="str">
+        <v>เข้าใจความรู้สึกของผู้อื่นและตอบสนองอย่างเหมาะสม</v>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B119" t="str">
+        <v/>
+      </c>
+      <c r="C119" t="str">
+        <v>การรับฟังอย่างเข้าใจ</v>
+      </c>
+      <c r="D119" t="str">
+        <v>ฟังโดยไม่ตัดสินและจับใจความสิ่งที่อีกฝ่ายต้องการสื่อ</v>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B120" t="str">
+        <v/>
+      </c>
+      <c r="C120" t="str">
+        <v>ความรู้พื้นฐานพฤติกรรมมนุษย์</v>
+      </c>
+      <c r="D120" t="str">
+        <v>เข้าใจเหตุผลที่คนคิด รู้สึก และกระทำแบบต่าง ๆ</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B121" t="str">
+        <v/>
+      </c>
+      <c r="C121" t="str">
+        <v>การทำงานร่วมกับชุมชน</v>
+      </c>
+      <c r="D121" t="str">
+        <v>ลงพื้นที่ รับฟัง และทำงานร่วมกับคนในชุมชน</v>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B122" t="str">
+        <v/>
+      </c>
+      <c r="C122" t="str">
+        <v>ความเข้าใจปัญหาสังคม</v>
+      </c>
+      <c r="D122" t="str">
+        <v>มองเห็นสาเหตุและผลกระทบของปัญหาในสังคม</v>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B123" t="str">
+        <v/>
+      </c>
+      <c r="C123" t="str">
+        <v>กายวิภาคศาสตร์</v>
+      </c>
+      <c r="D123" t="str">
+        <v>รู้จักโครงสร้างกระดูก กล้ามเนื้อ และอวัยวะของร่างกายคน</v>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B124" t="str">
+        <v/>
+      </c>
+      <c r="C124" t="str">
+        <v>เทคนิคการฟื้นฟูร่างกาย</v>
+      </c>
+      <c r="D124" t="str">
+        <v>วิธีช่วยให้ร่างกายกลับมาเคลื่อนไหวได้ดีขึ้น</v>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B125" t="str">
+        <v/>
+      </c>
+      <c r="C125" t="str">
+        <v>การให้ความรู้ด้านสุขภาพ</v>
+      </c>
+      <c r="D125" t="str">
+        <v>อธิบายเรื่องสุขภาพให้คนทั่วไปเข้าใจและนำไปใช้ได้</v>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B126" t="str">
+        <v/>
+      </c>
+      <c r="C126" t="str">
+        <v>ความเข้าใจพัฒนาการเด็ก</v>
+      </c>
+      <c r="D126" t="str">
+        <v>รู้ว่าเด็กแต่ละวัยเติบโตและเรียนรู้อย่างไร</v>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B127" t="str">
+        <v/>
+      </c>
+      <c r="C127" t="str">
+        <v>ความอดทนและความอ่อนโยน</v>
+      </c>
+      <c r="D127" t="str">
+        <v>ใจเย็นและดูแลผู้อื่นอย่างนุ่มนวล</v>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B128" t="str">
+        <v/>
+      </c>
+      <c r="C128" t="str">
+        <v>ความเข้าใจพัฒนาการและความบกพร่องทางร่างกาย/จิตใจ</v>
+      </c>
+      <c r="D128" t="str">
+        <v>เข้าใจข้อจำกัดของแต่ละคนเพื่อช่วยได้ตรงจุด</v>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B129" t="str">
+        <v/>
+      </c>
+      <c r="C129" t="str">
+        <v>การวิเคราะห์พฤติกรรมผู้บริโภค</v>
+      </c>
+      <c r="D129" t="str">
+        <v>ศึกษาว่าลูกค้าตัดสินใจซื้ออย่างไรและเพราะอะไร</v>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B130" t="str">
+        <v/>
+      </c>
+      <c r="C130" t="str">
+        <v>การนำเสนอ</v>
+      </c>
+      <c r="D130" t="str">
+        <v>เล่าข้อมูลหรือไอเดียให้ผู้ฟังเข้าใจและสนใจ</v>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B131" t="str">
+        <v/>
+      </c>
+      <c r="C131" t="str">
+        <v>ความคิดสร้างสรรค์เชิงธุรกิจ</v>
+      </c>
+      <c r="D131" t="str">
+        <v>คิดสินค้า บริการ หรือวิธีขายแบบใหม่</v>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B132" t="str">
+        <v/>
+      </c>
+      <c r="C132" t="str">
+        <v>การวางแผนกลยุทธ์</v>
+      </c>
+      <c r="D132" t="str">
+        <v>กำหนดเป้าหมายและวิธีไปให้ถึงในระยะยาว</v>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B133" t="str">
+        <v/>
+      </c>
+      <c r="C133" t="str">
+        <v>ภาวะผู้นำ</v>
+      </c>
+      <c r="D133" t="str">
+        <v>ชวนคนอื่นทำงานไปในทิศทางเดียวกันและตัดสินใจเมื่อจำเป็น</v>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B134" t="str">
+        <v/>
+      </c>
+      <c r="C134" t="str">
+        <v>การบริหารทีม</v>
+      </c>
+      <c r="D134" t="str">
+        <v>แบ่งงาน ติดตามงาน และดูแลสมาชิกในทีม</v>
+      </c>
+      <c r="E134" t="str">
+        <v/>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B135" t="str">
+        <v/>
+      </c>
+      <c r="C135" t="str">
+        <v>การอ่านและตีความกฎหมาย</v>
+      </c>
+      <c r="D135" t="str">
+        <v>อ่านตัวบทกฎหมายแล้วเข้าใจว่าใช้กับเรื่องใดอย่างไร</v>
+      </c>
+      <c r="E135" t="str">
+        <v/>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B136" t="str">
+        <v/>
+      </c>
+      <c r="C136" t="str">
+        <v>การโต้แย้งเชิงเหตุผล</v>
+      </c>
+      <c r="D136" t="str">
+        <v>เสนอความเห็นพร้อมหลักฐานและเหตุผลที่หนักแน่น</v>
+      </c>
+      <c r="E136" t="str">
+        <v/>
+      </c>
+      <c r="F136" t="str">
+        <v/>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B137" t="str">
+        <v/>
+      </c>
+      <c r="C137" t="str">
+        <v>ความเข้าใจการเมืองการปกครอง</v>
+      </c>
+      <c r="D137" t="str">
+        <v>เข้าใจโครงสร้างอำนาจรัฐและการบริหารประเทศ</v>
+      </c>
+      <c r="E137" t="str">
+        <v/>
+      </c>
+      <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B138" t="str">
+        <v/>
+      </c>
+      <c r="C138" t="str">
+        <v>ทักษะการเจรจา</v>
+      </c>
+      <c r="D138" t="str">
+        <v>พูดคุยหาข้อตกลงที่ทุกฝ่ายยอมรับได้</v>
+      </c>
+      <c r="E138" t="str">
+        <v/>
+      </c>
+      <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B139" t="str">
+        <v/>
+      </c>
+      <c r="C139" t="str">
+        <v>การวิเคราะห์ข้อมูลเศรษฐกิจ</v>
+      </c>
+      <c r="D139" t="str">
+        <v>อ่านตัวเลขเศรษฐกิจและอธิบายแนวโน้ม</v>
+      </c>
+      <c r="E139" t="str">
+        <v/>
+      </c>
+      <c r="F139" t="str">
+        <v/>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B140" t="str">
+        <v/>
+      </c>
+      <c r="C140" t="str">
+        <v>คณิตศาสตร์พื้นฐาน</v>
+      </c>
+      <c r="D140" t="str">
+        <v>การคำนวณ ร้อยละ และโจทย์ปัญหาทั่วไป</v>
+      </c>
+      <c r="E140" t="str">
+        <v/>
+      </c>
+      <c r="F140" t="str">
+        <v/>
+      </c>
+      <c r="G140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B141" t="str">
+        <v/>
+      </c>
+      <c r="C141" t="str">
+        <v>การบริการลูกค้า</v>
+      </c>
+      <c r="D141" t="str">
+        <v>ดูแลและแก้ปัญหาให้ลูกค้าอย่างสุภาพและรวดเร็ว</v>
+      </c>
+      <c r="E141" t="str">
+        <v/>
+      </c>
+      <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B142" t="str">
+        <v/>
+      </c>
+      <c r="C142" t="str">
+        <v>ภาษาต่างประเทศ</v>
+      </c>
+      <c r="D142" t="str">
+        <v>สื่อสารด้วยภาษาอื่นนอกจากภาษาไทย</v>
+      </c>
+      <c r="E142" t="str">
+        <v/>
+      </c>
+      <c r="F142" t="str">
+        <v/>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B143" t="str">
+        <v/>
+      </c>
+      <c r="C143" t="str">
+        <v>การบริหารงานบริการ</v>
+      </c>
+      <c r="D143" t="str">
+        <v>วางระบบงานบริการให้ลูกค้าได้รับประสบการณ์ที่ดี</v>
+      </c>
+      <c r="E143" t="str">
+        <v/>
+      </c>
+      <c r="F143" t="str">
+        <v/>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B144" t="str">
+        <v/>
+      </c>
+      <c r="C144" t="str">
+        <v>การสื่อสารเชิงกลยุทธ์</v>
+      </c>
+      <c r="D144" t="str">
+        <v>วางแผนว่าจะสื่อสารอะไร กับใคร ผ่านช่องทางไหน</v>
+      </c>
+      <c r="E144" t="str">
+        <v/>
+      </c>
+      <c r="F144" t="str">
+        <v/>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B145" t="str">
+        <v/>
+      </c>
+      <c r="C145" t="str">
+        <v>การเจรจาต่อรอง</v>
+      </c>
+      <c r="D145" t="str">
+        <v>ต่อรองราคาหรือเงื่อนไขให้ได้ผลที่ดีกับทุกฝ่าย</v>
+      </c>
+      <c r="E145" t="str">
+        <v/>
+      </c>
+      <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B146" t="str">
+        <v/>
+      </c>
+      <c r="C146" t="str">
+        <v>ภาษาอังกฤษเชิงธุรกิจ</v>
+      </c>
+      <c r="D146" t="str">
+        <v>ใช้ภาษาอังกฤษในการประชุม อีเมล และการค้า</v>
+      </c>
+      <c r="E146" t="str">
+        <v/>
+      </c>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B147" t="str">
+        <v/>
+      </c>
+      <c r="C147" t="str">
+        <v>ความเข้าใจตลาดต่างประเทศ</v>
+      </c>
+      <c r="D147" t="str">
+        <v>รู้ความต้องการ กฎระเบียบ และวัฒนธรรมของตลาดต่างชาติ</v>
+      </c>
+      <c r="E147" t="str">
+        <v/>
+      </c>
+      <c r="F147" t="str">
+        <v/>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B148" t="str">
+        <v/>
+      </c>
+      <c r="C148" t="str">
+        <v>หลักการบัญชี</v>
+      </c>
+      <c r="D148" t="str">
+        <v>บันทึกรายรับรายจ่ายและจัดทำงบตามมาตรฐาน</v>
+      </c>
+      <c r="E148" t="str">
+        <v/>
+      </c>
+      <c r="F148" t="str">
+        <v/>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B149" t="str">
+        <v/>
+      </c>
+      <c r="C149" t="str">
+        <v>การใช้โปรแกรมบัญชี</v>
+      </c>
+      <c r="D149" t="str">
+        <v>บันทึกและสรุปข้อมูลบัญชีด้วยคอมพิวเตอร์</v>
+      </c>
+      <c r="E149" t="str">
+        <v/>
+      </c>
+      <c r="F149" t="str">
+        <v/>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B150" t="str">
+        <v/>
+      </c>
+      <c r="C150" t="str">
+        <v>การวิเคราะห์งบการเงิน</v>
+      </c>
+      <c r="D150" t="str">
+        <v>อ่านงบการเงินเพื่อดูสุขภาพทางการเงินของกิจการ</v>
+      </c>
+      <c r="E150" t="str">
+        <v/>
+      </c>
+      <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B151" t="str">
+        <v/>
+      </c>
+      <c r="C151" t="str">
+        <v>คณิตศาสตร์การเงิน</v>
+      </c>
+      <c r="D151" t="str">
+        <v>คำนวณดอกเบี้ย ผลตอบแทน และมูลค่าของเงินตามเวลา</v>
+      </c>
+      <c r="E151" t="str">
+        <v/>
+      </c>
+      <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B152" t="str">
+        <v/>
+      </c>
+      <c r="C152" t="str">
+        <v>สถิติ</v>
+      </c>
+      <c r="D152" t="str">
+        <v>เก็บ สรุป และตีความข้อมูลตัวเลข</v>
+      </c>
+      <c r="E152" t="str">
+        <v/>
+      </c>
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B153" t="str">
+        <v/>
+      </c>
+      <c r="C153" t="str">
+        <v>การวิเคราะห์ข้อมูลเชิงตัวเลข</v>
+      </c>
+      <c r="D153" t="str">
+        <v>หาความหมายและแนวโน้มจากตัวเลข</v>
+      </c>
+      <c r="E153" t="str">
+        <v/>
+      </c>
+      <c r="F153" t="str">
+        <v/>
+      </c>
+      <c r="G153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B154" t="str">
+        <v/>
+      </c>
+      <c r="C154" t="str">
+        <v>สถิติขั้นสูง</v>
+      </c>
+      <c r="D154" t="str">
+        <v>สร้างแบบจำลองและทดสอบสมมติฐานจากข้อมูล</v>
+      </c>
+      <c r="E154" t="str">
+        <v/>
+      </c>
+      <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B155" t="str">
+        <v/>
+      </c>
+      <c r="C155" t="str">
+        <v>การเขียนโปรแกรมวิเคราะห์ข้อมูล</v>
+      </c>
+      <c r="D155" t="str">
+        <v>ใช้โปรแกรมจัดการและคำนวณข้อมูลจำนวนมาก</v>
+      </c>
+      <c r="E155" t="str">
+        <v/>
+      </c>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B156" t="str">
+        <v/>
+      </c>
+      <c r="C156" t="str">
+        <v>ความเข้าใจระบบราชการ</v>
+      </c>
+      <c r="D156" t="str">
+        <v>รู้ขั้นตอน ระเบียบ และโครงสร้างของหน่วยงานรัฐ</v>
+      </c>
+      <c r="E156" t="str">
+        <v/>
+      </c>
+      <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B157" t="str">
+        <v/>
+      </c>
+      <c r="C157" t="str">
+        <v>การจัดการเอกสาร/ข้อมูล</v>
+      </c>
+      <c r="D157" t="str">
+        <v>จัดเก็บเอกสารและข้อมูลให้ค้นหาได้ง่ายและถูกต้อง</v>
+      </c>
+      <c r="E157" t="str">
+        <v/>
+      </c>
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B158" t="str">
+        <v/>
+      </c>
+      <c r="C158" t="str">
+        <v>การจัดการฐานข้อมูล</v>
+      </c>
+      <c r="D158" t="str">
+        <v>ออกแบบและดูแลระบบเก็บข้อมูลขององค์กร</v>
+      </c>
+      <c r="E158" t="str">
+        <v/>
+      </c>
+      <c r="F158" t="str">
+        <v/>
+      </c>
+      <c r="G158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B159" t="str">
+        <v/>
+      </c>
+      <c r="C159" t="str">
+        <v>ความเข้าใจกระบวนการธุรกิจ</v>
+      </c>
+      <c r="D159" t="str">
+        <v>รู้ว่างานแต่ละฝ่ายในองค์กรเชื่อมโยงกันอย่างไร</v>
+      </c>
+      <c r="E159" t="str">
+        <v/>
+      </c>
+      <c r="F159" t="str">
+        <v/>
+      </c>
+      <c r="G159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B160" t="str">
+        <v/>
+      </c>
+      <c r="C160" t="str">
+        <v>การวางแผนและจัดการกระบวนการ</v>
+      </c>
+      <c r="D160" t="str">
+        <v>จัดลำดับงานให้คนและทรัพยากรทำงานได้คุ้มค่า</v>
+      </c>
+      <c r="E160" t="str">
+        <v/>
+      </c>
+      <c r="F160" t="str">
+        <v/>
+      </c>
+      <c r="G160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B161" t="str">
+        <v/>
+      </c>
+      <c r="C161" t="str">
+        <v>โปรแกรมออกแบบ 3 มิติ (CAD)</v>
+      </c>
+      <c r="D161" t="str">
+        <v>สร้างแบบชิ้นงานสามมิติด้วยคอมพิวเตอร์</v>
+      </c>
+      <c r="E161" t="str">
+        <v/>
+      </c>
+      <c r="F161" t="str">
+        <v/>
+      </c>
+      <c r="G161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B162" t="str">
+        <v/>
+      </c>
+      <c r="C162" t="str">
+        <v>ความเข้าใจวัสดุและกระบวนการผลิต</v>
+      </c>
+      <c r="D162" t="str">
+        <v>รู้ว่าวัสดุแต่ละชนิดผลิตเป็นสินค้าได้อย่างไร</v>
+      </c>
+      <c r="E162" t="str">
+        <v/>
+      </c>
+      <c r="F162" t="str">
+        <v/>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B163" t="str">
+        <v/>
+      </c>
+      <c r="C163" t="str">
+        <v>ฟิสิกส์รังสี</v>
+      </c>
+      <c r="D163" t="str">
+        <v>เข้าใจรังสีชนิดต่าง ๆ และการป้องกันอันตราย</v>
+      </c>
+      <c r="E163" t="str">
+        <v/>
+      </c>
+      <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B164" t="str">
+        <v/>
+      </c>
+      <c r="C164" t="str">
+        <v>การใช้เครื่องมือถ่ายภาพทางการแพทย์</v>
+      </c>
+      <c r="D164" t="str">
+        <v>ใช้เครื่องเอกซเรย์และเครื่องสร้างภาพอวัยวะ</v>
+      </c>
+      <c r="E164" t="str">
+        <v/>
+      </c>
+      <c r="F164" t="str">
+        <v/>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B165" t="str">
+        <v/>
+      </c>
+      <c r="C165" t="str">
+        <v>ความเข้าใจเทคโนโลยี</v>
+      </c>
+      <c r="D165" t="str">
+        <v>รู้ว่าเทคโนโลยีแต่ละแบบทำอะไรได้และเหมาะกับงานใด</v>
+      </c>
+      <c r="E165" t="str">
+        <v/>
+      </c>
+      <c r="F165" t="str">
+        <v/>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B166" t="str">
+        <v/>
+      </c>
+      <c r="C166" t="str">
+        <v>การบริหารโครงการ</v>
+      </c>
+      <c r="D166" t="str">
+        <v>วางแผนเวลา งบ และคนให้งานเสร็จตามเป้า</v>
+      </c>
+      <c r="E166" t="str">
+        <v/>
+      </c>
+      <c r="F166" t="str">
+        <v/>
+      </c>
+      <c r="G166" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B167" t="str">
+        <v/>
+      </c>
+      <c r="C167" t="str">
+        <v>การวิเคราะห์ธุรกิจ</v>
+      </c>
+      <c r="D167" t="str">
+        <v>ใช้ข้อมูลหาปัญหาและโอกาสของธุรกิจ</v>
+      </c>
+      <c r="E167" t="str">
+        <v/>
+      </c>
+      <c r="F167" t="str">
+        <v/>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B168" t="str">
+        <v/>
+      </c>
+      <c r="C168" t="str">
+        <v>ระบบเครือข่าย</v>
+      </c>
+      <c r="D168" t="str">
+        <v>เชื่อมต่อคอมพิวเตอร์และอุปกรณ์ให้สื่อสารกันได้</v>
+      </c>
+      <c r="E168" t="str">
+        <v/>
+      </c>
+      <c r="F168" t="str">
+        <v/>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B169" t="str">
+        <v/>
+      </c>
+      <c r="C169" t="str">
+        <v>ฐานข้อมูล</v>
+      </c>
+      <c r="D169" t="str">
+        <v>ระบบเก็บและเรียกใช้ข้อมูลอย่างเป็นระเบียบ</v>
+      </c>
+      <c r="E169" t="str">
+        <v/>
+      </c>
+      <c r="F169" t="str">
+        <v/>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B170" t="str">
+        <v/>
+      </c>
+      <c r="C170" t="str">
+        <v>ทักษะศิลปะปฏิบัติ</v>
+      </c>
+      <c r="D170" t="str">
+        <v>ลงมือวาด ปั้น หรือสร้างงานศิลปะได้จริง</v>
+      </c>
+      <c r="E170" t="str">
+        <v/>
+      </c>
+      <c r="F170" t="str">
+        <v/>
+      </c>
+      <c r="G170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B171" t="str">
+        <v/>
+      </c>
+      <c r="C171" t="str">
+        <v>การสอนและอธิบาย</v>
+      </c>
+      <c r="D171" t="str">
+        <v>แบ่งเรื่องยากเป็นขั้นตอนให้ผู้เรียนเข้าใจ</v>
+      </c>
+      <c r="E171" t="str">
+        <v/>
+      </c>
+      <c r="F171" t="str">
+        <v/>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B172" t="str">
+        <v/>
+      </c>
+      <c r="C172" t="str">
+        <v>การออกแบบกิจกรรมการเรียนรู้</v>
+      </c>
+      <c r="D172" t="str">
+        <v>วางกิจกรรมที่ช่วยให้ผู้เรียนเข้าใจและสนุก</v>
+      </c>
+      <c r="E172" t="str">
+        <v/>
+      </c>
+      <c r="F172" t="str">
+        <v/>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B173" t="str">
+        <v/>
+      </c>
+      <c r="C173" t="str">
+        <v>การเขียนแบบ</v>
+      </c>
+      <c r="D173" t="str">
+        <v>วาดแบบที่มีขนาดและสัดส่วนถูกต้องสำหรับนำไปสร้างจริง</v>
+      </c>
+      <c r="E173" t="str">
+        <v/>
+      </c>
+      <c r="F173" t="str">
+        <v/>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B174" t="str">
+        <v/>
+      </c>
+      <c r="C174" t="str">
+        <v>การเลือกวัสดุและสี</v>
+      </c>
+      <c r="D174" t="str">
+        <v>เลือกวัสดุและสีให้เหมาะกับการใช้งานและบรรยากาศ</v>
+      </c>
+      <c r="E174" t="str">
+        <v/>
+      </c>
+      <c r="F174" t="str">
+        <v/>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B175" t="str">
+        <v/>
+      </c>
+      <c r="C175" t="str">
+        <v>ทักษะกีฬา</v>
+      </c>
+      <c r="D175" t="str">
+        <v>เล่นกีฬาได้ถูกเทคนิคและเข้าใจกติกา</v>
+      </c>
+      <c r="E175" t="str">
+        <v/>
+      </c>
+      <c r="F175" t="str">
+        <v/>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B176" t="str">
+        <v/>
+      </c>
+      <c r="C176" t="str">
+        <v>การสอนและการจัดกิจกรรม</v>
+      </c>
+      <c r="D176" t="str">
+        <v>นำกิจกรรมและสอนให้ผู้เข้าร่วมทำตามได้</v>
+      </c>
+      <c r="E176" t="str">
+        <v/>
+      </c>
+      <c r="F176" t="str">
+        <v/>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B177" t="str">
+        <v/>
+      </c>
+      <c r="C177" t="str">
+        <v>ความรู้สุขภาพและสรีรวิทยา</v>
+      </c>
+      <c r="D177" t="str">
+        <v>เข้าใจการทำงานของร่างกายและการดูแลสุขภาพ</v>
+      </c>
+      <c r="E177" t="str">
+        <v/>
+      </c>
+      <c r="F177" t="str">
+        <v/>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B178" t="str">
+        <v/>
+      </c>
+      <c r="C178" t="str">
+        <v>การประเมินความเสี่ยง</v>
+      </c>
+      <c r="D178" t="str">
+        <v>มองหาสิ่งที่อาจเกิดอันตรายและหาทางป้องกัน</v>
+      </c>
+      <c r="E178" t="str">
+        <v/>
+      </c>
+      <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B179" t="str">
+        <v/>
+      </c>
+      <c r="C179" t="str">
+        <v>กฎหมายความปลอดภัย</v>
+      </c>
+      <c r="D179" t="str">
+        <v>รู้ข้อกำหนดด้านความปลอดภัยในการทำงานตามกฎหมาย</v>
+      </c>
+      <c r="E179" t="str">
+        <v/>
+      </c>
+      <c r="F179" t="str">
+        <v/>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B180" t="str">
+        <v/>
+      </c>
+      <c r="C180" t="str">
+        <v>ความรู้ด้านวิศวกรรมพื้นฐาน</v>
+      </c>
+      <c r="D180" t="str">
+        <v>หลักการทางวิศวกรรมที่ใช้ในเครื่องจักรและอาคาร</v>
+      </c>
+      <c r="E180" t="str">
+        <v/>
+      </c>
+      <c r="F180" t="str">
+        <v/>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B181" t="str">
+        <v/>
+      </c>
+      <c r="C181" t="str">
+        <v>วิทยาศาสตร์สิ่งแวดล้อม</v>
+      </c>
+      <c r="D181" t="str">
+        <v>เข้าใจดิน น้ำ อากาศ และผลกระทบจากกิจกรรมของมนุษย์</v>
+      </c>
+      <c r="E181" t="str">
+        <v/>
+      </c>
+      <c r="F181" t="str">
+        <v/>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B182" t="str">
+        <v/>
+      </c>
+      <c r="C182" t="str">
+        <v>การเก็บและวิเคราะห์ข้อมูลภาคสนาม</v>
+      </c>
+      <c r="D182" t="str">
+        <v>เก็บตัวอย่างในพื้นที่จริงแล้วนำมาวิเคราะห์</v>
+      </c>
+      <c r="E182" t="str">
+        <v/>
+      </c>
+      <c r="F182" t="str">
+        <v/>
+      </c>
+      <c r="G182" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B183" t="str">
+        <v/>
+      </c>
+      <c r="C183" t="str">
+        <v>กฎหมายสิ่งแวดล้อม</v>
+      </c>
+      <c r="D183" t="str">
+        <v>รู้ข้อกำหนดทางกฎหมายเกี่ยวกับมลพิษและทรัพยากร</v>
+      </c>
+      <c r="E183" t="str">
+        <v/>
+      </c>
+      <c r="F183" t="str">
+        <v/>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B184" t="str">
+        <v/>
+      </c>
+      <c r="C184" t="str">
+        <v>การปฐมพยาบาลและช่วยชีวิต</v>
+      </c>
+      <c r="D184" t="str">
+        <v>ช่วยเหลือผู้บาดเจ็บเบื้องต้น เช่น การทำ CPR</v>
+      </c>
+      <c r="E184" t="str">
+        <v/>
+      </c>
+      <c r="F184" t="str">
+        <v/>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B185" t="str">
+        <v/>
+      </c>
+      <c r="C185" t="str">
+        <v>การตัดสินใจภายใต้ความกดดัน</v>
+      </c>
+      <c r="D185" t="str">
+        <v>เลือกทางที่เหมาะสมได้รวดเร็วในสถานการณ์เร่งด่วน</v>
+      </c>
+      <c r="E185" t="str">
+        <v/>
+      </c>
+      <c r="F185" t="str">
+        <v/>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B186" t="str">
+        <v/>
+      </c>
+      <c r="C186" t="str">
+        <v>การทำงานเป็นทีม</v>
+      </c>
+      <c r="D186" t="str">
+        <v>แบ่งหน้าที่และช่วยเหลือกันจนงานสำเร็จ</v>
+      </c>
+      <c r="E186" t="str">
+        <v/>
+      </c>
+      <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B187" t="str">
+        <v/>
+      </c>
+      <c r="C187" t="str">
+        <v>การประกอบอาหาร</v>
+      </c>
+      <c r="D187" t="str">
+        <v>ทำอาหารได้ถูกวิธี ถูกสุขอนามัย และอร่อย</v>
+      </c>
+      <c r="E187" t="str">
+        <v/>
+      </c>
+      <c r="F187" t="str">
+        <v/>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B188" t="str">
+        <v/>
+      </c>
+      <c r="C188" t="str">
+        <v>การบริหารต้นทุน</v>
+      </c>
+      <c r="D188" t="str">
+        <v>ควบคุมค่าใช้จ่ายให้ธุรกิจมีกำไร</v>
+      </c>
+      <c r="E188" t="str">
+        <v/>
+      </c>
+      <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B189" t="str">
+        <v/>
+      </c>
+      <c r="C189" t="str">
+        <v>การวางแผนการผลิต</v>
+      </c>
+      <c r="D189" t="str">
+        <v>กำหนดว่าจะผลิตอะไร เท่าไร และเมื่อไร</v>
+      </c>
+      <c r="E189" t="str">
+        <v/>
+      </c>
+      <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B190" t="str">
+        <v/>
+      </c>
+      <c r="C190" t="str">
+        <v>การควบคุมคุณภาพ</v>
+      </c>
+      <c r="D190" t="str">
+        <v>ตรวจสินค้าหรืองานให้ได้ตามมาตรฐาน</v>
+      </c>
+      <c r="E190" t="str">
+        <v/>
+      </c>
+      <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B191" t="str">
+        <v/>
+      </c>
+      <c r="C191" t="str">
+        <v>โครงสร้างข้อมูลและอัลกอริทึม</v>
+      </c>
+      <c r="D191" t="str">
+        <v>วิธีจัดเก็บข้อมูลและขั้นตอนแก้ปัญหาในโปรแกรม</v>
+      </c>
+      <c r="E191" t="str">
+        <v/>
+      </c>
+      <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B192" t="str">
+        <v/>
+      </c>
+      <c r="C192" t="str">
+        <v>ระบบคอมพิวเตอร์และฮาร์ดแวร์</v>
+      </c>
+      <c r="D192" t="str">
+        <v>เข้าใจชิ้นส่วนและการทำงานภายในคอมพิวเตอร์</v>
+      </c>
+      <c r="E192" t="str">
+        <v/>
+      </c>
+      <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B193" t="str">
+        <v/>
+      </c>
+      <c r="C193" t="str">
+        <v>ความรู้แร่และอัญมณี</v>
+      </c>
+      <c r="D193" t="str">
+        <v>รู้จักชนิดและคุณสมบัติของแร่และพลอย</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v/>
+      </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
+        <v>การออกแบบเครื่องประดับ</v>
+      </c>
+      <c r="D194" t="str">
+        <v>ออกแบบแหวน สร้อย หรือเครื่องประดับให้สวยและสวมใส่ได้</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B195" t="str">
+        <v/>
+      </c>
+      <c r="C195" t="str">
+        <v>การใช้เครื่องมือตรวจสอบ</v>
+      </c>
+      <c r="D195" t="str">
+        <v>ใช้เครื่องมือวัดและตรวจคุณภาพอย่างถูกวิธี</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
+        <v>เทคโนโลยีการพิมพ์</v>
+      </c>
+      <c r="D196" t="str">
+        <v>เข้าใจเครื่องพิมพ์และกระบวนการพิมพ์แบบต่าง ๆ</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v/>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
+        <v>การจัดการสีและภาพ</v>
+      </c>
+      <c r="D197" t="str">
+        <v>ปรับสีและภาพให้ตรงกันทั้งบนจอและงานพิมพ์</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v/>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>การควบคุมคุณภาพการผลิต</v>
+      </c>
+      <c r="D198" t="str">
+        <v>ตรวจงานในแต่ละขั้นตอนการผลิตให้ได้มาตรฐาน</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v/>
+      </c>
+      <c r="G198" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>สุขศาสตร์อุตสาหกรรม</v>
+      </c>
+      <c r="D199" t="str">
+        <v>ป้องกันอันตรายต่อสุขภาพจากสภาพแวดล้อมในที่ทำงาน</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>วิศวกรรมไฟฟ้า/อิเล็กทรอนิกส์</v>
+      </c>
+      <c r="D200" t="str">
+        <v>หลักการของวงจรและอุปกรณ์อิเล็กทรอนิกส์</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v/>
+      </c>
+      <c r="G200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>ชีววิทยาและสรีรวิทยา</v>
+      </c>
+      <c r="D201" t="str">
+        <v>เข้าใจสิ่งมีชีวิตและการทำงานของร่างกาย</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v/>
+      </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>การออกแบบอุปกรณ์</v>
+      </c>
+      <c r="D202" t="str">
+        <v>ออกแบบเครื่องมือให้ใช้งานได้จริงและปลอดภัย</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v/>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>กราฟิกคอมพิวเตอร์</v>
+      </c>
+      <c r="D203" t="str">
+        <v>สร้างภาพและภาพเคลื่อนไหวด้วยคอมพิวเตอร์</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v/>
+      </c>
+      <c r="G203" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>การประมวลผลภาพและเสียง</v>
+      </c>
+      <c r="D204" t="str">
+        <v>ปรับแต่งและวิเคราะห์ภาพหรือเสียงด้วยโปรแกรม</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>การคิดเชิงออกแบบ (Design Thinking)</v>
+      </c>
+      <c r="D205" t="str">
+        <v>เริ่มจากเข้าใจผู้ใช้ แล้วทดลองหาทางแก้ปัญหาซ้ำจนได้ผล</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>การทำงานกับชุมชน</v>
+      </c>
+      <c r="D206" t="str">
+        <v>ลงพื้นที่ รับฟัง และทำงานร่วมกับคนในชุมชน</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>การวิจัยผู้ใช้</v>
+      </c>
+      <c r="D207" t="str">
+        <v>สัมภาษณ์และสังเกตผู้ใช้เพื่อเข้าใจความต้องการจริง</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>การออกแบบหน้าจอ (Figma)</v>
+      </c>
+      <c r="D208" t="str">
+        <v>ออกแบบหน้าตาแอปหรือเว็บด้วยโปรแกรม Figma</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v/>
+      </c>
+      <c r="G208" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>การคิดเชิงออกแบบ</v>
+      </c>
+      <c r="D209" t="str">
+        <v>เริ่มจากเข้าใจผู้ใช้ แล้วทดลองหาทางแก้ปัญหาซ้ำจนได้ผล</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v/>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>การเขียนโปรแกรม (Python)</v>
+      </c>
+      <c r="D210" t="str">
+        <v>เขียนโปรแกรมด้วยภาษา Python ซึ่งนิยมใช้กับงานข้อมูล</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>การนำเสนอข้อมูลด้วยภาพ</v>
+      </c>
+      <c r="D211" t="str">
+        <v>ทำกราฟหรืออินโฟกราฟิกให้ข้อมูลเข้าใจง่าย</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>การวิจัยภาคสนาม</v>
+      </c>
+      <c r="D212" t="str">
+        <v>เก็บข้อมูลจากคนหรือพื้นที่จริงอย่างเป็นระบบ</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v/>
+      </c>
+      <c r="G212" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>การวิเคราะห์ประเด็นสังคม</v>
+      </c>
+      <c r="D213" t="str">
+        <v>มองปัญหาสังคมจากหลายมุมและหาสาเหตุ</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v/>
+      </c>
+      <c r="G213" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>การเขียนรายงาน</v>
+      </c>
+      <c r="D214" t="str">
+        <v>สรุปข้อมูลเป็นรายงานที่ชัดเจนและมีที่มา</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v/>
+      </c>
+      <c r="G214" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
+        <v>โภชนศาสตร์</v>
+      </c>
+      <c r="D215" t="str">
+        <v>ความรู้เรื่องสารอาหารและผลต่อร่างกาย</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v/>
+      </c>
+      <c r="G215" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B216" t="str">
+        <v/>
+      </c>
+      <c r="C216" t="str">
+        <v>การให้คำปรึกษาด้านอาหาร</v>
+      </c>
+      <c r="D216" t="str">
+        <v>แนะนำการกินให้เหมาะกับสุขภาพของแต่ละคน</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
+        <v/>
+      </c>
+      <c r="G216" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B217" t="str">
+        <v/>
+      </c>
+      <c r="C217" t="str">
+        <v>การวิเคราะห์โครงสร้างภาษา</v>
+      </c>
+      <c r="D217" t="str">
+        <v>ศึกษาเสียง คำ และไวยากรณ์ของภาษา</v>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
+        <v/>
+      </c>
+      <c r="G217" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B218" t="str">
+        <v/>
+      </c>
+      <c r="C218" t="str">
+        <v>การใช้เครื่องมือวิเคราะห์ภาษา</v>
+      </c>
+      <c r="D218" t="str">
+        <v>ใช้โปรแกรมช่วยศึกษาข้อมูลภาษาจำนวนมาก</v>
+      </c>
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" t="str">
+        <v/>
+      </c>
+      <c r="G218" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B219" t="str">
+        <v/>
+      </c>
+      <c r="C219" t="str">
+        <v>การจัดระบบข้อมูล</v>
+      </c>
+      <c r="D219" t="str">
+        <v>จัดหมวดหมู่ข้อมูลให้ค้นหาและใช้ต่อได้ง่าย</v>
+      </c>
+      <c r="E219" t="str">
+        <v/>
+      </c>
+      <c r="F219" t="str">
+        <v/>
+      </c>
+      <c r="G219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B220" t="str">
+        <v/>
+      </c>
+      <c r="C220" t="str">
+        <v>การสืบค้นสารสนเทศ</v>
+      </c>
+      <c r="D220" t="str">
+        <v>หาข้อมูลจากแหล่งที่น่าเชื่อถือได้อย่างรวดเร็ว</v>
+      </c>
+      <c r="E220" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
+        <v/>
+      </c>
+      <c r="G220" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B221" t="str">
+        <v/>
+      </c>
+      <c r="C221" t="str">
+        <v>เทคโนโลยีฐานข้อมูล</v>
+      </c>
+      <c r="D221" t="str">
+        <v>ระบบและโปรแกรมที่ใช้เก็บและค้นข้อมูล</v>
+      </c>
+      <c r="E221" t="str">
+        <v/>
+      </c>
+      <c r="F221" t="str">
+        <v/>
+      </c>
+      <c r="G221" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B222" t="str">
+        <v/>
+      </c>
+      <c r="C222" t="str">
+        <v>รหัสโรคและหัตถการ (ICD)</v>
+      </c>
+      <c r="D222" t="str">
+        <v>ใช้รหัสมาตรฐานบันทึกโรคและการรักษา</v>
+      </c>
+      <c r="E222" t="str">
+        <v/>
+      </c>
+      <c r="F222" t="str">
+        <v/>
+      </c>
+      <c r="G222" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B223" t="str">
+        <v/>
+      </c>
+      <c r="C223" t="str">
+        <v>การจัดการข้อมูลสุขภาพ</v>
+      </c>
+      <c r="D223" t="str">
+        <v>ดูแลข้อมูลผู้ป่วยให้ถูกต้อง ครบถ้วน และปลอดภัย</v>
+      </c>
+      <c r="E223" t="str">
+        <v/>
+      </c>
+      <c r="F223" t="str">
+        <v/>
+      </c>
+      <c r="G223" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B224" t="str">
+        <v/>
+      </c>
+      <c r="C224" t="str">
+        <v>ทักษะการแสดงและนาฏศิลป์</v>
+      </c>
+      <c r="D224" t="str">
+        <v>รำ เต้น หรือแสดงได้ถูกท่าทางและมีอารมณ์</v>
+      </c>
+      <c r="E224" t="str">
+        <v/>
+      </c>
+      <c r="F224" t="str">
+        <v/>
+      </c>
+      <c r="G224" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B225" t="str">
+        <v/>
+      </c>
+      <c r="C225" t="str">
+        <v>การสื่อสารด้วยร่างกาย</v>
+      </c>
+      <c r="D225" t="str">
+        <v>ใช้ท่าทางและสีหน้าสื่ออารมณ์และความหมาย</v>
+      </c>
+      <c r="E225" t="str">
+        <v/>
+      </c>
+      <c r="F225" t="str">
+        <v/>
+      </c>
+      <c r="G225" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B226" t="str">
+        <v/>
+      </c>
+      <c r="C226" t="str">
+        <v>การทำงานเป็นคณะ</v>
+      </c>
+      <c r="D226" t="str">
+        <v>ซ้อมและแสดงร่วมกับผู้อื่นอย่างพร้อมเพรียง</v>
+      </c>
+      <c r="E226" t="str">
+        <v/>
+      </c>
+      <c r="F226" t="str">
+        <v/>
+      </c>
+      <c r="G226" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B227" t="str">
+        <v/>
+      </c>
+      <c r="C227" t="str">
+        <v>การจัดองค์ประกอบ</v>
+      </c>
+      <c r="D227" t="str">
+        <v>จัดวางภาพ ตัวอักษร และพื้นที่ว่างให้ดูดีและอ่านง่าย</v>
+      </c>
+      <c r="E227" t="str">
+        <v/>
+      </c>
+      <c r="F227" t="str">
+        <v/>
+      </c>
+      <c r="G227" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B228" t="str">
+        <v/>
+      </c>
+      <c r="C228" t="str">
+        <v>ตัวอักษรและสี</v>
+      </c>
+      <c r="D228" t="str">
+        <v>เลือกแบบอักษรและคู่สีให้สื่ออารมณ์ของงาน</v>
+      </c>
+      <c r="E228" t="str">
+        <v/>
+      </c>
+      <c r="F228" t="str">
+        <v/>
+      </c>
+      <c r="G228" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B229" t="str">
+        <v/>
+      </c>
+      <c r="C229" t="str">
+        <v>โปรแกรมกราฟิก</v>
+      </c>
+      <c r="D229" t="str">
+        <v>ใช้โปรแกรมอย่าง Photoshop หรือ Illustrator สร้างงาน</v>
+      </c>
+      <c r="E229" t="str">
+        <v/>
+      </c>
+      <c r="F229" t="str">
+        <v/>
+      </c>
+      <c r="G229" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B230" t="str">
+        <v/>
+      </c>
+      <c r="C230" t="str">
+        <v>การเขียนโปรแกรมเกม</v>
+      </c>
+      <c r="D230" t="str">
+        <v>เขียนโค้ดให้ตัวละครและระบบในเกมทำงาน</v>
+      </c>
+      <c r="E230" t="str">
+        <v/>
+      </c>
+      <c r="F230" t="str">
+        <v/>
+      </c>
+      <c r="G230" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B231" t="str">
+        <v/>
+      </c>
+      <c r="C231" t="str">
+        <v>Game Engine (Unity/Unreal)</v>
+      </c>
+      <c r="D231" t="str">
+        <v>ใช้โปรแกรมสร้างเกมที่นิยมในวงการ</v>
+      </c>
+      <c r="E231" t="str">
+        <v/>
+      </c>
+      <c r="F231" t="str">
+        <v/>
+      </c>
+      <c r="G231" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B232" t="str">
+        <v/>
+      </c>
+      <c r="C232" t="str">
+        <v>การออกแบบเกมเพลย์</v>
+      </c>
+      <c r="D232" t="str">
+        <v>ออกแบบกติกาและความท้าทายให้เกมสนุก</v>
+      </c>
+      <c r="E232" t="str">
+        <v/>
+      </c>
+      <c r="F232" t="str">
+        <v/>
+      </c>
+      <c r="G232" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B233" t="str">
+        <v/>
+      </c>
+      <c r="C233" t="str">
+        <v>การวางแผนงาน</v>
+      </c>
+      <c r="D233" t="str">
+        <v>กำหนดขั้นตอน เวลา และผู้รับผิดชอบก่อนเริ่มงาน</v>
+      </c>
+      <c r="E233" t="str">
+        <v/>
+      </c>
+      <c r="F233" t="str">
+        <v/>
+      </c>
+      <c r="G233" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B234" t="str">
+        <v/>
+      </c>
+      <c r="C234" t="str">
+        <v>การประสานงาน</v>
+      </c>
+      <c r="D234" t="str">
+        <v>ติดต่อหลายฝ่ายให้ทำงานไปพร้อมกันได้</v>
+      </c>
+      <c r="E234" t="str">
+        <v/>
+      </c>
+      <c r="F234" t="str">
+        <v/>
+      </c>
+      <c r="G234" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B235" t="str">
+        <v/>
+      </c>
+      <c r="C235" t="str">
+        <v>การบริหารงบประมาณ</v>
+      </c>
+      <c r="D235" t="str">
+        <v>วางแผนและควบคุมการใช้เงินให้พอและคุ้มค่า</v>
+      </c>
+      <c r="E235" t="str">
+        <v/>
+      </c>
+      <c r="F235" t="str">
+        <v/>
+      </c>
+      <c r="G235" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B236" t="str">
+        <v/>
+      </c>
+      <c r="C236" t="str">
+        <v>การเขียนข่าว</v>
+      </c>
+      <c r="D236" t="str">
+        <v>เรียบเรียงข้อเท็จจริงให้กระชับ ชัดเจน และเป็นกลาง</v>
+      </c>
+      <c r="E236" t="str">
+        <v/>
+      </c>
+      <c r="F236" t="str">
+        <v/>
+      </c>
+      <c r="G236" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B237" t="str">
+        <v/>
+      </c>
+      <c r="C237" t="str">
+        <v>การสัมภาษณ์</v>
+      </c>
+      <c r="D237" t="str">
+        <v>ตั้งคำถามและฟังเพื่อได้ข้อมูลที่ต้องการ</v>
+      </c>
+      <c r="E237" t="str">
+        <v/>
+      </c>
+      <c r="F237" t="str">
+        <v/>
+      </c>
+      <c r="G237" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B238" t="str">
+        <v/>
+      </c>
+      <c r="C238" t="str">
+        <v>การตรวจสอบข้อเท็จจริง</v>
+      </c>
+      <c r="D238" t="str">
+        <v>เช็กว่าข้อมูลถูกต้องจากหลายแหล่งก่อนเผยแพร่</v>
+      </c>
+      <c r="E238" t="str">
+        <v/>
+      </c>
+      <c r="F238" t="str">
+        <v/>
+      </c>
+      <c r="G238" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B239" t="str">
+        <v/>
+      </c>
+      <c r="C239" t="str">
+        <v>การสร้างแบรนด์</v>
+      </c>
+      <c r="D239" t="str">
+        <v>ทำให้คนจดจำและรู้สึกดีกับสินค้าหรือองค์กร</v>
+      </c>
+      <c r="E239" t="str">
+        <v/>
+      </c>
+      <c r="F239" t="str">
+        <v/>
+      </c>
+      <c r="G239" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B240" t="str">
+        <v/>
+      </c>
+      <c r="C240" t="str">
+        <v>การทำคอนเทนต์</v>
+      </c>
+      <c r="D240" t="str">
+        <v>สร้างโพสต์ วิดีโอ หรือบทความให้น่าสนใจ</v>
+      </c>
+      <c r="E240" t="str">
+        <v/>
+      </c>
+      <c r="F240" t="str">
+        <v/>
+      </c>
+      <c r="G240" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B241" t="str">
+        <v/>
+      </c>
+      <c r="C241" t="str">
+        <v>การวิเคราะห์ข้อมูลการตลาด</v>
+      </c>
+      <c r="D241" t="str">
+        <v>ดูยอดขายและพฤติกรรมลูกค้าจากข้อมูล</v>
+      </c>
+      <c r="E241" t="str">
+        <v/>
+      </c>
+      <c r="F241" t="str">
+        <v/>
+      </c>
+      <c r="G241" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B242" t="str">
+        <v/>
+      </c>
+      <c r="C242" t="str">
+        <v>ความเข้าใจธุรกิจสื่อและวัฒนธรรม</v>
+      </c>
+      <c r="D242" t="str">
+        <v>รู้ว่างานสร้างสรรค์สร้างรายได้และถึงผู้ชมอย่างไร</v>
+      </c>
+      <c r="E242" t="str">
+        <v/>
+      </c>
+      <c r="F242" t="str">
+        <v/>
+      </c>
+      <c r="G242" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B243" t="str">
+        <v/>
+      </c>
+      <c r="C243" t="str">
+        <v>การตลาด</v>
+      </c>
+      <c r="D243" t="str">
+        <v>ทำให้สินค้าเป็นที่รู้จักและมีคนอยากซื้อ</v>
+      </c>
+      <c r="E243" t="str">
+        <v/>
+      </c>
+      <c r="F243" t="str">
+        <v/>
+      </c>
+      <c r="G243" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B244" t="str">
+        <v/>
+      </c>
+      <c r="C244" t="str">
+        <v>การผลิตสื่อดิจิทัล</v>
+      </c>
+      <c r="D244" t="str">
+        <v>สร้างภาพ เสียง และวิดีโอสำหรับใช้ออนไลน์</v>
+      </c>
+      <c r="E244" t="str">
+        <v/>
+      </c>
+      <c r="F244" t="str">
+        <v/>
+      </c>
+      <c r="G244" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B245" t="str">
+        <v/>
+      </c>
+      <c r="C245" t="str">
+        <v>การออกแบบการเรียนการสอน</v>
+      </c>
+      <c r="D245" t="str">
+        <v>วางเนื้อหาและวิธีสอนให้ผู้เรียนบรรลุเป้าหมาย</v>
+      </c>
+      <c r="E245" t="str">
+        <v/>
+      </c>
+      <c r="F245" t="str">
+        <v/>
+      </c>
+      <c r="G245" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B246" t="str">
+        <v/>
+      </c>
+      <c r="C246" t="str">
+        <v>ระบบการเรียนออนไลน์</v>
+      </c>
+      <c r="D246" t="str">
+        <v>ใช้แพลตฟอร์มสอนและติดตามผู้เรียนผ่านอินเทอร์เน็ต</v>
+      </c>
+      <c r="E246" t="str">
+        <v/>
+      </c>
+      <c r="F246" t="str">
+        <v/>
+      </c>
+      <c r="G246" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B247" t="str">
+        <v/>
+      </c>
+      <c r="C247" t="str">
+        <v>การจัดกิจกรรม</v>
+      </c>
+      <c r="D247" t="str">
+        <v>วางแผนและดำเนินกิจกรรมให้เป็นไปตามกำหนด</v>
+      </c>
+      <c r="E247" t="str">
+        <v/>
+      </c>
+      <c r="F247" t="str">
+        <v/>
+      </c>
+      <c r="G247" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B248" t="str">
+        <v/>
+      </c>
+      <c r="C248" t="str">
+        <v>การเขียนโครงการ</v>
+      </c>
+      <c r="D248" t="str">
+        <v>เขียนแผนงานพร้อมเหตุผล งบ และผลที่คาดหวัง</v>
+      </c>
+      <c r="E248" t="str">
+        <v/>
+      </c>
+      <c r="F248" t="str">
+        <v/>
+      </c>
+      <c r="G248" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B249" t="str">
+        <v/>
+      </c>
+      <c r="C249" t="str">
+        <v>การวางแผนฉุกเฉิน</v>
+      </c>
+      <c r="D249" t="str">
+        <v>เตรียมแผนรับมือเหตุไม่คาดคิดล่วงหน้า</v>
+      </c>
+      <c r="E249" t="str">
+        <v/>
+      </c>
+      <c r="F249" t="str">
+        <v/>
+      </c>
+      <c r="G249" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B250" t="str">
+        <v/>
+      </c>
+      <c r="C250" t="str">
+        <v>การประสานงานหลายหน่วยงาน</v>
+      </c>
+      <c r="D250" t="str">
+        <v>ติดต่อหลายองค์กรให้ทำงานร่วมกันได้</v>
+      </c>
+      <c r="E250" t="str">
+        <v/>
+      </c>
+      <c r="F250" t="str">
+        <v/>
+      </c>
+      <c r="G250" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B251" t="str">
+        <v/>
+      </c>
+      <c r="C251" t="str">
+        <v>การสื่อสาร</v>
+      </c>
+      <c r="D251" t="str">
+        <v>ถ่ายทอดความคิดให้ผู้อื่นเข้าใจตรงกัน</v>
+      </c>
+      <c r="E251" t="str">
+        <v/>
+      </c>
+      <c r="F251" t="str">
+        <v/>
+      </c>
+      <c r="G251" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B252" t="str">
+        <v/>
+      </c>
+      <c r="C252" t="str">
+        <v>กฎหมายแรงงาน</v>
+      </c>
+      <c r="D252" t="str">
+        <v>รู้สิทธิและหน้าที่ของนายจ้างและลูกจ้าง</v>
+      </c>
+      <c r="E252" t="str">
+        <v/>
+      </c>
+      <c r="F252" t="str">
+        <v/>
+      </c>
+      <c r="G252" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B253" t="str">
+        <v/>
+      </c>
+      <c r="C253" t="str">
+        <v>การพัฒนาบุคลากร</v>
+      </c>
+      <c r="D253" t="str">
+        <v>ช่วยให้พนักงานเรียนรู้และเติบโตในงาน</v>
+      </c>
+      <c r="E253" t="str">
+        <v/>
+      </c>
+      <c r="F253" t="str">
+        <v/>
+      </c>
+      <c r="G253" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B254" t="str">
+        <v/>
+      </c>
+      <c r="C254" t="str">
+        <v>การบริหารโปรเจกต์บันเทิง</v>
+      </c>
+      <c r="D254" t="str">
+        <v>ดูแลงานคอนเสิร์ต ละคร หรือรายการให้สำเร็จ</v>
+      </c>
+      <c r="E254" t="str">
+        <v/>
+      </c>
+      <c r="F254" t="str">
+        <v/>
+      </c>
+      <c r="G254" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B255" t="str">
+        <v/>
+      </c>
+      <c r="C255" t="str">
+        <v>ทักษะภาษาต่างประเทศ</v>
+      </c>
+      <c r="D255" t="str">
+        <v>สื่อสารด้วยภาษาอื่นนอกจากภาษาไทย</v>
+      </c>
+      <c r="E255" t="str">
+        <v/>
+      </c>
+      <c r="F255" t="str">
+        <v/>
+      </c>
+      <c r="G255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B256" t="str">
+        <v/>
+      </c>
+      <c r="C256" t="str">
+        <v>การพูดนำเสนอ</v>
+      </c>
+      <c r="D256" t="str">
+        <v>พูดต่อหน้าผู้ฟังได้ชัดเจนและน่าสนใจ</v>
+      </c>
+      <c r="E256" t="str">
+        <v/>
+      </c>
+      <c r="F256" t="str">
+        <v/>
+      </c>
+      <c r="G256" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+      </c>
+      <c r="B257" t="str">
+        <v/>
+      </c>
+      <c r="C257" t="str">
+        <v>การเขียนเชิงสื่อสาร</v>
+      </c>
+      <c r="D257" t="str">
+        <v>เขียนข้อความให้กลุ่มเป้าหมายเข้าใจง่าย</v>
+      </c>
+      <c r="E257" t="str">
+        <v/>
+      </c>
+      <c r="F257" t="str">
+        <v/>
+      </c>
+      <c r="G257" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
         <v>ประโยคแม่แบบ</v>
       </c>
-      <c r="B47" t="str">
-        <v/>
-      </c>
-      <c r="C47" t="str">
+      <c r="B258" t="str">
+        <v/>
+      </c>
+      <c r="C258" t="str">
+        <v>ประโยคสรุปความสนใจ</v>
+      </c>
+      <c r="D258" t="str">
+        <v>คุณมีความสนใจเด่นด้าน{ด้านอันดับ 1–2}[ในระดับใกล้เคียงกัน] + ขณะเดียวกันก็มีความสนใจด้าน{ด้านที่เหลือ}ในระดับใกล้เคียงกัน / รองลงมาคือด้าน{…}</v>
+      </c>
+      <c r="E258" t="str">
+        <v/>
+      </c>
+      <c r="F258" t="str">
+        <v/>
+      </c>
+      <c r="G258" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>ประโยคแม่แบบ</v>
+      </c>
+      <c r="B259" t="str">
+        <v/>
+      </c>
+      <c r="C259" t="str">
+        <v>เหตุผลสาขาที่ควรสำรวจ</v>
+      </c>
+      <c r="D259" t="str">
+        <v>สาขานี้อาจเป็นทางเลือกที่น่าสำรวจสำหรับคุณ เนื่องจากเกี่ยวข้องกับ{วลีของสาขา} ซึ่งเชื่อมโยงกับความสนใจด้าน{…}ของคุณ</v>
+      </c>
+      <c r="E259" t="str">
+        <v/>
+      </c>
+      <c r="F259" t="str">
+        <v/>
+      </c>
+      <c r="G259" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>ประโยคแม่แบบ</v>
+      </c>
+      <c r="B260" t="str">
+        <v/>
+      </c>
+      <c r="C260" t="str">
+        <v>การ์ดเป้าหมาย</v>
+      </c>
+      <c r="D260" t="str">
+        <v>สาขานี้เน้น{วลีของสาขา} ซึ่งเชื่อมโยงกับความสนใจด้าน{…}ของคุณ ลองทำกิจกรรมจริงตามข้อด้านล่าง แล้วสังเกตว่าคุณสนุกกับงานลักษณะนี้มากน้อยเพียงใด</v>
+      </c>
+      <c r="E260" t="str">
+        <v/>
+      </c>
+      <c r="F260" t="str">
+        <v/>
+      </c>
+      <c r="G260" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>ประโยคแม่แบบ</v>
+      </c>
+      <c r="B261" t="str">
+        <v/>
+      </c>
+      <c r="C261" t="str">
+        <v>กรณีระดับต่ำ</v>
+      </c>
+      <c r="D261" t="str">
+        <v>ความสนใจที่โดดเด่นของคุณอาจแตกต่างจากลักษณะการเรียนหรือการทำงานบางส่วนของสาขานี้ แต่ไม่ได้หมายความว่าคุณเรียนสาขานี้ไม่ได้ หากสาขานี้ยังเป็นเป้าหมาย ลองศึกษารายวิชาและลักษณะการเรียนจริง และทดลองกิจกรรมด้าน{…} เพื่อสำรวจว่าคุณชอบและอยากพัฒนาทักษะด้านใดเพิ่ม</v>
+      </c>
+      <c r="E261" t="str">
+        <v/>
+      </c>
+      <c r="F261" t="str">
+        <v/>
+      </c>
+      <c r="G261" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>ประโยคแม่แบบ</v>
+      </c>
+      <c r="B262" t="str">
+        <v/>
+      </c>
+      <c r="C262" t="str">
+        <v>ข้อจำกัดของผล</v>
+      </c>
+      <c r="D262" t="str">
+        <v>การเชื่อมโยงนี้สะท้อนความสนใจ ไม่ใช่การยืนยันความพร้อมในการเรียนหรือโอกาสสอบติด</v>
+      </c>
+      <c r="E262" t="str">
+        <v/>
+      </c>
+      <c r="F262" t="str">
+        <v/>
+      </c>
+      <c r="G262" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>ประโยคแม่แบบ</v>
+      </c>
+      <c r="B263" t="str">
+        <v/>
+      </c>
+      <c r="C263" t="str">
         <v>สาขาทางเลือกของเป้าหมาย</v>
       </c>
-      <c r="D47" t="str">
+      <c r="D263" t="str">
         <v>เหมาะสำหรับการสำรวจเพิ่มเติม หากสนใจงานด้าน{งานร่วม} โดยมีส่วนที่แตกต่างจาก{เป้าหมาย}คือการเรียนด้าน{ทักษะที่ต่าง}</v>
       </c>
-      <c r="E47" t="str">
-        <v/>
-      </c>
-      <c r="F47" t="str">
-        <v/>
-      </c>
-      <c r="G47" t="str">
+      <c r="E263" t="str">
+        <v/>
+      </c>
+      <c r="F263" t="str">
+        <v/>
+      </c>
+      <c r="G263" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G263"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
+++ b/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
@@ -10714,7 +10714,7 @@
         <v>recommended</v>
       </c>
       <c r="D38" t="str">
-        <v>ตาราง 120 รหัสในข้อมูลแนะแนวของโรงเรียนแนะนำสาขานี้สำหรับรหัสของคุณ</v>
+        <v>สาขานี้เป็นหนึ่งในสาขาที่แนะนำสำหรับรหัสความสนใจของคุณ</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -10737,7 +10737,7 @@
         <v>main</v>
       </c>
       <c r="D39" t="str">
-        <v>สาขานี้ไม่อยู่ในรายการแนะนำของรหัสคุณ แต่ด้านหลักของสาขาเป็นหนึ่งในความสนใจเด่นของคุณ (อันดับ 1–3 รวมคะแนนเท่ากัน)</v>
+        <v>สาขานี้ใช้ความสนใจด้าน{ด้าน}เป็นหลัก ซึ่งเป็นหนึ่งในความสนใจเด่นของคุณ</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -10760,7 +10760,7 @@
         <v>partial</v>
       </c>
       <c r="D40" t="str">
-        <v>ด้านหลักของสาขายังไม่อยู่ในความสนใจเด่นของคุณ แต่มีคุณลักษณะบางข้อของสาขาที่เชื่อมกับความสนใจเด่น</v>
+        <v>สาขานี้ใช้ความสนใจด้าน{ด้าน}เป็นหลัก ซึ่งยังไม่ใช่ความสนใจเด่นของคุณ แต่บางส่วนของสาขาเชื่อมกับสิ่งที่คุณสนใจ</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -10783,7 +10783,7 @@
         <v>none</v>
       </c>
       <c r="D41" t="str">
-        <v>ด้านหลักของสาขายังไม่อยู่ในความสนใจเด่นของคุณ และยังไม่พบคุณลักษณะของสาขาที่เชื่อมกับความสนใจเด่น</v>
+        <v>สาขานี้ใช้ความสนใจด้าน{ด้าน}เป็นหลัก ซึ่งยังไม่ใช่ความสนใจเด่นของคุณ</v>
       </c>
       <c r="E41" t="str">
         <v/>

--- a/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
+++ b/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
@@ -426,7 +426,7 @@
         <v>สร้างเมื่อ</v>
       </c>
       <c r="B2" t="str">
-        <v>14 ตุลาคม 2569</v>
+        <v>15 ตุลาคม 2569</v>
       </c>
     </row>
     <row r="3">
@@ -9841,7 +9841,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G263"/>
+  <dimension ref="A1:G264"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" customWidth="1"/>
@@ -10714,7 +10714,7 @@
         <v>recommended</v>
       </c>
       <c r="D38" t="str">
-        <v>สาขานี้เป็นหนึ่งในสาขาที่แนะนำสำหรับรหัสความสนใจของคุณ</v>
+        <v>สอดคล้องสูง เพราะสาขานี้แนะนำสำหรับคนที่สนใจด้าน{ด้านของรหัส} แบบเดียวกับคุณ</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -10734,10 +10734,10 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>main</v>
+        <v>recommendedDim</v>
       </c>
       <c r="D39" t="str">
-        <v>สาขานี้ใช้ความสนใจด้าน{ด้าน}เป็นหลัก ซึ่งเป็นหนึ่งในความสนใจเด่นของคุณ</v>
+        <v xml:space="preserve"> โดยใช้ความสนใจด้าน{ด้าน}เป็นหลัก ซึ่งเป็นความสนใจ{อันดับ} ของคุณ</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -10757,10 +10757,10 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>partial</v>
+        <v>main</v>
       </c>
       <c r="D40" t="str">
-        <v>สาขานี้ใช้ความสนใจด้าน{ด้าน}เป็นหลัก ซึ่งยังไม่ใช่ความสนใจเด่นของคุณ แต่บางส่วนของสาขาเชื่อมกับสิ่งที่คุณสนใจ</v>
+        <v>สอดคล้องปานกลาง เพราะสาขานี้ใช้ความสนใจด้าน{ด้าน}เป็นหลัก ซึ่งเป็นความสนใจ{อันดับ} ของคุณ แต่ยังไม่ใช่สาขาที่แนะนำโดยตรงสำหรับรหัส {รหัส}</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -10780,10 +10780,10 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>none</v>
+        <v>partial</v>
       </c>
       <c r="D41" t="str">
-        <v>สาขานี้ใช้ความสนใจด้าน{ด้าน}เป็นหลัก ซึ่งยังไม่ใช่ความสนใจเด่นของคุณ</v>
+        <v>สอดคล้องต่ำ เพราะสาขานี้ใช้ความสนใจด้าน{ด้าน}เป็นหลัก ซึ่งอยู่{อันดับ} ของคุณ ยังไม่ใช่ความสนใจเด่น แต่บางส่วนของสาขา{วลี}เชื่อมกับความสนใจด้าน{ด้านที่เชื่อม}ของคุณ</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -10797,16 +10797,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
+        <v>เหตุผลของระดับความสอดคล้อง</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>คณิตศาสตร์-ฟิสิกส์ประยุกต์</v>
+        <v>none</v>
       </c>
       <c r="D42" t="str">
-        <v>ใช้คณิตศาสตร์และฟิสิกส์คำนวณแรงและโครงสร้างในงานจริง</v>
+        <v>สอดคล้องต่ำ เพราะสาขานี้ใช้ความสนใจด้าน{ด้าน}เป็นหลัก ซึ่งอยู่{อันดับ} ของคุณ ยังไม่ใช่ความสนใจเด่น</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -10826,10 +10826,10 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>การอ่านแบบก่อสร้าง</v>
+        <v>คณิตศาสตร์-ฟิสิกส์ประยุกต์</v>
       </c>
       <c r="D43" t="str">
-        <v>อ่านแบบแปลน รูปตัด และสัญลักษณ์ในแบบก่อสร้าง</v>
+        <v>ใช้คณิตศาสตร์และฟิสิกส์คำนวณแรงและโครงสร้างในงานจริง</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -10849,10 +10849,10 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>การใช้โปรแกรม CAD</v>
+        <v>การอ่านแบบก่อสร้าง</v>
       </c>
       <c r="D44" t="str">
-        <v>เขียนแบบและออกแบบชิ้นงานด้วยคอมพิวเตอร์</v>
+        <v>อ่านแบบแปลน รูปตัด และสัญลักษณ์ในแบบก่อสร้าง</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -10872,10 +10872,10 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>กลศาสตร์</v>
+        <v>การใช้โปรแกรม CAD</v>
       </c>
       <c r="D45" t="str">
-        <v>เข้าใจแรง การเคลื่อนที่ และการรับน้ำหนักของวัตถุ</v>
+        <v>เขียนแบบและออกแบบชิ้นงานด้วยคอมพิวเตอร์</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -10895,10 +10895,10 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>การออกแบบเชิงกล</v>
+        <v>กลศาสตร์</v>
       </c>
       <c r="D46" t="str">
-        <v>ออกแบบชิ้นส่วนเครื่องจักรให้ทำงานได้และแข็งแรงพอ</v>
+        <v>เข้าใจแรง การเคลื่อนที่ และการรับน้ำหนักของวัตถุ</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -10918,10 +10918,10 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>การใช้ซอฟต์แวร์จำลอง (CAE)</v>
+        <v>การออกแบบเชิงกล</v>
       </c>
       <c r="D47" t="str">
-        <v>ใช้โปรแกรมทดสอบชิ้นงานในคอมพิวเตอร์ก่อนสร้างจริง</v>
+        <v>ออกแบบชิ้นส่วนเครื่องจักรให้ทำงานได้และแข็งแรงพอ</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -10941,10 +10941,10 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>วงจรไฟฟ้า</v>
+        <v>การใช้ซอฟต์แวร์จำลอง (CAE)</v>
       </c>
       <c r="D48" t="str">
-        <v>เข้าใจการไหลของกระแสไฟฟ้าและการต่อวงจร</v>
+        <v>ใช้โปรแกรมทดสอบชิ้นงานในคอมพิวเตอร์ก่อนสร้างจริง</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -10964,10 +10964,10 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>ระบบควบคุมอัตโนมัติ</v>
+        <v>วงจรไฟฟ้า</v>
       </c>
       <c r="D49" t="str">
-        <v>ทำให้เครื่องจักรหรือระบบทำงานเองตามเงื่อนไขที่ตั้งไว้</v>
+        <v>เข้าใจการไหลของกระแสไฟฟ้าและการต่อวงจร</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -10987,10 +10987,10 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>การเขียนโปรแกรมไมโครคอนโทรลเลอร์</v>
+        <v>ระบบควบคุมอัตโนมัติ</v>
       </c>
       <c r="D50" t="str">
-        <v>เขียนโปรแกรมสั่งงานบอร์ดควบคุมขนาดเล็ก เช่น Arduino</v>
+        <v>ทำให้เครื่องจักรหรือระบบทำงานเองตามเงื่อนไขที่ตั้งไว้</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -11010,10 +11010,10 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>การบริหารกระบวนการผลิต</v>
+        <v>การเขียนโปรแกรมไมโครคอนโทรลเลอร์</v>
       </c>
       <c r="D51" t="str">
-        <v>วางลำดับขั้นตอนการผลิตให้เร็ว ประหยัด และได้คุณภาพ</v>
+        <v>เขียนโปรแกรมสั่งงานบอร์ดควบคุมขนาดเล็ก เช่น Arduino</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -11033,10 +11033,10 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>สถิติเชิงคุณภาพ</v>
+        <v>การบริหารกระบวนการผลิต</v>
       </c>
       <c r="D52" t="str">
-        <v>ใช้สถิติตรวจว่าสินค้าหรือกระบวนการได้มาตรฐานหรือไม่</v>
+        <v>วางลำดับขั้นตอนการผลิตให้เร็ว ประหยัด และได้คุณภาพ</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -11056,10 +11056,10 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>การจัดการโลจิสติกส์</v>
+        <v>สถิติเชิงคุณภาพ</v>
       </c>
       <c r="D53" t="str">
-        <v>วางแผนการขนส่ง การเก็บ และการกระจายสินค้า</v>
+        <v>ใช้สถิติตรวจว่าสินค้าหรือกระบวนการได้มาตรฐานหรือไม่</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -11079,10 +11079,10 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>ชีววิทยาพืช/สัตว์</v>
+        <v>การจัดการโลจิสติกส์</v>
       </c>
       <c r="D54" t="str">
-        <v>เข้าใจโครงสร้าง การเจริญเติบโต และการดำรงชีวิตของพืชและสัตว์</v>
+        <v>วางแผนการขนส่ง การเก็บ และการกระจายสินค้า</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -11102,10 +11102,10 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>การจัดการดินและน้ำ</v>
+        <v>ชีววิทยาพืช/สัตว์</v>
       </c>
       <c r="D55" t="str">
-        <v>ดูแลดินและน้ำให้เหมาะกับการเพาะปลูก</v>
+        <v>เข้าใจโครงสร้าง การเจริญเติบโต และการดำรงชีวิตของพืชและสัตว์</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -11125,10 +11125,10 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>เทคโนโลยีการเกษตรสมัยใหม่</v>
+        <v>การจัดการดินและน้ำ</v>
       </c>
       <c r="D56" t="str">
-        <v>ใช้เครื่องมือ เซนเซอร์ และข้อมูลช่วยทำการเกษตร</v>
+        <v>ดูแลดินและน้ำให้เหมาะกับการเพาะปลูก</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -11148,10 +11148,10 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>กายวิภาคสัตว์</v>
+        <v>เทคโนโลยีการเกษตรสมัยใหม่</v>
       </c>
       <c r="D57" t="str">
-        <v>รู้จักโครงสร้างและอวัยวะในร่างกายของสัตว์</v>
+        <v>ใช้เครื่องมือ เซนเซอร์ และข้อมูลช่วยทำการเกษตร</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -11171,10 +11171,10 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>ชีวเคมี</v>
+        <v>กายวิภาคสัตว์</v>
       </c>
       <c r="D58" t="str">
-        <v>เข้าใจปฏิกิริยาเคมีที่เกิดขึ้นในสิ่งมีชีวิต</v>
+        <v>รู้จักโครงสร้างและอวัยวะในร่างกายของสัตว์</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -11194,10 +11194,10 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>ทักษะการดูแลสัตว์</v>
+        <v>ชีวเคมี</v>
       </c>
       <c r="D59" t="str">
-        <v>จับ เลี้ยง และสังเกตอาการสัตว์อย่างปลอดภัย</v>
+        <v>เข้าใจปฏิกิริยาเคมีที่เกิดขึ้นในสิ่งมีชีวิต</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -11217,10 +11217,10 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>ชีววิทยาทางน้ำ</v>
+        <v>ทักษะการดูแลสัตว์</v>
       </c>
       <c r="D60" t="str">
-        <v>เข้าใจสิ่งมีชีวิตและระบบนิเวศในน้ำ</v>
+        <v>จับ เลี้ยง และสังเกตอาการสัตว์อย่างปลอดภัย</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -11240,10 +11240,10 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>การจัดการคุณภาพน้ำ</v>
+        <v>ชีววิทยาทางน้ำ</v>
       </c>
       <c r="D61" t="str">
-        <v>ตรวจและปรับค่าน้ำให้เหมาะกับสัตว์น้ำหรือการใช้งาน</v>
+        <v>เข้าใจสิ่งมีชีวิตและระบบนิเวศในน้ำ</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -11263,10 +11263,10 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>เทคโนโลยีการเพาะเลี้ยง</v>
+        <v>การจัดการคุณภาพน้ำ</v>
       </c>
       <c r="D62" t="str">
-        <v>ใช้วิธีและอุปกรณ์เลี้ยงสัตว์น้ำให้เติบโตได้ดี</v>
+        <v>ตรวจและปรับค่าน้ำให้เหมาะกับสัตว์น้ำหรือการใช้งาน</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -11286,10 +11286,10 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>นิเวศวิทยาป่าไม้</v>
+        <v>เทคโนโลยีการเพาะเลี้ยง</v>
       </c>
       <c r="D63" t="str">
-        <v>เข้าใจความสัมพันธ์ของพืช สัตว์ และสภาพแวดล้อมในป่า</v>
+        <v>ใช้วิธีและอุปกรณ์เลี้ยงสัตว์น้ำให้เติบโตได้ดี</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -11309,10 +11309,10 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>การสำรวจภาคสนาม</v>
+        <v>นิเวศวิทยาป่าไม้</v>
       </c>
       <c r="D64" t="str">
-        <v>ออกไปเก็บข้อมูลในพื้นที่จริงอย่างเป็นระบบ</v>
+        <v>เข้าใจความสัมพันธ์ของพืช สัตว์ และสภาพแวดล้อมในป่า</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -11332,10 +11332,10 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>GIS เบื้องต้น</v>
+        <v>การสำรวจภาคสนาม</v>
       </c>
       <c r="D65" t="str">
-        <v>ใช้แผนที่และข้อมูลตำแหน่งบนคอมพิวเตอร์วิเคราะห์พื้นที่</v>
+        <v>ออกไปเก็บข้อมูลในพื้นที่จริงอย่างเป็นระบบ</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -11355,10 +11355,10 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>ฟิสิกส์การบิน</v>
+        <v>GIS เบื้องต้น</v>
       </c>
       <c r="D66" t="str">
-        <v>เข้าใจแรงยกและหลักการที่ทำให้อากาศยานบินได้</v>
+        <v>ใช้แผนที่และข้อมูลตำแหน่งบนคอมพิวเตอร์วิเคราะห์พื้นที่</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -11378,10 +11378,10 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>ภาษาอังกฤษเชิงเทคนิค</v>
+        <v>ฟิสิกส์การบิน</v>
       </c>
       <c r="D67" t="str">
-        <v>อ่านคู่มือและใช้ศัพท์เฉพาะทางเป็นภาษาอังกฤษ</v>
+        <v>เข้าใจแรงยกและหลักการที่ทำให้อากาศยานบินได้</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -11401,10 +11401,10 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>การทำงานภายใต้กฎระเบียบเข้มงวด</v>
+        <v>ภาษาอังกฤษเชิงเทคนิค</v>
       </c>
       <c r="D68" t="str">
-        <v>ทำตามขั้นตอนความปลอดภัยอย่างเคร่งครัดทุกครั้ง</v>
+        <v>อ่านคู่มือและใช้ศัพท์เฉพาะทางเป็นภาษาอังกฤษ</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -11424,10 +11424,10 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>สรีรวิทยาการออกกำลังกาย</v>
+        <v>การทำงานภายใต้กฎระเบียบเข้มงวด</v>
       </c>
       <c r="D69" t="str">
-        <v>เข้าใจการทำงานของร่างกายขณะออกกำลังกาย</v>
+        <v>ทำตามขั้นตอนความปลอดภัยอย่างเคร่งครัดทุกครั้ง</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -11447,10 +11447,10 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>โภชนาการนักกีฬา</v>
+        <v>สรีรวิทยาการออกกำลังกาย</v>
       </c>
       <c r="D70" t="str">
-        <v>วางแผนอาหารให้เหมาะกับการฝึกและการแข่งขัน</v>
+        <v>เข้าใจการทำงานของร่างกายขณะออกกำลังกาย</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -11470,10 +11470,10 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>การวิเคราะห์การเคลื่อนไหว</v>
+        <v>โภชนาการนักกีฬา</v>
       </c>
       <c r="D71" t="str">
-        <v>สังเกตและวัดท่าทางเพื่อปรับปรุงการเคลื่อนไหว</v>
+        <v>วางแผนอาหารให้เหมาะกับการฝึกและการแข่งขัน</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -11493,10 +11493,10 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>ชีววิทยา-เคมีขั้นสูง</v>
+        <v>การวิเคราะห์การเคลื่อนไหว</v>
       </c>
       <c r="D72" t="str">
-        <v>ความรู้ชีววิทยาและเคมีในระดับลึกที่ใช้ในวิชาการแพทย์</v>
+        <v>สังเกตและวัดท่าทางเพื่อปรับปรุงการเคลื่อนไหว</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -11516,10 +11516,10 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>การคิดวิเคราะห์เชิงเหตุผล</v>
+        <v>ชีววิทยา-เคมีขั้นสูง</v>
       </c>
       <c r="D73" t="str">
-        <v>ไล่เหตุและผลจากข้อมูลเพื่อหาข้อสรุปที่น่าเชื่อถือ</v>
+        <v>ความรู้ชีววิทยาและเคมีในระดับลึกที่ใช้ในวิชาการแพทย์</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -11539,10 +11539,10 @@
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>ความอดทนต่อความกดดัน</v>
+        <v>การคิดวิเคราะห์เชิงเหตุผล</v>
       </c>
       <c r="D74" t="str">
-        <v>ทำงานได้ดีแม้มีเวลาจำกัดหรือมีความรับผิดชอบสูง</v>
+        <v>ไล่เหตุและผลจากข้อมูลเพื่อหาข้อสรุปที่น่าเชื่อถือ</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -11562,10 +11562,10 @@
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>ความละเอียดในการใช้มือ (fine motor skills)</v>
+        <v>ความอดทนต่อความกดดัน</v>
       </c>
       <c r="D75" t="str">
-        <v>ใช้มือทำงานชิ้นเล็กอย่างแม่นยำ</v>
+        <v>ทำงานได้ดีแม้มีเวลาจำกัดหรือมีความรับผิดชอบสูง</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -11585,10 +11585,10 @@
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>ชีววิทยา-เคมี</v>
+        <v>ความละเอียดในการใช้มือ (fine motor skills)</v>
       </c>
       <c r="D76" t="str">
-        <v>ความรู้พื้นฐานเรื่องสิ่งมีชีวิตและสารเคมี</v>
+        <v>ใช้มือทำงานชิ้นเล็กอย่างแม่นยำ</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -11608,10 +11608,10 @@
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>ทักษะการสื่อสารกับผู้ป่วย</v>
+        <v>ชีววิทยา-เคมี</v>
       </c>
       <c r="D77" t="str">
-        <v>อธิบายและรับฟังผู้ป่วยด้วยภาษาที่เข้าใจง่าย</v>
+        <v>ความรู้พื้นฐานเรื่องสิ่งมีชีวิตและสารเคมี</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -11631,10 +11631,10 @@
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>เคมีขั้นสูง</v>
+        <v>ทักษะการสื่อสารกับผู้ป่วย</v>
       </c>
       <c r="D78" t="str">
-        <v>ความรู้เรื่องสารและปฏิกิริยาเคมีในระดับลึก</v>
+        <v>อธิบายและรับฟังผู้ป่วยด้วยภาษาที่เข้าใจง่าย</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -11654,10 +11654,10 @@
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>ความละเอียดรอบคอบ</v>
+        <v>เคมีขั้นสูง</v>
       </c>
       <c r="D79" t="str">
-        <v>ตรวจงานทีละขั้นเพื่อไม่ให้ผิดพลาด</v>
+        <v>ความรู้เรื่องสารและปฏิกิริยาเคมีในระดับลึก</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -11677,10 +11677,10 @@
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>ความรู้ด้านกฎหมายยา</v>
+        <v>ความละเอียดรอบคอบ</v>
       </c>
       <c r="D80" t="str">
-        <v>รู้กฎหมายเกี่ยวกับการผลิต การจ่าย และการขายยา</v>
+        <v>ตรวจงานทีละขั้นเพื่อไม่ให้ผิดพลาด</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -11700,10 +11700,10 @@
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>การทดลองในห้องปฏิบัติการ</v>
+        <v>ความรู้ด้านกฎหมายยา</v>
       </c>
       <c r="D81" t="str">
-        <v>ทำการทดลองตามขั้นตอนและบันทึกผลอย่างถูกต้อง</v>
+        <v>รู้กฎหมายเกี่ยวกับการผลิต การจ่าย และการขายยา</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -11723,10 +11723,10 @@
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>การวิเคราะห์ข้อมูลเชิงปริมาณ</v>
+        <v>การทดลองในห้องปฏิบัติการ</v>
       </c>
       <c r="D82" t="str">
-        <v>ใช้ตัวเลขและสถิติหาข้อสรุปจากข้อมูล</v>
+        <v>ทำการทดลองตามขั้นตอนและบันทึกผลอย่างถูกต้อง</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -11746,10 +11746,10 @@
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>ชีววิทยาระดับเซลล์/โมเลกุล</v>
+        <v>การวิเคราะห์ข้อมูลเชิงปริมาณ</v>
       </c>
       <c r="D83" t="str">
-        <v>เข้าใจการทำงานของเซลล์ ยีน และ DNA</v>
+        <v>ใช้ตัวเลขและสถิติหาข้อสรุปจากข้อมูล</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -11769,10 +11769,10 @@
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>การใช้กล้องจุลทรรศน์และเครื่องมือแล็บ</v>
+        <v>ชีววิทยาระดับเซลล์/โมเลกุล</v>
       </c>
       <c r="D84" t="str">
-        <v>ใช้อุปกรณ์ในห้องปฏิบัติการได้ถูกวิธีและปลอดภัย</v>
+        <v>เข้าใจการทำงานของเซลล์ ยีน และ DNA</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -11792,10 +11792,10 @@
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>การเขียนโปรแกรม</v>
+        <v>การใช้กล้องจุลทรรศน์และเครื่องมือแล็บ</v>
       </c>
       <c r="D85" t="str">
-        <v>เขียนคำสั่งให้คอมพิวเตอร์ทำงานตามที่ต้องการ</v>
+        <v>ใช้อุปกรณ์ในห้องปฏิบัติการได้ถูกวิธีและปลอดภัย</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -11815,10 +11815,10 @@
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>ตรรกะและคณิตศาสตร์ไม่ต่อเนื่อง</v>
+        <v>การเขียนโปรแกรม</v>
       </c>
       <c r="D86" t="str">
-        <v>คณิตศาสตร์ที่ใช้คิดเชิงตรรกะและออกแบบโปรแกรม</v>
+        <v>เขียนคำสั่งให้คอมพิวเตอร์ทำงานตามที่ต้องการ</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -11838,10 +11838,10 @@
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>การวิเคราะห์ข้อมูล</v>
+        <v>ตรรกะและคณิตศาสตร์ไม่ต่อเนื่อง</v>
       </c>
       <c r="D87" t="str">
-        <v>จัดระเบียบและตีความข้อมูลเพื่อตอบคำถาม</v>
+        <v>คณิตศาสตร์ที่ใช้คิดเชิงตรรกะและออกแบบโปรแกรม</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -11861,10 +11861,10 @@
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>การตรวจวิเคราะห์ทางห้องปฏิบัติการ</v>
+        <v>การวิเคราะห์ข้อมูล</v>
       </c>
       <c r="D88" t="str">
-        <v>ตรวจตัวอย่าง เช่น เลือดหรือปัสสาวะ ด้วยเครื่องมือแล็บ</v>
+        <v>จัดระเบียบและตีความข้อมูลเพื่อตอบคำถาม</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -11884,10 +11884,10 @@
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>สถิติพื้นฐาน</v>
+        <v>การตรวจวิเคราะห์ทางห้องปฏิบัติการ</v>
       </c>
       <c r="D89" t="str">
-        <v>ค่าเฉลี่ย ร้อยละ และการอ่านกราฟเบื้องต้น</v>
+        <v>ตรวจตัวอย่าง เช่น เลือดหรือปัสสาวะ ด้วยเครื่องมือแล็บ</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -11907,10 +11907,10 @@
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>การวิเคราะห์ข้อมูลสุขภาพประชากร</v>
+        <v>สถิติพื้นฐาน</v>
       </c>
       <c r="D90" t="str">
-        <v>ดูแนวโน้มโรคและสุขภาพของคนจำนวนมากจากข้อมูล</v>
+        <v>ค่าเฉลี่ย ร้อยละ และการอ่านกราฟเบื้องต้น</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -11930,10 +11930,10 @@
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>คณิตศาสตร์ขั้นสูง</v>
+        <v>การวิเคราะห์ข้อมูลสุขภาพประชากร</v>
       </c>
       <c r="D91" t="str">
-        <v>แคลคูลัส พีชคณิต และการแก้โจทย์ที่ซับซ้อน</v>
+        <v>ดูแนวโน้มโรคและสุขภาพของคนจำนวนมากจากข้อมูล</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -11953,10 +11953,10 @@
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>การเขียนโปรแกรมเพื่อการวิเคราะห์ข้อมูล</v>
+        <v>คณิตศาสตร์ขั้นสูง</v>
       </c>
       <c r="D92" t="str">
-        <v>ใช้โปรแกรมจัดการและคำนวณข้อมูลจำนวนมาก</v>
+        <v>แคลคูลัส พีชคณิต และการแก้โจทย์ที่ซับซ้อน</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -11976,10 +11976,10 @@
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>เทคนิคการวาด/ระบายสี</v>
+        <v>การเขียนโปรแกรมเพื่อการวิเคราะห์ข้อมูล</v>
       </c>
       <c r="D93" t="str">
-        <v>ใช้เส้น แสงเงา และสีถ่ายทอดภาพ</v>
+        <v>ใช้โปรแกรมจัดการและคำนวณข้อมูลจำนวนมาก</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -11999,10 +11999,10 @@
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>การสร้างสรรค์แนวคิด (concept art)</v>
+        <v>เทคนิคการวาด/ระบายสี</v>
       </c>
       <c r="D94" t="str">
-        <v>ร่างภาพไอเดียตัวละคร ฉาก หรือผลงานก่อนลงมือจริง</v>
+        <v>ใช้เส้น แสงเงา และสีถ่ายทอดภาพ</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -12022,10 +12022,10 @@
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>การออกแบบเชิงพื้นที่</v>
+        <v>การสร้างสรรค์แนวคิด (concept art)</v>
       </c>
       <c r="D95" t="str">
-        <v>จัดวางพื้นที่ให้ใช้งานได้ดีและสวยงาม</v>
+        <v>ร่างภาพไอเดียตัวละคร ฉาก หรือผลงานก่อนลงมือจริง</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -12045,10 +12045,10 @@
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>โปรแกรมออกแบบ 3 มิติ</v>
+        <v>การออกแบบเชิงพื้นที่</v>
       </c>
       <c r="D96" t="str">
-        <v>สร้างแบบจำลองสามมิติด้วยคอมพิวเตอร์</v>
+        <v>จัดวางพื้นที่ให้ใช้งานได้ดีและสวยงาม</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -12068,10 +12068,10 @@
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>คณิตศาสตร์เชิงเรขาคณิต</v>
+        <v>โปรแกรมออกแบบ 3 มิติ</v>
       </c>
       <c r="D97" t="str">
-        <v>คำนวณรูปทรง มุม และระยะ</v>
+        <v>สร้างแบบจำลองสามมิติด้วยคอมพิวเตอร์</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -12091,10 +12091,10 @@
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>ความคิดสร้างสรรค์เชิงพื้นที่</v>
+        <v>คณิตศาสตร์เชิงเรขาคณิต</v>
       </c>
       <c r="D98" t="str">
-        <v>นึกภาพพื้นที่และรูปทรงสามมิติในหัวได้</v>
+        <v>คำนวณรูปทรง มุม และระยะ</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -12114,10 +12114,10 @@
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>การเลือกใช้วัสดุและสี</v>
+        <v>ความคิดสร้างสรรค์เชิงพื้นที่</v>
       </c>
       <c r="D99" t="str">
-        <v>เลือกวัสดุและสีให้เหมาะกับการใช้งานและบรรยากาศ</v>
+        <v>นึกภาพพื้นที่และรูปทรงสามมิติในหัวได้</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -12137,10 +12137,10 @@
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>การเล่าเรื่อง (storytelling)</v>
+        <v>การเลือกใช้วัสดุและสี</v>
       </c>
       <c r="D100" t="str">
-        <v>เรียงเรื่องราวให้น่าติดตามและเข้าใจง่าย</v>
+        <v>เลือกวัสดุและสีให้เหมาะกับการใช้งานและบรรยากาศ</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -12160,10 +12160,10 @@
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>การถ่ายภาพ/วิดีโอเบื้องต้น</v>
+        <v>การเล่าเรื่อง (storytelling)</v>
       </c>
       <c r="D101" t="str">
-        <v>จัดมุมกล้อง แสง และองค์ประกอบภาพ</v>
+        <v>เรียงเรื่องราวให้น่าติดตามและเข้าใจง่าย</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -12183,10 +12183,10 @@
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>ทักษะเครื่องดนตรี/การขับร้อง</v>
+        <v>การถ่ายภาพ/วิดีโอเบื้องต้น</v>
       </c>
       <c r="D102" t="str">
-        <v>เล่นดนตรีหรือร้องเพลงได้อย่างมีคุณภาพ</v>
+        <v>จัดมุมกล้อง แสง และองค์ประกอบภาพ</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -12206,10 +12206,10 @@
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>ทฤษฎีดนตรี</v>
+        <v>ทักษะเครื่องดนตรี/การขับร้อง</v>
       </c>
       <c r="D103" t="str">
-        <v>เข้าใจโน้ต จังหวะ และการประสานเสียง</v>
+        <v>เล่นดนตรีหรือร้องเพลงได้อย่างมีคุณภาพ</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -12229,10 +12229,10 @@
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>การออกแบบลวดลาย</v>
+        <v>ทฤษฎีดนตรี</v>
       </c>
       <c r="D104" t="str">
-        <v>สร้างลายสำหรับผ้า สินค้า หรือของตกแต่ง</v>
+        <v>เข้าใจโน้ต จังหวะ และการประสานเสียง</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -12252,10 +12252,10 @@
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>การตัดเย็บเบื้องต้น</v>
+        <v>การออกแบบลวดลาย</v>
       </c>
       <c r="D105" t="str">
-        <v>วัดตัว ตัดผ้า และเย็บชิ้นงานพื้นฐาน</v>
+        <v>สร้างลายสำหรับผ้า สินค้า หรือของตกแต่ง</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -12275,10 +12275,10 @@
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>แนวโน้มแฟชั่น</v>
+        <v>การตัดเย็บเบื้องต้น</v>
       </c>
       <c r="D106" t="str">
-        <v>ติดตามสไตล์และกระแสการแต่งกาย</v>
+        <v>วัดตัว ตัดผ้า และเย็บชิ้นงานพื้นฐาน</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -12298,10 +12298,10 @@
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>การร่างแบบ</v>
+        <v>แนวโน้มแฟชั่น</v>
       </c>
       <c r="D107" t="str">
-        <v>สเก็ตช์ไอเดียออกมาเป็นภาพอย่างรวดเร็ว</v>
+        <v>ติดตามสไตล์และกระแสการแต่งกาย</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -12321,10 +12321,10 @@
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>การใช้โปรแกรมออกแบบ 3 มิติ</v>
+        <v>การร่างแบบ</v>
       </c>
       <c r="D108" t="str">
-        <v>สร้างแบบจำลองสามมิติด้วยคอมพิวเตอร์</v>
+        <v>สเก็ตช์ไอเดียออกมาเป็นภาพอย่างรวดเร็ว</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -12344,10 +12344,10 @@
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>ความเข้าใจวัสดุ</v>
+        <v>การใช้โปรแกรมออกแบบ 3 มิติ</v>
       </c>
       <c r="D109" t="str">
-        <v>รู้คุณสมบัติของวัสดุแต่ละชนิดและเลือกใช้ให้เหมาะ</v>
+        <v>สร้างแบบจำลองสามมิติด้วยคอมพิวเตอร์</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -12367,10 +12367,10 @@
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>การเขียนเชิงสร้างสรรค์</v>
+        <v>ความเข้าใจวัสดุ</v>
       </c>
       <c r="D110" t="str">
-        <v>เขียนเรื่อง บทกวี หรือบทความให้มีชีวิตชีวา</v>
+        <v>รู้คุณสมบัติของวัสดุแต่ละชนิดและเลือกใช้ให้เหมาะ</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -12390,10 +12390,10 @@
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>ทักษะภาษาไทย/ภาษาต่างประเทศ</v>
+        <v>การเขียนเชิงสร้างสรรค์</v>
       </c>
       <c r="D111" t="str">
-        <v>อ่าน เขียน และสื่อสารได้ถูกต้องและสละสลวย</v>
+        <v>เขียนเรื่อง บทกวี หรือบทความให้มีชีวิตชีวา</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -12413,10 +12413,10 @@
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>การตัดต่อวิดีโอ</v>
+        <v>ทักษะภาษาไทย/ภาษาต่างประเทศ</v>
       </c>
       <c r="D112" t="str">
-        <v>เรียงภาพและเสียงให้เป็นเรื่องราวที่ลื่นไหล</v>
+        <v>อ่าน เขียน และสื่อสารได้ถูกต้องและสละสลวย</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -12436,10 +12436,10 @@
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>การเล่าเรื่องด้วยภาพ</v>
+        <v>การตัดต่อวิดีโอ</v>
       </c>
       <c r="D113" t="str">
-        <v>ใช้ภาพหรือฉากสื่อความหมายแทนคำพูด</v>
+        <v>เรียงภาพและเสียงให้เป็นเรื่องราวที่ลื่นไหล</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -12459,10 +12459,10 @@
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>ซอฟต์แวร์ตัดต่อ/แอนิเมชัน</v>
+        <v>การเล่าเรื่องด้วยภาพ</v>
       </c>
       <c r="D114" t="str">
-        <v>ใช้โปรแกรมตัดต่อวิดีโอหรือทำภาพเคลื่อนไหว</v>
+        <v>ใช้ภาพหรือฉากสื่อความหมายแทนคำพูด</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -12482,10 +12482,10 @@
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>การสื่อสารกับเด็ก/เยาวชน</v>
+        <v>ซอฟต์แวร์ตัดต่อ/แอนิเมชัน</v>
       </c>
       <c r="D115" t="str">
-        <v>พูดและอธิบายให้เด็กเข้าใจและไว้ใจ</v>
+        <v>ใช้โปรแกรมตัดต่อวิดีโอหรือทำภาพเคลื่อนไหว</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -12505,10 +12505,10 @@
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>การจัดการชั้นเรียน</v>
+        <v>การสื่อสารกับเด็ก/เยาวชน</v>
       </c>
       <c r="D116" t="str">
-        <v>ดูแลผู้เรียนทั้งห้องให้เรียนได้อย่างราบรื่น</v>
+        <v>พูดและอธิบายให้เด็กเข้าใจและไว้ใจ</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -12528,10 +12528,10 @@
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>ความรู้ทางการพยาบาล</v>
+        <v>การจัดการชั้นเรียน</v>
       </c>
       <c r="D117" t="str">
-        <v>การดูแลผู้ป่วยและหลักการรักษาพยาบาลเบื้องต้น</v>
+        <v>ดูแลผู้เรียนทั้งห้องให้เรียนได้อย่างราบรื่น</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -12551,10 +12551,10 @@
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>ความเห็นอกเห็นใจ</v>
+        <v>ความรู้ทางการพยาบาล</v>
       </c>
       <c r="D118" t="str">
-        <v>เข้าใจความรู้สึกของผู้อื่นและตอบสนองอย่างเหมาะสม</v>
+        <v>การดูแลผู้ป่วยและหลักการรักษาพยาบาลเบื้องต้น</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -12574,10 +12574,10 @@
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>การรับฟังอย่างเข้าใจ</v>
+        <v>ความเห็นอกเห็นใจ</v>
       </c>
       <c r="D119" t="str">
-        <v>ฟังโดยไม่ตัดสินและจับใจความสิ่งที่อีกฝ่ายต้องการสื่อ</v>
+        <v>เข้าใจความรู้สึกของผู้อื่นและตอบสนองอย่างเหมาะสม</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -12597,10 +12597,10 @@
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>ความรู้พื้นฐานพฤติกรรมมนุษย์</v>
+        <v>การรับฟังอย่างเข้าใจ</v>
       </c>
       <c r="D120" t="str">
-        <v>เข้าใจเหตุผลที่คนคิด รู้สึก และกระทำแบบต่าง ๆ</v>
+        <v>ฟังโดยไม่ตัดสินและจับใจความสิ่งที่อีกฝ่ายต้องการสื่อ</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -12620,10 +12620,10 @@
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>การทำงานร่วมกับชุมชน</v>
+        <v>ความรู้พื้นฐานพฤติกรรมมนุษย์</v>
       </c>
       <c r="D121" t="str">
-        <v>ลงพื้นที่ รับฟัง และทำงานร่วมกับคนในชุมชน</v>
+        <v>เข้าใจเหตุผลที่คนคิด รู้สึก และกระทำแบบต่าง ๆ</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -12643,10 +12643,10 @@
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>ความเข้าใจปัญหาสังคม</v>
+        <v>การทำงานร่วมกับชุมชน</v>
       </c>
       <c r="D122" t="str">
-        <v>มองเห็นสาเหตุและผลกระทบของปัญหาในสังคม</v>
+        <v>ลงพื้นที่ รับฟัง และทำงานร่วมกับคนในชุมชน</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -12666,10 +12666,10 @@
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>กายวิภาคศาสตร์</v>
+        <v>ความเข้าใจปัญหาสังคม</v>
       </c>
       <c r="D123" t="str">
-        <v>รู้จักโครงสร้างกระดูก กล้ามเนื้อ และอวัยวะของร่างกายคน</v>
+        <v>มองเห็นสาเหตุและผลกระทบของปัญหาในสังคม</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -12689,10 +12689,10 @@
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>เทคนิคการฟื้นฟูร่างกาย</v>
+        <v>กายวิภาคศาสตร์</v>
       </c>
       <c r="D124" t="str">
-        <v>วิธีช่วยให้ร่างกายกลับมาเคลื่อนไหวได้ดีขึ้น</v>
+        <v>รู้จักโครงสร้างกระดูก กล้ามเนื้อ และอวัยวะของร่างกายคน</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -12712,10 +12712,10 @@
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>การให้ความรู้ด้านสุขภาพ</v>
+        <v>เทคนิคการฟื้นฟูร่างกาย</v>
       </c>
       <c r="D125" t="str">
-        <v>อธิบายเรื่องสุขภาพให้คนทั่วไปเข้าใจและนำไปใช้ได้</v>
+        <v>วิธีช่วยให้ร่างกายกลับมาเคลื่อนไหวได้ดีขึ้น</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -12735,10 +12735,10 @@
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>ความเข้าใจพัฒนาการเด็ก</v>
+        <v>การให้ความรู้ด้านสุขภาพ</v>
       </c>
       <c r="D126" t="str">
-        <v>รู้ว่าเด็กแต่ละวัยเติบโตและเรียนรู้อย่างไร</v>
+        <v>อธิบายเรื่องสุขภาพให้คนทั่วไปเข้าใจและนำไปใช้ได้</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -12758,10 +12758,10 @@
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>ความอดทนและความอ่อนโยน</v>
+        <v>ความเข้าใจพัฒนาการเด็ก</v>
       </c>
       <c r="D127" t="str">
-        <v>ใจเย็นและดูแลผู้อื่นอย่างนุ่มนวล</v>
+        <v>รู้ว่าเด็กแต่ละวัยเติบโตและเรียนรู้อย่างไร</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -12781,10 +12781,10 @@
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>ความเข้าใจพัฒนาการและความบกพร่องทางร่างกาย/จิตใจ</v>
+        <v>ความอดทนและความอ่อนโยน</v>
       </c>
       <c r="D128" t="str">
-        <v>เข้าใจข้อจำกัดของแต่ละคนเพื่อช่วยได้ตรงจุด</v>
+        <v>ใจเย็นและดูแลผู้อื่นอย่างนุ่มนวล</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -12804,10 +12804,10 @@
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>การวิเคราะห์พฤติกรรมผู้บริโภค</v>
+        <v>ความเข้าใจพัฒนาการและความบกพร่องทางร่างกาย/จิตใจ</v>
       </c>
       <c r="D129" t="str">
-        <v>ศึกษาว่าลูกค้าตัดสินใจซื้ออย่างไรและเพราะอะไร</v>
+        <v>เข้าใจข้อจำกัดของแต่ละคนเพื่อช่วยได้ตรงจุด</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -12827,10 +12827,10 @@
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>การนำเสนอ</v>
+        <v>การวิเคราะห์พฤติกรรมผู้บริโภค</v>
       </c>
       <c r="D130" t="str">
-        <v>เล่าข้อมูลหรือไอเดียให้ผู้ฟังเข้าใจและสนใจ</v>
+        <v>ศึกษาว่าลูกค้าตัดสินใจซื้ออย่างไรและเพราะอะไร</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -12850,10 +12850,10 @@
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>ความคิดสร้างสรรค์เชิงธุรกิจ</v>
+        <v>การนำเสนอ</v>
       </c>
       <c r="D131" t="str">
-        <v>คิดสินค้า บริการ หรือวิธีขายแบบใหม่</v>
+        <v>เล่าข้อมูลหรือไอเดียให้ผู้ฟังเข้าใจและสนใจ</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -12873,10 +12873,10 @@
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>การวางแผนกลยุทธ์</v>
+        <v>ความคิดสร้างสรรค์เชิงธุรกิจ</v>
       </c>
       <c r="D132" t="str">
-        <v>กำหนดเป้าหมายและวิธีไปให้ถึงในระยะยาว</v>
+        <v>คิดสินค้า บริการ หรือวิธีขายแบบใหม่</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -12896,10 +12896,10 @@
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>ภาวะผู้นำ</v>
+        <v>การวางแผนกลยุทธ์</v>
       </c>
       <c r="D133" t="str">
-        <v>ชวนคนอื่นทำงานไปในทิศทางเดียวกันและตัดสินใจเมื่อจำเป็น</v>
+        <v>กำหนดเป้าหมายและวิธีไปให้ถึงในระยะยาว</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -12919,10 +12919,10 @@
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>การบริหารทีม</v>
+        <v>ภาวะผู้นำ</v>
       </c>
       <c r="D134" t="str">
-        <v>แบ่งงาน ติดตามงาน และดูแลสมาชิกในทีม</v>
+        <v>ชวนคนอื่นทำงานไปในทิศทางเดียวกันและตัดสินใจเมื่อจำเป็น</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -12942,10 +12942,10 @@
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>การอ่านและตีความกฎหมาย</v>
+        <v>การบริหารทีม</v>
       </c>
       <c r="D135" t="str">
-        <v>อ่านตัวบทกฎหมายแล้วเข้าใจว่าใช้กับเรื่องใดอย่างไร</v>
+        <v>แบ่งงาน ติดตามงาน และดูแลสมาชิกในทีม</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -12965,10 +12965,10 @@
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>การโต้แย้งเชิงเหตุผล</v>
+        <v>การอ่านและตีความกฎหมาย</v>
       </c>
       <c r="D136" t="str">
-        <v>เสนอความเห็นพร้อมหลักฐานและเหตุผลที่หนักแน่น</v>
+        <v>อ่านตัวบทกฎหมายแล้วเข้าใจว่าใช้กับเรื่องใดอย่างไร</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -12988,10 +12988,10 @@
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>ความเข้าใจการเมืองการปกครอง</v>
+        <v>การโต้แย้งเชิงเหตุผล</v>
       </c>
       <c r="D137" t="str">
-        <v>เข้าใจโครงสร้างอำนาจรัฐและการบริหารประเทศ</v>
+        <v>เสนอความเห็นพร้อมหลักฐานและเหตุผลที่หนักแน่น</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -13011,10 +13011,10 @@
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>ทักษะการเจรจา</v>
+        <v>ความเข้าใจการเมืองการปกครอง</v>
       </c>
       <c r="D138" t="str">
-        <v>พูดคุยหาข้อตกลงที่ทุกฝ่ายยอมรับได้</v>
+        <v>เข้าใจโครงสร้างอำนาจรัฐและการบริหารประเทศ</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -13034,10 +13034,10 @@
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>การวิเคราะห์ข้อมูลเศรษฐกิจ</v>
+        <v>ทักษะการเจรจา</v>
       </c>
       <c r="D139" t="str">
-        <v>อ่านตัวเลขเศรษฐกิจและอธิบายแนวโน้ม</v>
+        <v>พูดคุยหาข้อตกลงที่ทุกฝ่ายยอมรับได้</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -13057,10 +13057,10 @@
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>คณิตศาสตร์พื้นฐาน</v>
+        <v>การวิเคราะห์ข้อมูลเศรษฐกิจ</v>
       </c>
       <c r="D140" t="str">
-        <v>การคำนวณ ร้อยละ และโจทย์ปัญหาทั่วไป</v>
+        <v>อ่านตัวเลขเศรษฐกิจและอธิบายแนวโน้ม</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -13080,10 +13080,10 @@
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>การบริการลูกค้า</v>
+        <v>คณิตศาสตร์พื้นฐาน</v>
       </c>
       <c r="D141" t="str">
-        <v>ดูแลและแก้ปัญหาให้ลูกค้าอย่างสุภาพและรวดเร็ว</v>
+        <v>การคำนวณ ร้อยละ และโจทย์ปัญหาทั่วไป</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -13103,10 +13103,10 @@
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>ภาษาต่างประเทศ</v>
+        <v>การบริการลูกค้า</v>
       </c>
       <c r="D142" t="str">
-        <v>สื่อสารด้วยภาษาอื่นนอกจากภาษาไทย</v>
+        <v>ดูแลและแก้ปัญหาให้ลูกค้าอย่างสุภาพและรวดเร็ว</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -13126,10 +13126,10 @@
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>การบริหารงานบริการ</v>
+        <v>ภาษาต่างประเทศ</v>
       </c>
       <c r="D143" t="str">
-        <v>วางระบบงานบริการให้ลูกค้าได้รับประสบการณ์ที่ดี</v>
+        <v>สื่อสารด้วยภาษาอื่นนอกจากภาษาไทย</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -13149,10 +13149,10 @@
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>การสื่อสารเชิงกลยุทธ์</v>
+        <v>การบริหารงานบริการ</v>
       </c>
       <c r="D144" t="str">
-        <v>วางแผนว่าจะสื่อสารอะไร กับใคร ผ่านช่องทางไหน</v>
+        <v>วางระบบงานบริการให้ลูกค้าได้รับประสบการณ์ที่ดี</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -13172,10 +13172,10 @@
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>การเจรจาต่อรอง</v>
+        <v>การสื่อสารเชิงกลยุทธ์</v>
       </c>
       <c r="D145" t="str">
-        <v>ต่อรองราคาหรือเงื่อนไขให้ได้ผลที่ดีกับทุกฝ่าย</v>
+        <v>วางแผนว่าจะสื่อสารอะไร กับใคร ผ่านช่องทางไหน</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -13195,10 +13195,10 @@
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>ภาษาอังกฤษเชิงธุรกิจ</v>
+        <v>การเจรจาต่อรอง</v>
       </c>
       <c r="D146" t="str">
-        <v>ใช้ภาษาอังกฤษในการประชุม อีเมล และการค้า</v>
+        <v>ต่อรองราคาหรือเงื่อนไขให้ได้ผลที่ดีกับทุกฝ่าย</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -13218,10 +13218,10 @@
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>ความเข้าใจตลาดต่างประเทศ</v>
+        <v>ภาษาอังกฤษเชิงธุรกิจ</v>
       </c>
       <c r="D147" t="str">
-        <v>รู้ความต้องการ กฎระเบียบ และวัฒนธรรมของตลาดต่างชาติ</v>
+        <v>ใช้ภาษาอังกฤษในการประชุม อีเมล และการค้า</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -13241,10 +13241,10 @@
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>หลักการบัญชี</v>
+        <v>ความเข้าใจตลาดต่างประเทศ</v>
       </c>
       <c r="D148" t="str">
-        <v>บันทึกรายรับรายจ่ายและจัดทำงบตามมาตรฐาน</v>
+        <v>รู้ความต้องการ กฎระเบียบ และวัฒนธรรมของตลาดต่างชาติ</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -13264,10 +13264,10 @@
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>การใช้โปรแกรมบัญชี</v>
+        <v>หลักการบัญชี</v>
       </c>
       <c r="D149" t="str">
-        <v>บันทึกและสรุปข้อมูลบัญชีด้วยคอมพิวเตอร์</v>
+        <v>บันทึกรายรับรายจ่ายและจัดทำงบตามมาตรฐาน</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -13287,10 +13287,10 @@
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>การวิเคราะห์งบการเงิน</v>
+        <v>การใช้โปรแกรมบัญชี</v>
       </c>
       <c r="D150" t="str">
-        <v>อ่านงบการเงินเพื่อดูสุขภาพทางการเงินของกิจการ</v>
+        <v>บันทึกและสรุปข้อมูลบัญชีด้วยคอมพิวเตอร์</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -13310,10 +13310,10 @@
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>คณิตศาสตร์การเงิน</v>
+        <v>การวิเคราะห์งบการเงิน</v>
       </c>
       <c r="D151" t="str">
-        <v>คำนวณดอกเบี้ย ผลตอบแทน และมูลค่าของเงินตามเวลา</v>
+        <v>อ่านงบการเงินเพื่อดูสุขภาพทางการเงินของกิจการ</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -13333,10 +13333,10 @@
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>สถิติ</v>
+        <v>คณิตศาสตร์การเงิน</v>
       </c>
       <c r="D152" t="str">
-        <v>เก็บ สรุป และตีความข้อมูลตัวเลข</v>
+        <v>คำนวณดอกเบี้ย ผลตอบแทน และมูลค่าของเงินตามเวลา</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -13356,10 +13356,10 @@
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>การวิเคราะห์ข้อมูลเชิงตัวเลข</v>
+        <v>สถิติ</v>
       </c>
       <c r="D153" t="str">
-        <v>หาความหมายและแนวโน้มจากตัวเลข</v>
+        <v>เก็บ สรุป และตีความข้อมูลตัวเลข</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -13379,10 +13379,10 @@
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>สถิติขั้นสูง</v>
+        <v>การวิเคราะห์ข้อมูลเชิงตัวเลข</v>
       </c>
       <c r="D154" t="str">
-        <v>สร้างแบบจำลองและทดสอบสมมติฐานจากข้อมูล</v>
+        <v>หาความหมายและแนวโน้มจากตัวเลข</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -13402,10 +13402,10 @@
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>การเขียนโปรแกรมวิเคราะห์ข้อมูล</v>
+        <v>สถิติขั้นสูง</v>
       </c>
       <c r="D155" t="str">
-        <v>ใช้โปรแกรมจัดการและคำนวณข้อมูลจำนวนมาก</v>
+        <v>สร้างแบบจำลองและทดสอบสมมติฐานจากข้อมูล</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -13425,10 +13425,10 @@
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>ความเข้าใจระบบราชการ</v>
+        <v>การเขียนโปรแกรมวิเคราะห์ข้อมูล</v>
       </c>
       <c r="D156" t="str">
-        <v>รู้ขั้นตอน ระเบียบ และโครงสร้างของหน่วยงานรัฐ</v>
+        <v>ใช้โปรแกรมจัดการและคำนวณข้อมูลจำนวนมาก</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -13448,10 +13448,10 @@
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>การจัดการเอกสาร/ข้อมูล</v>
+        <v>ความเข้าใจระบบราชการ</v>
       </c>
       <c r="D157" t="str">
-        <v>จัดเก็บเอกสารและข้อมูลให้ค้นหาได้ง่ายและถูกต้อง</v>
+        <v>รู้ขั้นตอน ระเบียบ และโครงสร้างของหน่วยงานรัฐ</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -13471,10 +13471,10 @@
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>การจัดการฐานข้อมูล</v>
+        <v>การจัดการเอกสาร/ข้อมูล</v>
       </c>
       <c r="D158" t="str">
-        <v>ออกแบบและดูแลระบบเก็บข้อมูลขององค์กร</v>
+        <v>จัดเก็บเอกสารและข้อมูลให้ค้นหาได้ง่ายและถูกต้อง</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -13494,10 +13494,10 @@
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>ความเข้าใจกระบวนการธุรกิจ</v>
+        <v>การจัดการฐานข้อมูล</v>
       </c>
       <c r="D159" t="str">
-        <v>รู้ว่างานแต่ละฝ่ายในองค์กรเชื่อมโยงกันอย่างไร</v>
+        <v>ออกแบบและดูแลระบบเก็บข้อมูลขององค์กร</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -13517,10 +13517,10 @@
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>การวางแผนและจัดการกระบวนการ</v>
+        <v>ความเข้าใจกระบวนการธุรกิจ</v>
       </c>
       <c r="D160" t="str">
-        <v>จัดลำดับงานให้คนและทรัพยากรทำงานได้คุ้มค่า</v>
+        <v>รู้ว่างานแต่ละฝ่ายในองค์กรเชื่อมโยงกันอย่างไร</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -13540,10 +13540,10 @@
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>โปรแกรมออกแบบ 3 มิติ (CAD)</v>
+        <v>การวางแผนและจัดการกระบวนการ</v>
       </c>
       <c r="D161" t="str">
-        <v>สร้างแบบชิ้นงานสามมิติด้วยคอมพิวเตอร์</v>
+        <v>จัดลำดับงานให้คนและทรัพยากรทำงานได้คุ้มค่า</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -13563,10 +13563,10 @@
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>ความเข้าใจวัสดุและกระบวนการผลิต</v>
+        <v>โปรแกรมออกแบบ 3 มิติ (CAD)</v>
       </c>
       <c r="D162" t="str">
-        <v>รู้ว่าวัสดุแต่ละชนิดผลิตเป็นสินค้าได้อย่างไร</v>
+        <v>สร้างแบบชิ้นงานสามมิติด้วยคอมพิวเตอร์</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -13586,10 +13586,10 @@
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>ฟิสิกส์รังสี</v>
+        <v>ความเข้าใจวัสดุและกระบวนการผลิต</v>
       </c>
       <c r="D163" t="str">
-        <v>เข้าใจรังสีชนิดต่าง ๆ และการป้องกันอันตราย</v>
+        <v>รู้ว่าวัสดุแต่ละชนิดผลิตเป็นสินค้าได้อย่างไร</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -13609,10 +13609,10 @@
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>การใช้เครื่องมือถ่ายภาพทางการแพทย์</v>
+        <v>ฟิสิกส์รังสี</v>
       </c>
       <c r="D164" t="str">
-        <v>ใช้เครื่องเอกซเรย์และเครื่องสร้างภาพอวัยวะ</v>
+        <v>เข้าใจรังสีชนิดต่าง ๆ และการป้องกันอันตราย</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -13632,10 +13632,10 @@
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>ความเข้าใจเทคโนโลยี</v>
+        <v>การใช้เครื่องมือถ่ายภาพทางการแพทย์</v>
       </c>
       <c r="D165" t="str">
-        <v>รู้ว่าเทคโนโลยีแต่ละแบบทำอะไรได้และเหมาะกับงานใด</v>
+        <v>ใช้เครื่องเอกซเรย์และเครื่องสร้างภาพอวัยวะ</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -13655,10 +13655,10 @@
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>การบริหารโครงการ</v>
+        <v>ความเข้าใจเทคโนโลยี</v>
       </c>
       <c r="D166" t="str">
-        <v>วางแผนเวลา งบ และคนให้งานเสร็จตามเป้า</v>
+        <v>รู้ว่าเทคโนโลยีแต่ละแบบทำอะไรได้และเหมาะกับงานใด</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -13678,10 +13678,10 @@
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>การวิเคราะห์ธุรกิจ</v>
+        <v>การบริหารโครงการ</v>
       </c>
       <c r="D167" t="str">
-        <v>ใช้ข้อมูลหาปัญหาและโอกาสของธุรกิจ</v>
+        <v>วางแผนเวลา งบ และคนให้งานเสร็จตามเป้า</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -13701,10 +13701,10 @@
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>ระบบเครือข่าย</v>
+        <v>การวิเคราะห์ธุรกิจ</v>
       </c>
       <c r="D168" t="str">
-        <v>เชื่อมต่อคอมพิวเตอร์และอุปกรณ์ให้สื่อสารกันได้</v>
+        <v>ใช้ข้อมูลหาปัญหาและโอกาสของธุรกิจ</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -13724,10 +13724,10 @@
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>ฐานข้อมูล</v>
+        <v>ระบบเครือข่าย</v>
       </c>
       <c r="D169" t="str">
-        <v>ระบบเก็บและเรียกใช้ข้อมูลอย่างเป็นระเบียบ</v>
+        <v>เชื่อมต่อคอมพิวเตอร์และอุปกรณ์ให้สื่อสารกันได้</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -13747,10 +13747,10 @@
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>ทักษะศิลปะปฏิบัติ</v>
+        <v>ฐานข้อมูล</v>
       </c>
       <c r="D170" t="str">
-        <v>ลงมือวาด ปั้น หรือสร้างงานศิลปะได้จริง</v>
+        <v>ระบบเก็บและเรียกใช้ข้อมูลอย่างเป็นระเบียบ</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -13770,10 +13770,10 @@
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>การสอนและอธิบาย</v>
+        <v>ทักษะศิลปะปฏิบัติ</v>
       </c>
       <c r="D171" t="str">
-        <v>แบ่งเรื่องยากเป็นขั้นตอนให้ผู้เรียนเข้าใจ</v>
+        <v>ลงมือวาด ปั้น หรือสร้างงานศิลปะได้จริง</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -13793,10 +13793,10 @@
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>การออกแบบกิจกรรมการเรียนรู้</v>
+        <v>การสอนและอธิบาย</v>
       </c>
       <c r="D172" t="str">
-        <v>วางกิจกรรมที่ช่วยให้ผู้เรียนเข้าใจและสนุก</v>
+        <v>แบ่งเรื่องยากเป็นขั้นตอนให้ผู้เรียนเข้าใจ</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -13816,10 +13816,10 @@
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>การเขียนแบบ</v>
+        <v>การออกแบบกิจกรรมการเรียนรู้</v>
       </c>
       <c r="D173" t="str">
-        <v>วาดแบบที่มีขนาดและสัดส่วนถูกต้องสำหรับนำไปสร้างจริง</v>
+        <v>วางกิจกรรมที่ช่วยให้ผู้เรียนเข้าใจและสนุก</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -13839,10 +13839,10 @@
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>การเลือกวัสดุและสี</v>
+        <v>การเขียนแบบ</v>
       </c>
       <c r="D174" t="str">
-        <v>เลือกวัสดุและสีให้เหมาะกับการใช้งานและบรรยากาศ</v>
+        <v>วาดแบบที่มีขนาดและสัดส่วนถูกต้องสำหรับนำไปสร้างจริง</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -13862,10 +13862,10 @@
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>ทักษะกีฬา</v>
+        <v>การเลือกวัสดุและสี</v>
       </c>
       <c r="D175" t="str">
-        <v>เล่นกีฬาได้ถูกเทคนิคและเข้าใจกติกา</v>
+        <v>เลือกวัสดุและสีให้เหมาะกับการใช้งานและบรรยากาศ</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -13885,10 +13885,10 @@
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>การสอนและการจัดกิจกรรม</v>
+        <v>ทักษะกีฬา</v>
       </c>
       <c r="D176" t="str">
-        <v>นำกิจกรรมและสอนให้ผู้เข้าร่วมทำตามได้</v>
+        <v>เล่นกีฬาได้ถูกเทคนิคและเข้าใจกติกา</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -13908,10 +13908,10 @@
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>ความรู้สุขภาพและสรีรวิทยา</v>
+        <v>การสอนและการจัดกิจกรรม</v>
       </c>
       <c r="D177" t="str">
-        <v>เข้าใจการทำงานของร่างกายและการดูแลสุขภาพ</v>
+        <v>นำกิจกรรมและสอนให้ผู้เข้าร่วมทำตามได้</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -13931,10 +13931,10 @@
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>การประเมินความเสี่ยง</v>
+        <v>ความรู้สุขภาพและสรีรวิทยา</v>
       </c>
       <c r="D178" t="str">
-        <v>มองหาสิ่งที่อาจเกิดอันตรายและหาทางป้องกัน</v>
+        <v>เข้าใจการทำงานของร่างกายและการดูแลสุขภาพ</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -13954,10 +13954,10 @@
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>กฎหมายความปลอดภัย</v>
+        <v>การประเมินความเสี่ยง</v>
       </c>
       <c r="D179" t="str">
-        <v>รู้ข้อกำหนดด้านความปลอดภัยในการทำงานตามกฎหมาย</v>
+        <v>มองหาสิ่งที่อาจเกิดอันตรายและหาทางป้องกัน</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -13977,10 +13977,10 @@
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>ความรู้ด้านวิศวกรรมพื้นฐาน</v>
+        <v>กฎหมายความปลอดภัย</v>
       </c>
       <c r="D180" t="str">
-        <v>หลักการทางวิศวกรรมที่ใช้ในเครื่องจักรและอาคาร</v>
+        <v>รู้ข้อกำหนดด้านความปลอดภัยในการทำงานตามกฎหมาย</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -14000,10 +14000,10 @@
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>วิทยาศาสตร์สิ่งแวดล้อม</v>
+        <v>ความรู้ด้านวิศวกรรมพื้นฐาน</v>
       </c>
       <c r="D181" t="str">
-        <v>เข้าใจดิน น้ำ อากาศ และผลกระทบจากกิจกรรมของมนุษย์</v>
+        <v>หลักการทางวิศวกรรมที่ใช้ในเครื่องจักรและอาคาร</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -14023,10 +14023,10 @@
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>การเก็บและวิเคราะห์ข้อมูลภาคสนาม</v>
+        <v>วิทยาศาสตร์สิ่งแวดล้อม</v>
       </c>
       <c r="D182" t="str">
-        <v>เก็บตัวอย่างในพื้นที่จริงแล้วนำมาวิเคราะห์</v>
+        <v>เข้าใจดิน น้ำ อากาศ และผลกระทบจากกิจกรรมของมนุษย์</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -14046,10 +14046,10 @@
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>กฎหมายสิ่งแวดล้อม</v>
+        <v>การเก็บและวิเคราะห์ข้อมูลภาคสนาม</v>
       </c>
       <c r="D183" t="str">
-        <v>รู้ข้อกำหนดทางกฎหมายเกี่ยวกับมลพิษและทรัพยากร</v>
+        <v>เก็บตัวอย่างในพื้นที่จริงแล้วนำมาวิเคราะห์</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -14069,10 +14069,10 @@
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>การปฐมพยาบาลและช่วยชีวิต</v>
+        <v>กฎหมายสิ่งแวดล้อม</v>
       </c>
       <c r="D184" t="str">
-        <v>ช่วยเหลือผู้บาดเจ็บเบื้องต้น เช่น การทำ CPR</v>
+        <v>รู้ข้อกำหนดทางกฎหมายเกี่ยวกับมลพิษและทรัพยากร</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -14092,10 +14092,10 @@
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>การตัดสินใจภายใต้ความกดดัน</v>
+        <v>การปฐมพยาบาลและช่วยชีวิต</v>
       </c>
       <c r="D185" t="str">
-        <v>เลือกทางที่เหมาะสมได้รวดเร็วในสถานการณ์เร่งด่วน</v>
+        <v>ช่วยเหลือผู้บาดเจ็บเบื้องต้น เช่น การทำ CPR</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -14115,10 +14115,10 @@
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>การทำงานเป็นทีม</v>
+        <v>การตัดสินใจภายใต้ความกดดัน</v>
       </c>
       <c r="D186" t="str">
-        <v>แบ่งหน้าที่และช่วยเหลือกันจนงานสำเร็จ</v>
+        <v>เลือกทางที่เหมาะสมได้รวดเร็วในสถานการณ์เร่งด่วน</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -14138,10 +14138,10 @@
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>การประกอบอาหาร</v>
+        <v>การทำงานเป็นทีม</v>
       </c>
       <c r="D187" t="str">
-        <v>ทำอาหารได้ถูกวิธี ถูกสุขอนามัย และอร่อย</v>
+        <v>แบ่งหน้าที่และช่วยเหลือกันจนงานสำเร็จ</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -14161,10 +14161,10 @@
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>การบริหารต้นทุน</v>
+        <v>การประกอบอาหาร</v>
       </c>
       <c r="D188" t="str">
-        <v>ควบคุมค่าใช้จ่ายให้ธุรกิจมีกำไร</v>
+        <v>ทำอาหารได้ถูกวิธี ถูกสุขอนามัย และอร่อย</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -14184,10 +14184,10 @@
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>การวางแผนการผลิต</v>
+        <v>การบริหารต้นทุน</v>
       </c>
       <c r="D189" t="str">
-        <v>กำหนดว่าจะผลิตอะไร เท่าไร และเมื่อไร</v>
+        <v>ควบคุมค่าใช้จ่ายให้ธุรกิจมีกำไร</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -14207,10 +14207,10 @@
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>การควบคุมคุณภาพ</v>
+        <v>การวางแผนการผลิต</v>
       </c>
       <c r="D190" t="str">
-        <v>ตรวจสินค้าหรืองานให้ได้ตามมาตรฐาน</v>
+        <v>กำหนดว่าจะผลิตอะไร เท่าไร และเมื่อไร</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -14230,10 +14230,10 @@
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>โครงสร้างข้อมูลและอัลกอริทึม</v>
+        <v>การควบคุมคุณภาพ</v>
       </c>
       <c r="D191" t="str">
-        <v>วิธีจัดเก็บข้อมูลและขั้นตอนแก้ปัญหาในโปรแกรม</v>
+        <v>ตรวจสินค้าหรืองานให้ได้ตามมาตรฐาน</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -14253,10 +14253,10 @@
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>ระบบคอมพิวเตอร์และฮาร์ดแวร์</v>
+        <v>โครงสร้างข้อมูลและอัลกอริทึม</v>
       </c>
       <c r="D192" t="str">
-        <v>เข้าใจชิ้นส่วนและการทำงานภายในคอมพิวเตอร์</v>
+        <v>วิธีจัดเก็บข้อมูลและขั้นตอนแก้ปัญหาในโปรแกรม</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -14276,10 +14276,10 @@
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>ความรู้แร่และอัญมณี</v>
+        <v>ระบบคอมพิวเตอร์และฮาร์ดแวร์</v>
       </c>
       <c r="D193" t="str">
-        <v>รู้จักชนิดและคุณสมบัติของแร่และพลอย</v>
+        <v>เข้าใจชิ้นส่วนและการทำงานภายในคอมพิวเตอร์</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -14299,10 +14299,10 @@
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>การออกแบบเครื่องประดับ</v>
+        <v>ความรู้แร่และอัญมณี</v>
       </c>
       <c r="D194" t="str">
-        <v>ออกแบบแหวน สร้อย หรือเครื่องประดับให้สวยและสวมใส่ได้</v>
+        <v>รู้จักชนิดและคุณสมบัติของแร่และพลอย</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -14322,10 +14322,10 @@
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>การใช้เครื่องมือตรวจสอบ</v>
+        <v>การออกแบบเครื่องประดับ</v>
       </c>
       <c r="D195" t="str">
-        <v>ใช้เครื่องมือวัดและตรวจคุณภาพอย่างถูกวิธี</v>
+        <v>ออกแบบแหวน สร้อย หรือเครื่องประดับให้สวยและสวมใส่ได้</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -14345,10 +14345,10 @@
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>เทคโนโลยีการพิมพ์</v>
+        <v>การใช้เครื่องมือตรวจสอบ</v>
       </c>
       <c r="D196" t="str">
-        <v>เข้าใจเครื่องพิมพ์และกระบวนการพิมพ์แบบต่าง ๆ</v>
+        <v>ใช้เครื่องมือวัดและตรวจคุณภาพอย่างถูกวิธี</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -14368,10 +14368,10 @@
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>การจัดการสีและภาพ</v>
+        <v>เทคโนโลยีการพิมพ์</v>
       </c>
       <c r="D197" t="str">
-        <v>ปรับสีและภาพให้ตรงกันทั้งบนจอและงานพิมพ์</v>
+        <v>เข้าใจเครื่องพิมพ์และกระบวนการพิมพ์แบบต่าง ๆ</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -14391,10 +14391,10 @@
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>การควบคุมคุณภาพการผลิต</v>
+        <v>การจัดการสีและภาพ</v>
       </c>
       <c r="D198" t="str">
-        <v>ตรวจงานในแต่ละขั้นตอนการผลิตให้ได้มาตรฐาน</v>
+        <v>ปรับสีและภาพให้ตรงกันทั้งบนจอและงานพิมพ์</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -14414,10 +14414,10 @@
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>สุขศาสตร์อุตสาหกรรม</v>
+        <v>การควบคุมคุณภาพการผลิต</v>
       </c>
       <c r="D199" t="str">
-        <v>ป้องกันอันตรายต่อสุขภาพจากสภาพแวดล้อมในที่ทำงาน</v>
+        <v>ตรวจงานในแต่ละขั้นตอนการผลิตให้ได้มาตรฐาน</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -14437,10 +14437,10 @@
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>วิศวกรรมไฟฟ้า/อิเล็กทรอนิกส์</v>
+        <v>สุขศาสตร์อุตสาหกรรม</v>
       </c>
       <c r="D200" t="str">
-        <v>หลักการของวงจรและอุปกรณ์อิเล็กทรอนิกส์</v>
+        <v>ป้องกันอันตรายต่อสุขภาพจากสภาพแวดล้อมในที่ทำงาน</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -14460,10 +14460,10 @@
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>ชีววิทยาและสรีรวิทยา</v>
+        <v>วิศวกรรมไฟฟ้า/อิเล็กทรอนิกส์</v>
       </c>
       <c r="D201" t="str">
-        <v>เข้าใจสิ่งมีชีวิตและการทำงานของร่างกาย</v>
+        <v>หลักการของวงจรและอุปกรณ์อิเล็กทรอนิกส์</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -14483,10 +14483,10 @@
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>การออกแบบอุปกรณ์</v>
+        <v>ชีววิทยาและสรีรวิทยา</v>
       </c>
       <c r="D202" t="str">
-        <v>ออกแบบเครื่องมือให้ใช้งานได้จริงและปลอดภัย</v>
+        <v>เข้าใจสิ่งมีชีวิตและการทำงานของร่างกาย</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -14506,10 +14506,10 @@
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>กราฟิกคอมพิวเตอร์</v>
+        <v>การออกแบบอุปกรณ์</v>
       </c>
       <c r="D203" t="str">
-        <v>สร้างภาพและภาพเคลื่อนไหวด้วยคอมพิวเตอร์</v>
+        <v>ออกแบบเครื่องมือให้ใช้งานได้จริงและปลอดภัย</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -14529,10 +14529,10 @@
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>การประมวลผลภาพและเสียง</v>
+        <v>กราฟิกคอมพิวเตอร์</v>
       </c>
       <c r="D204" t="str">
-        <v>ปรับแต่งและวิเคราะห์ภาพหรือเสียงด้วยโปรแกรม</v>
+        <v>สร้างภาพและภาพเคลื่อนไหวด้วยคอมพิวเตอร์</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -14552,10 +14552,10 @@
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>การคิดเชิงออกแบบ (Design Thinking)</v>
+        <v>การประมวลผลภาพและเสียง</v>
       </c>
       <c r="D205" t="str">
-        <v>เริ่มจากเข้าใจผู้ใช้ แล้วทดลองหาทางแก้ปัญหาซ้ำจนได้ผล</v>
+        <v>ปรับแต่งและวิเคราะห์ภาพหรือเสียงด้วยโปรแกรม</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -14575,10 +14575,10 @@
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>การทำงานกับชุมชน</v>
+        <v>การคิดเชิงออกแบบ (Design Thinking)</v>
       </c>
       <c r="D206" t="str">
-        <v>ลงพื้นที่ รับฟัง และทำงานร่วมกับคนในชุมชน</v>
+        <v>เริ่มจากเข้าใจผู้ใช้ แล้วทดลองหาทางแก้ปัญหาซ้ำจนได้ผล</v>
       </c>
       <c r="E206" t="str">
         <v/>
@@ -14598,10 +14598,10 @@
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>การวิจัยผู้ใช้</v>
+        <v>การทำงานกับชุมชน</v>
       </c>
       <c r="D207" t="str">
-        <v>สัมภาษณ์และสังเกตผู้ใช้เพื่อเข้าใจความต้องการจริง</v>
+        <v>ลงพื้นที่ รับฟัง และทำงานร่วมกับคนในชุมชน</v>
       </c>
       <c r="E207" t="str">
         <v/>
@@ -14621,10 +14621,10 @@
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>การออกแบบหน้าจอ (Figma)</v>
+        <v>การวิจัยผู้ใช้</v>
       </c>
       <c r="D208" t="str">
-        <v>ออกแบบหน้าตาแอปหรือเว็บด้วยโปรแกรม Figma</v>
+        <v>สัมภาษณ์และสังเกตผู้ใช้เพื่อเข้าใจความต้องการจริง</v>
       </c>
       <c r="E208" t="str">
         <v/>
@@ -14644,10 +14644,10 @@
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>การคิดเชิงออกแบบ</v>
+        <v>การออกแบบหน้าจอ (Figma)</v>
       </c>
       <c r="D209" t="str">
-        <v>เริ่มจากเข้าใจผู้ใช้ แล้วทดลองหาทางแก้ปัญหาซ้ำจนได้ผล</v>
+        <v>ออกแบบหน้าตาแอปหรือเว็บด้วยโปรแกรม Figma</v>
       </c>
       <c r="E209" t="str">
         <v/>
@@ -14667,10 +14667,10 @@
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>การเขียนโปรแกรม (Python)</v>
+        <v>การคิดเชิงออกแบบ</v>
       </c>
       <c r="D210" t="str">
-        <v>เขียนโปรแกรมด้วยภาษา Python ซึ่งนิยมใช้กับงานข้อมูล</v>
+        <v>เริ่มจากเข้าใจผู้ใช้ แล้วทดลองหาทางแก้ปัญหาซ้ำจนได้ผล</v>
       </c>
       <c r="E210" t="str">
         <v/>
@@ -14690,10 +14690,10 @@
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>การนำเสนอข้อมูลด้วยภาพ</v>
+        <v>การเขียนโปรแกรม (Python)</v>
       </c>
       <c r="D211" t="str">
-        <v>ทำกราฟหรืออินโฟกราฟิกให้ข้อมูลเข้าใจง่าย</v>
+        <v>เขียนโปรแกรมด้วยภาษา Python ซึ่งนิยมใช้กับงานข้อมูล</v>
       </c>
       <c r="E211" t="str">
         <v/>
@@ -14713,10 +14713,10 @@
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>การวิจัยภาคสนาม</v>
+        <v>การนำเสนอข้อมูลด้วยภาพ</v>
       </c>
       <c r="D212" t="str">
-        <v>เก็บข้อมูลจากคนหรือพื้นที่จริงอย่างเป็นระบบ</v>
+        <v>ทำกราฟหรืออินโฟกราฟิกให้ข้อมูลเข้าใจง่าย</v>
       </c>
       <c r="E212" t="str">
         <v/>
@@ -14736,10 +14736,10 @@
         <v/>
       </c>
       <c r="C213" t="str">
-        <v>การวิเคราะห์ประเด็นสังคม</v>
+        <v>การวิจัยภาคสนาม</v>
       </c>
       <c r="D213" t="str">
-        <v>มองปัญหาสังคมจากหลายมุมและหาสาเหตุ</v>
+        <v>เก็บข้อมูลจากคนหรือพื้นที่จริงอย่างเป็นระบบ</v>
       </c>
       <c r="E213" t="str">
         <v/>
@@ -14759,10 +14759,10 @@
         <v/>
       </c>
       <c r="C214" t="str">
-        <v>การเขียนรายงาน</v>
+        <v>การวิเคราะห์ประเด็นสังคม</v>
       </c>
       <c r="D214" t="str">
-        <v>สรุปข้อมูลเป็นรายงานที่ชัดเจนและมีที่มา</v>
+        <v>มองปัญหาสังคมจากหลายมุมและหาสาเหตุ</v>
       </c>
       <c r="E214" t="str">
         <v/>
@@ -14782,10 +14782,10 @@
         <v/>
       </c>
       <c r="C215" t="str">
-        <v>โภชนศาสตร์</v>
+        <v>การเขียนรายงาน</v>
       </c>
       <c r="D215" t="str">
-        <v>ความรู้เรื่องสารอาหารและผลต่อร่างกาย</v>
+        <v>สรุปข้อมูลเป็นรายงานที่ชัดเจนและมีที่มา</v>
       </c>
       <c r="E215" t="str">
         <v/>
@@ -14805,10 +14805,10 @@
         <v/>
       </c>
       <c r="C216" t="str">
-        <v>การให้คำปรึกษาด้านอาหาร</v>
+        <v>โภชนศาสตร์</v>
       </c>
       <c r="D216" t="str">
-        <v>แนะนำการกินให้เหมาะกับสุขภาพของแต่ละคน</v>
+        <v>ความรู้เรื่องสารอาหารและผลต่อร่างกาย</v>
       </c>
       <c r="E216" t="str">
         <v/>
@@ -14828,10 +14828,10 @@
         <v/>
       </c>
       <c r="C217" t="str">
-        <v>การวิเคราะห์โครงสร้างภาษา</v>
+        <v>การให้คำปรึกษาด้านอาหาร</v>
       </c>
       <c r="D217" t="str">
-        <v>ศึกษาเสียง คำ และไวยากรณ์ของภาษา</v>
+        <v>แนะนำการกินให้เหมาะกับสุขภาพของแต่ละคน</v>
       </c>
       <c r="E217" t="str">
         <v/>
@@ -14851,10 +14851,10 @@
         <v/>
       </c>
       <c r="C218" t="str">
-        <v>การใช้เครื่องมือวิเคราะห์ภาษา</v>
+        <v>การวิเคราะห์โครงสร้างภาษา</v>
       </c>
       <c r="D218" t="str">
-        <v>ใช้โปรแกรมช่วยศึกษาข้อมูลภาษาจำนวนมาก</v>
+        <v>ศึกษาเสียง คำ และไวยากรณ์ของภาษา</v>
       </c>
       <c r="E218" t="str">
         <v/>
@@ -14874,10 +14874,10 @@
         <v/>
       </c>
       <c r="C219" t="str">
-        <v>การจัดระบบข้อมูล</v>
+        <v>การใช้เครื่องมือวิเคราะห์ภาษา</v>
       </c>
       <c r="D219" t="str">
-        <v>จัดหมวดหมู่ข้อมูลให้ค้นหาและใช้ต่อได้ง่าย</v>
+        <v>ใช้โปรแกรมช่วยศึกษาข้อมูลภาษาจำนวนมาก</v>
       </c>
       <c r="E219" t="str">
         <v/>
@@ -14897,10 +14897,10 @@
         <v/>
       </c>
       <c r="C220" t="str">
-        <v>การสืบค้นสารสนเทศ</v>
+        <v>การจัดระบบข้อมูล</v>
       </c>
       <c r="D220" t="str">
-        <v>หาข้อมูลจากแหล่งที่น่าเชื่อถือได้อย่างรวดเร็ว</v>
+        <v>จัดหมวดหมู่ข้อมูลให้ค้นหาและใช้ต่อได้ง่าย</v>
       </c>
       <c r="E220" t="str">
         <v/>
@@ -14920,10 +14920,10 @@
         <v/>
       </c>
       <c r="C221" t="str">
-        <v>เทคโนโลยีฐานข้อมูล</v>
+        <v>การสืบค้นสารสนเทศ</v>
       </c>
       <c r="D221" t="str">
-        <v>ระบบและโปรแกรมที่ใช้เก็บและค้นข้อมูล</v>
+        <v>หาข้อมูลจากแหล่งที่น่าเชื่อถือได้อย่างรวดเร็ว</v>
       </c>
       <c r="E221" t="str">
         <v/>
@@ -14943,10 +14943,10 @@
         <v/>
       </c>
       <c r="C222" t="str">
-        <v>รหัสโรคและหัตถการ (ICD)</v>
+        <v>เทคโนโลยีฐานข้อมูล</v>
       </c>
       <c r="D222" t="str">
-        <v>ใช้รหัสมาตรฐานบันทึกโรคและการรักษา</v>
+        <v>ระบบและโปรแกรมที่ใช้เก็บและค้นข้อมูล</v>
       </c>
       <c r="E222" t="str">
         <v/>
@@ -14966,10 +14966,10 @@
         <v/>
       </c>
       <c r="C223" t="str">
-        <v>การจัดการข้อมูลสุขภาพ</v>
+        <v>รหัสโรคและหัตถการ (ICD)</v>
       </c>
       <c r="D223" t="str">
-        <v>ดูแลข้อมูลผู้ป่วยให้ถูกต้อง ครบถ้วน และปลอดภัย</v>
+        <v>ใช้รหัสมาตรฐานบันทึกโรคและการรักษา</v>
       </c>
       <c r="E223" t="str">
         <v/>
@@ -14989,10 +14989,10 @@
         <v/>
       </c>
       <c r="C224" t="str">
-        <v>ทักษะการแสดงและนาฏศิลป์</v>
+        <v>การจัดการข้อมูลสุขภาพ</v>
       </c>
       <c r="D224" t="str">
-        <v>รำ เต้น หรือแสดงได้ถูกท่าทางและมีอารมณ์</v>
+        <v>ดูแลข้อมูลผู้ป่วยให้ถูกต้อง ครบถ้วน และปลอดภัย</v>
       </c>
       <c r="E224" t="str">
         <v/>
@@ -15012,10 +15012,10 @@
         <v/>
       </c>
       <c r="C225" t="str">
-        <v>การสื่อสารด้วยร่างกาย</v>
+        <v>ทักษะการแสดงและนาฏศิลป์</v>
       </c>
       <c r="D225" t="str">
-        <v>ใช้ท่าทางและสีหน้าสื่ออารมณ์และความหมาย</v>
+        <v>รำ เต้น หรือแสดงได้ถูกท่าทางและมีอารมณ์</v>
       </c>
       <c r="E225" t="str">
         <v/>
@@ -15035,10 +15035,10 @@
         <v/>
       </c>
       <c r="C226" t="str">
-        <v>การทำงานเป็นคณะ</v>
+        <v>การสื่อสารด้วยร่างกาย</v>
       </c>
       <c r="D226" t="str">
-        <v>ซ้อมและแสดงร่วมกับผู้อื่นอย่างพร้อมเพรียง</v>
+        <v>ใช้ท่าทางและสีหน้าสื่ออารมณ์และความหมาย</v>
       </c>
       <c r="E226" t="str">
         <v/>
@@ -15058,10 +15058,10 @@
         <v/>
       </c>
       <c r="C227" t="str">
-        <v>การจัดองค์ประกอบ</v>
+        <v>การทำงานเป็นคณะ</v>
       </c>
       <c r="D227" t="str">
-        <v>จัดวางภาพ ตัวอักษร และพื้นที่ว่างให้ดูดีและอ่านง่าย</v>
+        <v>ซ้อมและแสดงร่วมกับผู้อื่นอย่างพร้อมเพรียง</v>
       </c>
       <c r="E227" t="str">
         <v/>
@@ -15081,10 +15081,10 @@
         <v/>
       </c>
       <c r="C228" t="str">
-        <v>ตัวอักษรและสี</v>
+        <v>การจัดองค์ประกอบ</v>
       </c>
       <c r="D228" t="str">
-        <v>เลือกแบบอักษรและคู่สีให้สื่ออารมณ์ของงาน</v>
+        <v>จัดวางภาพ ตัวอักษร และพื้นที่ว่างให้ดูดีและอ่านง่าย</v>
       </c>
       <c r="E228" t="str">
         <v/>
@@ -15104,10 +15104,10 @@
         <v/>
       </c>
       <c r="C229" t="str">
-        <v>โปรแกรมกราฟิก</v>
+        <v>ตัวอักษรและสี</v>
       </c>
       <c r="D229" t="str">
-        <v>ใช้โปรแกรมอย่าง Photoshop หรือ Illustrator สร้างงาน</v>
+        <v>เลือกแบบอักษรและคู่สีให้สื่ออารมณ์ของงาน</v>
       </c>
       <c r="E229" t="str">
         <v/>
@@ -15127,10 +15127,10 @@
         <v/>
       </c>
       <c r="C230" t="str">
-        <v>การเขียนโปรแกรมเกม</v>
+        <v>โปรแกรมกราฟิก</v>
       </c>
       <c r="D230" t="str">
-        <v>เขียนโค้ดให้ตัวละครและระบบในเกมทำงาน</v>
+        <v>ใช้โปรแกรมอย่าง Photoshop หรือ Illustrator สร้างงาน</v>
       </c>
       <c r="E230" t="str">
         <v/>
@@ -15150,10 +15150,10 @@
         <v/>
       </c>
       <c r="C231" t="str">
-        <v>Game Engine (Unity/Unreal)</v>
+        <v>การเขียนโปรแกรมเกม</v>
       </c>
       <c r="D231" t="str">
-        <v>ใช้โปรแกรมสร้างเกมที่นิยมในวงการ</v>
+        <v>เขียนโค้ดให้ตัวละครและระบบในเกมทำงาน</v>
       </c>
       <c r="E231" t="str">
         <v/>
@@ -15173,10 +15173,10 @@
         <v/>
       </c>
       <c r="C232" t="str">
-        <v>การออกแบบเกมเพลย์</v>
+        <v>Game Engine (Unity/Unreal)</v>
       </c>
       <c r="D232" t="str">
-        <v>ออกแบบกติกาและความท้าทายให้เกมสนุก</v>
+        <v>ใช้โปรแกรมสร้างเกมที่นิยมในวงการ</v>
       </c>
       <c r="E232" t="str">
         <v/>
@@ -15196,10 +15196,10 @@
         <v/>
       </c>
       <c r="C233" t="str">
-        <v>การวางแผนงาน</v>
+        <v>การออกแบบเกมเพลย์</v>
       </c>
       <c r="D233" t="str">
-        <v>กำหนดขั้นตอน เวลา และผู้รับผิดชอบก่อนเริ่มงาน</v>
+        <v>ออกแบบกติกาและความท้าทายให้เกมสนุก</v>
       </c>
       <c r="E233" t="str">
         <v/>
@@ -15219,10 +15219,10 @@
         <v/>
       </c>
       <c r="C234" t="str">
-        <v>การประสานงาน</v>
+        <v>การวางแผนงาน</v>
       </c>
       <c r="D234" t="str">
-        <v>ติดต่อหลายฝ่ายให้ทำงานไปพร้อมกันได้</v>
+        <v>กำหนดขั้นตอน เวลา และผู้รับผิดชอบก่อนเริ่มงาน</v>
       </c>
       <c r="E234" t="str">
         <v/>
@@ -15242,10 +15242,10 @@
         <v/>
       </c>
       <c r="C235" t="str">
-        <v>การบริหารงบประมาณ</v>
+        <v>การประสานงาน</v>
       </c>
       <c r="D235" t="str">
-        <v>วางแผนและควบคุมการใช้เงินให้พอและคุ้มค่า</v>
+        <v>ติดต่อหลายฝ่ายให้ทำงานไปพร้อมกันได้</v>
       </c>
       <c r="E235" t="str">
         <v/>
@@ -15265,10 +15265,10 @@
         <v/>
       </c>
       <c r="C236" t="str">
-        <v>การเขียนข่าว</v>
+        <v>การบริหารงบประมาณ</v>
       </c>
       <c r="D236" t="str">
-        <v>เรียบเรียงข้อเท็จจริงให้กระชับ ชัดเจน และเป็นกลาง</v>
+        <v>วางแผนและควบคุมการใช้เงินให้พอและคุ้มค่า</v>
       </c>
       <c r="E236" t="str">
         <v/>
@@ -15288,10 +15288,10 @@
         <v/>
       </c>
       <c r="C237" t="str">
-        <v>การสัมภาษณ์</v>
+        <v>การเขียนข่าว</v>
       </c>
       <c r="D237" t="str">
-        <v>ตั้งคำถามและฟังเพื่อได้ข้อมูลที่ต้องการ</v>
+        <v>เรียบเรียงข้อเท็จจริงให้กระชับ ชัดเจน และเป็นกลาง</v>
       </c>
       <c r="E237" t="str">
         <v/>
@@ -15311,10 +15311,10 @@
         <v/>
       </c>
       <c r="C238" t="str">
-        <v>การตรวจสอบข้อเท็จจริง</v>
+        <v>การสัมภาษณ์</v>
       </c>
       <c r="D238" t="str">
-        <v>เช็กว่าข้อมูลถูกต้องจากหลายแหล่งก่อนเผยแพร่</v>
+        <v>ตั้งคำถามและฟังเพื่อได้ข้อมูลที่ต้องการ</v>
       </c>
       <c r="E238" t="str">
         <v/>
@@ -15334,10 +15334,10 @@
         <v/>
       </c>
       <c r="C239" t="str">
-        <v>การสร้างแบรนด์</v>
+        <v>การตรวจสอบข้อเท็จจริง</v>
       </c>
       <c r="D239" t="str">
-        <v>ทำให้คนจดจำและรู้สึกดีกับสินค้าหรือองค์กร</v>
+        <v>เช็กว่าข้อมูลถูกต้องจากหลายแหล่งก่อนเผยแพร่</v>
       </c>
       <c r="E239" t="str">
         <v/>
@@ -15357,10 +15357,10 @@
         <v/>
       </c>
       <c r="C240" t="str">
-        <v>การทำคอนเทนต์</v>
+        <v>การสร้างแบรนด์</v>
       </c>
       <c r="D240" t="str">
-        <v>สร้างโพสต์ วิดีโอ หรือบทความให้น่าสนใจ</v>
+        <v>ทำให้คนจดจำและรู้สึกดีกับสินค้าหรือองค์กร</v>
       </c>
       <c r="E240" t="str">
         <v/>
@@ -15380,10 +15380,10 @@
         <v/>
       </c>
       <c r="C241" t="str">
-        <v>การวิเคราะห์ข้อมูลการตลาด</v>
+        <v>การทำคอนเทนต์</v>
       </c>
       <c r="D241" t="str">
-        <v>ดูยอดขายและพฤติกรรมลูกค้าจากข้อมูล</v>
+        <v>สร้างโพสต์ วิดีโอ หรือบทความให้น่าสนใจ</v>
       </c>
       <c r="E241" t="str">
         <v/>
@@ -15403,10 +15403,10 @@
         <v/>
       </c>
       <c r="C242" t="str">
-        <v>ความเข้าใจธุรกิจสื่อและวัฒนธรรม</v>
+        <v>การวิเคราะห์ข้อมูลการตลาด</v>
       </c>
       <c r="D242" t="str">
-        <v>รู้ว่างานสร้างสรรค์สร้างรายได้และถึงผู้ชมอย่างไร</v>
+        <v>ดูยอดขายและพฤติกรรมลูกค้าจากข้อมูล</v>
       </c>
       <c r="E242" t="str">
         <v/>
@@ -15426,10 +15426,10 @@
         <v/>
       </c>
       <c r="C243" t="str">
-        <v>การตลาด</v>
+        <v>ความเข้าใจธุรกิจสื่อและวัฒนธรรม</v>
       </c>
       <c r="D243" t="str">
-        <v>ทำให้สินค้าเป็นที่รู้จักและมีคนอยากซื้อ</v>
+        <v>รู้ว่างานสร้างสรรค์สร้างรายได้และถึงผู้ชมอย่างไร</v>
       </c>
       <c r="E243" t="str">
         <v/>
@@ -15449,10 +15449,10 @@
         <v/>
       </c>
       <c r="C244" t="str">
-        <v>การผลิตสื่อดิจิทัล</v>
+        <v>การตลาด</v>
       </c>
       <c r="D244" t="str">
-        <v>สร้างภาพ เสียง และวิดีโอสำหรับใช้ออนไลน์</v>
+        <v>ทำให้สินค้าเป็นที่รู้จักและมีคนอยากซื้อ</v>
       </c>
       <c r="E244" t="str">
         <v/>
@@ -15472,10 +15472,10 @@
         <v/>
       </c>
       <c r="C245" t="str">
-        <v>การออกแบบการเรียนการสอน</v>
+        <v>การผลิตสื่อดิจิทัล</v>
       </c>
       <c r="D245" t="str">
-        <v>วางเนื้อหาและวิธีสอนให้ผู้เรียนบรรลุเป้าหมาย</v>
+        <v>สร้างภาพ เสียง และวิดีโอสำหรับใช้ออนไลน์</v>
       </c>
       <c r="E245" t="str">
         <v/>
@@ -15495,10 +15495,10 @@
         <v/>
       </c>
       <c r="C246" t="str">
-        <v>ระบบการเรียนออนไลน์</v>
+        <v>การออกแบบการเรียนการสอน</v>
       </c>
       <c r="D246" t="str">
-        <v>ใช้แพลตฟอร์มสอนและติดตามผู้เรียนผ่านอินเทอร์เน็ต</v>
+        <v>วางเนื้อหาและวิธีสอนให้ผู้เรียนบรรลุเป้าหมาย</v>
       </c>
       <c r="E246" t="str">
         <v/>
@@ -15518,10 +15518,10 @@
         <v/>
       </c>
       <c r="C247" t="str">
-        <v>การจัดกิจกรรม</v>
+        <v>ระบบการเรียนออนไลน์</v>
       </c>
       <c r="D247" t="str">
-        <v>วางแผนและดำเนินกิจกรรมให้เป็นไปตามกำหนด</v>
+        <v>ใช้แพลตฟอร์มสอนและติดตามผู้เรียนผ่านอินเทอร์เน็ต</v>
       </c>
       <c r="E247" t="str">
         <v/>
@@ -15541,10 +15541,10 @@
         <v/>
       </c>
       <c r="C248" t="str">
-        <v>การเขียนโครงการ</v>
+        <v>การจัดกิจกรรม</v>
       </c>
       <c r="D248" t="str">
-        <v>เขียนแผนงานพร้อมเหตุผล งบ และผลที่คาดหวัง</v>
+        <v>วางแผนและดำเนินกิจกรรมให้เป็นไปตามกำหนด</v>
       </c>
       <c r="E248" t="str">
         <v/>
@@ -15564,10 +15564,10 @@
         <v/>
       </c>
       <c r="C249" t="str">
-        <v>การวางแผนฉุกเฉิน</v>
+        <v>การเขียนโครงการ</v>
       </c>
       <c r="D249" t="str">
-        <v>เตรียมแผนรับมือเหตุไม่คาดคิดล่วงหน้า</v>
+        <v>เขียนแผนงานพร้อมเหตุผล งบ และผลที่คาดหวัง</v>
       </c>
       <c r="E249" t="str">
         <v/>
@@ -15587,10 +15587,10 @@
         <v/>
       </c>
       <c r="C250" t="str">
-        <v>การประสานงานหลายหน่วยงาน</v>
+        <v>การวางแผนฉุกเฉิน</v>
       </c>
       <c r="D250" t="str">
-        <v>ติดต่อหลายองค์กรให้ทำงานร่วมกันได้</v>
+        <v>เตรียมแผนรับมือเหตุไม่คาดคิดล่วงหน้า</v>
       </c>
       <c r="E250" t="str">
         <v/>
@@ -15610,10 +15610,10 @@
         <v/>
       </c>
       <c r="C251" t="str">
-        <v>การสื่อสาร</v>
+        <v>การประสานงานหลายหน่วยงาน</v>
       </c>
       <c r="D251" t="str">
-        <v>ถ่ายทอดความคิดให้ผู้อื่นเข้าใจตรงกัน</v>
+        <v>ติดต่อหลายองค์กรให้ทำงานร่วมกันได้</v>
       </c>
       <c r="E251" t="str">
         <v/>
@@ -15633,10 +15633,10 @@
         <v/>
       </c>
       <c r="C252" t="str">
-        <v>กฎหมายแรงงาน</v>
+        <v>การสื่อสาร</v>
       </c>
       <c r="D252" t="str">
-        <v>รู้สิทธิและหน้าที่ของนายจ้างและลูกจ้าง</v>
+        <v>ถ่ายทอดความคิดให้ผู้อื่นเข้าใจตรงกัน</v>
       </c>
       <c r="E252" t="str">
         <v/>
@@ -15656,10 +15656,10 @@
         <v/>
       </c>
       <c r="C253" t="str">
-        <v>การพัฒนาบุคลากร</v>
+        <v>กฎหมายแรงงาน</v>
       </c>
       <c r="D253" t="str">
-        <v>ช่วยให้พนักงานเรียนรู้และเติบโตในงาน</v>
+        <v>รู้สิทธิและหน้าที่ของนายจ้างและลูกจ้าง</v>
       </c>
       <c r="E253" t="str">
         <v/>
@@ -15679,10 +15679,10 @@
         <v/>
       </c>
       <c r="C254" t="str">
-        <v>การบริหารโปรเจกต์บันเทิง</v>
+        <v>การพัฒนาบุคลากร</v>
       </c>
       <c r="D254" t="str">
-        <v>ดูแลงานคอนเสิร์ต ละคร หรือรายการให้สำเร็จ</v>
+        <v>ช่วยให้พนักงานเรียนรู้และเติบโตในงาน</v>
       </c>
       <c r="E254" t="str">
         <v/>
@@ -15702,10 +15702,10 @@
         <v/>
       </c>
       <c r="C255" t="str">
-        <v>ทักษะภาษาต่างประเทศ</v>
+        <v>การบริหารโปรเจกต์บันเทิง</v>
       </c>
       <c r="D255" t="str">
-        <v>สื่อสารด้วยภาษาอื่นนอกจากภาษาไทย</v>
+        <v>ดูแลงานคอนเสิร์ต ละคร หรือรายการให้สำเร็จ</v>
       </c>
       <c r="E255" t="str">
         <v/>
@@ -15725,10 +15725,10 @@
         <v/>
       </c>
       <c r="C256" t="str">
-        <v>การพูดนำเสนอ</v>
+        <v>ทักษะภาษาต่างประเทศ</v>
       </c>
       <c r="D256" t="str">
-        <v>พูดต่อหน้าผู้ฟังได้ชัดเจนและน่าสนใจ</v>
+        <v>สื่อสารด้วยภาษาอื่นนอกจากภาษาไทย</v>
       </c>
       <c r="E256" t="str">
         <v/>
@@ -15748,10 +15748,10 @@
         <v/>
       </c>
       <c r="C257" t="str">
-        <v>การเขียนเชิงสื่อสาร</v>
+        <v>การพูดนำเสนอ</v>
       </c>
       <c r="D257" t="str">
-        <v>เขียนข้อความให้กลุ่มเป้าหมายเข้าใจง่าย</v>
+        <v>พูดต่อหน้าผู้ฟังได้ชัดเจนและน่าสนใจ</v>
       </c>
       <c r="E257" t="str">
         <v/>
@@ -15765,16 +15765,16 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>ประโยคแม่แบบ</v>
+        <v>คำอธิบายทักษะที่ควรพัฒนา</v>
       </c>
       <c r="B258" t="str">
         <v/>
       </c>
       <c r="C258" t="str">
-        <v>ประโยคสรุปความสนใจ</v>
+        <v>การเขียนเชิงสื่อสาร</v>
       </c>
       <c r="D258" t="str">
-        <v>คุณมีความสนใจเด่นด้าน{ด้านอันดับ 1–2}[ในระดับใกล้เคียงกัน] + ขณะเดียวกันก็มีความสนใจด้าน{ด้านที่เหลือ}ในระดับใกล้เคียงกัน / รองลงมาคือด้าน{…}</v>
+        <v>เขียนข้อความให้กลุ่มเป้าหมายเข้าใจง่าย</v>
       </c>
       <c r="E258" t="str">
         <v/>
@@ -15794,10 +15794,10 @@
         <v/>
       </c>
       <c r="C259" t="str">
-        <v>เหตุผลสาขาที่ควรสำรวจ</v>
+        <v>ประโยคสรุปความสนใจ</v>
       </c>
       <c r="D259" t="str">
-        <v>สาขานี้อาจเป็นทางเลือกที่น่าสำรวจสำหรับคุณ เนื่องจากเกี่ยวข้องกับ{วลีของสาขา} ซึ่งเชื่อมโยงกับความสนใจด้าน{…}ของคุณ</v>
+        <v>คุณมีความสนใจเด่นด้าน{ด้านอันดับ 1–2}[ในระดับใกล้เคียงกัน] + ขณะเดียวกันก็มีความสนใจด้าน{ด้านที่เหลือ}ในระดับใกล้เคียงกัน / รองลงมาคือด้าน{…}</v>
       </c>
       <c r="E259" t="str">
         <v/>
@@ -15817,10 +15817,10 @@
         <v/>
       </c>
       <c r="C260" t="str">
-        <v>การ์ดเป้าหมาย</v>
+        <v>เหตุผลสาขาที่ควรสำรวจ</v>
       </c>
       <c r="D260" t="str">
-        <v>สาขานี้เน้น{วลีของสาขา} ซึ่งเชื่อมโยงกับความสนใจด้าน{…}ของคุณ ลองทำกิจกรรมจริงตามข้อด้านล่าง แล้วสังเกตว่าคุณสนุกกับงานลักษณะนี้มากน้อยเพียงใด</v>
+        <v>สาขานี้อาจเป็นทางเลือกที่น่าสำรวจสำหรับคุณ เนื่องจากเกี่ยวข้องกับ{วลีของสาขา} ซึ่งเชื่อมโยงกับความสนใจด้าน{…}ของคุณ</v>
       </c>
       <c r="E260" t="str">
         <v/>
@@ -15840,10 +15840,10 @@
         <v/>
       </c>
       <c r="C261" t="str">
-        <v>กรณีระดับต่ำ</v>
+        <v>การ์ดเป้าหมาย</v>
       </c>
       <c r="D261" t="str">
-        <v>ความสนใจที่โดดเด่นของคุณอาจแตกต่างจากลักษณะการเรียนหรือการทำงานบางส่วนของสาขานี้ แต่ไม่ได้หมายความว่าคุณเรียนสาขานี้ไม่ได้ หากสาขานี้ยังเป็นเป้าหมาย ลองศึกษารายวิชาและลักษณะการเรียนจริง และทดลองกิจกรรมด้าน{…} เพื่อสำรวจว่าคุณชอบและอยากพัฒนาทักษะด้านใดเพิ่ม</v>
+        <v>สาขานี้เน้น{วลีของสาขา} ซึ่งเชื่อมโยงกับความสนใจด้าน{…}ของคุณ ลองทำกิจกรรมจริงตามข้อด้านล่าง แล้วสังเกตว่าคุณสนุกกับงานลักษณะนี้มากน้อยเพียงใด</v>
       </c>
       <c r="E261" t="str">
         <v/>
@@ -15863,10 +15863,10 @@
         <v/>
       </c>
       <c r="C262" t="str">
-        <v>ข้อจำกัดของผล</v>
+        <v>กรณีระดับต่ำ</v>
       </c>
       <c r="D262" t="str">
-        <v>การเชื่อมโยงนี้สะท้อนความสนใจ ไม่ใช่การยืนยันความพร้อมในการเรียนหรือโอกาสสอบติด</v>
+        <v>ความสนใจที่โดดเด่นของคุณอาจแตกต่างจากลักษณะการเรียนหรือการทำงานบางส่วนของสาขานี้ แต่ไม่ได้หมายความว่าคุณเรียนสาขานี้ไม่ได้ หากสาขานี้ยังเป็นเป้าหมาย ลองศึกษารายวิชาและลักษณะการเรียนจริง และทดลองกิจกรรมด้าน{…} เพื่อสำรวจว่าคุณชอบและอยากพัฒนาทักษะด้านใดเพิ่ม</v>
       </c>
       <c r="E262" t="str">
         <v/>
@@ -15886,24 +15886,47 @@
         <v/>
       </c>
       <c r="C263" t="str">
+        <v>ข้อจำกัดของผล</v>
+      </c>
+      <c r="D263" t="str">
+        <v>การเชื่อมโยงนี้สะท้อนความสนใจ ไม่ใช่การยืนยันความพร้อมในการเรียนหรือโอกาสสอบติด</v>
+      </c>
+      <c r="E263" t="str">
+        <v/>
+      </c>
+      <c r="F263" t="str">
+        <v/>
+      </c>
+      <c r="G263" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>ประโยคแม่แบบ</v>
+      </c>
+      <c r="B264" t="str">
+        <v/>
+      </c>
+      <c r="C264" t="str">
         <v>สาขาทางเลือกของเป้าหมาย</v>
       </c>
-      <c r="D263" t="str">
+      <c r="D264" t="str">
         <v>เหมาะสำหรับการสำรวจเพิ่มเติม หากสนใจงานด้าน{งานร่วม} โดยมีส่วนที่แตกต่างจาก{เป้าหมาย}คือการเรียนด้าน{ทักษะที่ต่าง}</v>
       </c>
-      <c r="E263" t="str">
-        <v/>
-      </c>
-      <c r="F263" t="str">
-        <v/>
-      </c>
-      <c r="G263" t="str">
+      <c r="E264" t="str">
+        <v/>
+      </c>
+      <c r="F264" t="str">
+        <v/>
+      </c>
+      <c r="G264" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G263"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G264"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
+++ b/docs/teacher-review/ครูตรวจสอบ-ระบบแนะแนว-RIASEC.xlsx
@@ -14,6 +14,7 @@
     <sheet name="8-กิจกรรมจากข้อมูลโรงเรียน" sheetId="9" r:id="rId9"/>
     <sheet name="9-อาชีพตัวแทนONET" sheetId="10" r:id="rId10"/>
     <sheet name="10-แหล่งข้อมูล" sheetId="11" r:id="rId11"/>
+    <sheet name="11-ข้อคำถาม60ข้อ" sheetId="12" r:id="rId12"/>
   </sheets>
 </workbook>
 </file>
@@ -407,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="130.83203125" customWidth="1"/>
@@ -426,7 +427,7 @@
         <v>สร้างเมื่อ</v>
       </c>
       <c r="B2" t="str">
-        <v>15 ตุลาคม 2569</v>
+        <v>20 ตุลาคม 2569</v>
       </c>
     </row>
     <row r="3">
@@ -482,7 +483,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="str">
-        <v>ชีต 1-เกณฑ์ระบบ: เกณฑ์ที่ผู้พัฒนาตั้งขึ้นเอง (ระดับความสอดคล้อง, ใกล้เคียง = ห่าง ≤ 2 คะแนน, การนับอันดับร่วม ฯลฯ) — ยังไม่มีแหล่งอ้างอิงรับรอง</v>
+        <v>ชีต 11-ข้อคำถาม60ข้อ: ผู้เชี่ยวชาญ 3 คนให้คะแนนแต่ละข้อว่าวัดด้านที่ระบุจริงไหม (+1 ตรง / 0 ไม่แน่ใจ / −1 ไม่ตรง) — IOC ≥ 0.5 ใช้ได้ ข้อที่ต่ำกว่าควรปรับ</v>
       </c>
     </row>
     <row r="10">
@@ -490,15 +491,15 @@
         <v>1</v>
       </c>
       <c r="B10" t="str">
-        <v>ชีต 4-ข้อความที่ระบบเขียน: กิจกรรมทั่วไป 6 ด้าน คำถามทบทวนตัวเอง ประโยคแม่แบบ และคำอธิบายทักษะ 216 ข้อ — เขียนโดยระบบ ยังไม่ผ่านครู</v>
+        <v>ชีต 1-เกณฑ์ระบบ: เกณฑ์ที่ผู้พัฒนาตั้งขึ้นเอง (ระดับความสอดคล้อง, ใกล้เคียง = ห่าง ≤ 2 คะแนน, การนับอันดับร่วม ฯลฯ) — ยังไม่มีแหล่งอ้างอิงรับรอง</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="str">
-        <v>ชีต 3-ข้อมูลสาขา: เนื้อหาจาก Excel ของโรงเรียน (คุณลักษณะ ทักษะ คำแนะนำ วิชา อาชีพ มหาวิทยาลัย) — ยังไม่ได้ตรวจกับแหล่งภายนอก</v>
+        <v>ชีต 4-ข้อความที่ระบบเขียน: กิจกรรมทั่วไป 6 ด้าน คำถามทบทวนตัวเอง ประโยคแม่แบบ และคำอธิบายทักษะ 216 ข้อ — เขียนโดยระบบ ยังไม่ผ่านครู</v>
       </c>
     </row>
     <row r="12">
@@ -506,7 +507,7 @@
         <v>2</v>
       </c>
       <c r="B12" t="str">
-        <v>ชีต 5-6 คำจับคู่: คำที่ระบบใช้ตัดสินว่าวลีของสาขาเชื่อมกับด้านความสนใจใด / งานของสองสาขาคล้ายกัน — ชีต 7 แสดงผลการจับคู่จริงทุกวลี</v>
+        <v>ชีต 3-ข้อมูลสาขา: เนื้อหาจาก Excel ของโรงเรียน (คุณลักษณะ ทักษะ คำแนะนำ วิชา อาชีพ มหาวิทยาลัย) — ยังไม่ได้ตรวจกับแหล่งภายนอก</v>
       </c>
     </row>
     <row r="13">
@@ -514,15 +515,15 @@
         <v>2</v>
       </c>
       <c r="B13" t="str">
-        <v>ชีต 8-กิจกรรมจากข้อมูลโรงเรียน: การแยกคำแนะนำเป็นข้อ และข้อที่ถูกตัดออก (การเตรียมสอบ)</v>
+        <v>ชีต 5-6 คำจับคู่: คำที่ระบบใช้ตัดสินว่าวลีของสาขาเชื่อมกับด้านความสนใจใด / งานของสองสาขาคล้ายกัน — ชีต 7 แสดงผลการจับคู่จริงทุกวลี</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="str">
-        <v>ชีต 9-อาชีพตัวแทน O*NET: การจับคู่สาขากับอาชีพในฐานข้อมูลสหรัฐฯ และคำแปลชื่ออาชีพ/ความรู้</v>
+        <v>ชีต 8-กิจกรรมจากข้อมูลโรงเรียน: การแยกคำแนะนำเป็นข้อ และข้อที่ถูกตัดออก (การเตรียมสอบ)</v>
       </c>
     </row>
     <row r="15">
@@ -530,36 +531,44 @@
         <v>3</v>
       </c>
       <c r="B15" t="str">
-        <v>ชีต 10-แหล่งข้อมูล: URL และวันที่ตรวจ</v>
+        <v>ชีต 9-อาชีพตัวแทน O*NET: การจับคู่สาขากับอาชีพในฐานข้อมูลสหรัฐฯ และคำแปลชื่ออาชีพ/ความรู้</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>ชีต 10-แหล่งข้อมูล: URL และวันที่ตรวจ</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>สิ่งที่ระบบไม่ได้อ้าง</v>
+        <v/>
       </c>
       <c r="B17" t="str">
-        <v>ผล RIASEC บอกความสนใจ ไม่ได้วัดความสามารถ ผลการเรียน คุณสมบัติรับเข้า หรือโอกาสสอบติด • ระบบยังไม่ผ่านการตรวจความเที่ยง/ความตรงของแบบประเมิน</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v>สิ่งที่ระบบไม่ได้อ้าง</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ผล RIASEC บอกความสนใจ ไม่ได้วัดความสามารถ ผลการเรียน คุณสมบัติรับเข้า หรือโอกาสสอบติด • ระบบยังไม่ผ่านการตรวจความเที่ยง/ความตรงของแบบประเมิน</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
         <v>ข้อควรระวังเพิ่มเติม</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B19" t="str">
         <v>แบบประเมิน 60 ข้อยังไม่มีข้อมูลความเชื่อมั่น (เช่น Cronbach's alpha) กับนักเรียนจริง — ควรเก็บข้อมูลช่วงทดลองใช้</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3928,7 +3937,7 @@
         <v>ชื่อหลักสูตร มหาวิทยาลัย ลิงก์หลักสูตร (ตรวจด้วยสคริปต์) และเกณฑ์รับเข้า (ดึงตอนเปิดดู)</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-10-14</v>
+        <v>2026-10-20</v>
       </c>
       <c r="E6" t="str">
         <v>198 ลิงก์หลักสูตร ตรงกับ courses.json</v>
@@ -3972,6 +3981,2041 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J61"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="40.83203125" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ข้อ</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ด้าน</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ข้อคำถาม</v>
+      </c>
+      <c r="D1" t="str">
+        <v>มาตรวัดคำตอบ</v>
+      </c>
+      <c r="E1" t="str">
+        <v>ผู้เชี่ยวชาญ 1 (+1/0/−1)</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ผู้เชี่ยวชาญ 2 (+1/0/−1)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ผู้เชี่ยวชาญ 3 (+1/0/−1)</v>
+      </c>
+      <c r="H1" t="str">
+        <v>IOC (เฉลี่ย ≥ 0.5 ใช้ได้)</v>
+      </c>
+      <c r="I1" t="str">
+        <v>ข้อเสนอแก้ไข</v>
+      </c>
+      <c r="J1" t="str">
+        <v>ผู้ตรวจ / วันที่</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>R1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>R – นักปฏิบัติ</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ฉันชอบประกอบ ซ่อมแซม หรือดัดแปลงสิ่งของด้วยตนเอง</v>
+      </c>
+      <c r="D2" t="str">
+        <v>1 = น้อยที่สุด • 2 = น้อย • 3 = ปานกลาง • 4 = มาก • 5 = ตรงกับฉันมากที่สุด</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <f>IF(COUNT(E2:G2)=0,"",AVERAGE(E2:G2))</f>
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>R – นักปฏิบัติ</v>
+      </c>
+      <c r="C3" t="str">
+        <v>ฉันสนุกกับการเรียนรู้ผ่านการลงมือทำจริง</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <f>IF(COUNT(E3:G3)=0,"",AVERAGE(E3:G3))</f>
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>R – นักปฏิบัติ</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ฉันสนใจการทำงานกับเครื่องมือ อุปกรณ์หรือเทคโนโลยีต่าง ๆ</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <f>IF(COUNT(E4:G4)=0,"",AVERAGE(E4:G4))</f>
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>R – นักปฏิบัติ</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ฉันชอบกิจกรรมที่ต้องใช้ทักษะเชิงปฏิบัติ</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <f>IF(COUNT(E5:G5)=0,"",AVERAGE(E5:G5))</f>
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>R – นักปฏิบัติ</v>
+      </c>
+      <c r="C6" t="str">
+        <v>ฉันชอบแก้ปัญหาที่เกิดขึ้นระหว่างการทำงานจริง</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <f>IF(COUNT(E6:G6)=0,"",AVERAGE(E6:G6))</f>
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>R – นักปฏิบัติ</v>
+      </c>
+      <c r="C7" t="str">
+        <v>ฉันชอบสร้างหรือประดิษฐ์สิ่งใหม่ๆ</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <f>IF(COUNT(E7:G7)=0,"",AVERAGE(E7:G7))</f>
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>R – นักปฏิบัติ</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ฉันชอบงานที่สามารถเห็นผลลัพธ์ได้อย่างชัดเจน</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <f>IF(COUNT(E8:G8)=0,"",AVERAGE(E8:G8))</f>
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>R – นักปฏิบัติ</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ฉันสนใจกิจกรรมภาคสนามมากกว่าการนั่งเรียนอย่างเดียว</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <f>IF(COUNT(E9:G9)=0,"",AVERAGE(E9:G9))</f>
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>R9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>R – นักปฏิบัติ</v>
+      </c>
+      <c r="C10" t="str">
+        <v>ฉันชอบทดลองใช้อุปกรณ์หรือเทคโนโลยีใหม่ๆ</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <f>IF(COUNT(E10:G10)=0,"",AVERAGE(E10:G10))</f>
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>R – นักปฏิบัติ</v>
+      </c>
+      <c r="C11" t="str">
+        <v>ฉันรู้สึกภูมิใจเมื่อได้สร้างผลงานที่จับต้องได้</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <f>IF(COUNT(E11:G11)=0,"",AVERAGE(E11:G11))</f>
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>I1</v>
+      </c>
+      <c r="B12" t="str">
+        <v>I – นักคิดวิเคราะห์</v>
+      </c>
+      <c r="C12" t="str">
+        <v>ฉันชอบตั้งคำถามและค้นหาคำตอบด้วยตนเอง</v>
+      </c>
+      <c r="D12" t="str">
+        <v>1 = น้อยที่สุด • 2 = น้อย • 3 = ปานกลาง • 4 = มาก • 5 = ตรงกับฉันมากที่สุด</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <f>IF(COUNT(E12:G12)=0,"",AVERAGE(E12:G12))</f>
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>I2</v>
+      </c>
+      <c r="B13" t="str">
+        <v>I – นักคิดวิเคราะห์</v>
+      </c>
+      <c r="C13" t="str">
+        <v>ฉันสนุกกับการวิเคราะห์ข้อมูลหรือเหตุการณ์ต่าง ๆ</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <f>IF(COUNT(E13:G13)=0,"",AVERAGE(E13:G13))</f>
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>I3</v>
+      </c>
+      <c r="B14" t="str">
+        <v>I – นักคิดวิเคราะห์</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ฉันสนใจการทดลองหรือการวิจัย</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <f>IF(COUNT(E14:G14)=0,"",AVERAGE(E14:G14))</f>
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>I4</v>
+      </c>
+      <c r="B15" t="str">
+        <v>I – นักคิดวิเคราะห์</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ฉันชอบเรียนรู้เรื่องที่ซับซ้อนและท้าทาย</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <f>IF(COUNT(E15:G15)=0,"",AVERAGE(E15:G15))</f>
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>I5</v>
+      </c>
+      <c r="B16" t="str">
+        <v>I – นักคิดวิเคราะห์</v>
+      </c>
+      <c r="C16" t="str">
+        <v>ฉันชอบแก้ปัญหาที่ต้องใช้เหตุผลและตรรกะ</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <f>IF(COUNT(E16:G16)=0,"",AVERAGE(E16:G16))</f>
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>I6</v>
+      </c>
+      <c r="B17" t="str">
+        <v>I – นักคิดวิเคราะห์</v>
+      </c>
+      <c r="C17" t="str">
+        <v>ฉันมักค้นคว้าข้อมูลเพิ่มเติมนอกเหนือจากที่เรียน</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <f>IF(COUNT(E17:G17)=0,"",AVERAGE(E17:G17))</f>
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>I7</v>
+      </c>
+      <c r="B18" t="str">
+        <v>I – นักคิดวิเคราะห์</v>
+      </c>
+      <c r="C18" t="str">
+        <v>ฉันชอบเปรียบเทียบข้อมูลก่อนตัดสินใจ</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <f>IF(COUNT(E18:G18)=0,"",AVERAGE(E18:G18))</f>
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>I8</v>
+      </c>
+      <c r="B19" t="str">
+        <v>I – นักคิดวิเคราะห์</v>
+      </c>
+      <c r="C19" t="str">
+        <v>ฉันสนใจวิทยาศาสตร์ เทคโนโลยี หรือการค้นพบใหม่ๆ</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <f>IF(COUNT(E19:G19)=0,"",AVERAGE(E19:G19))</f>
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>I9</v>
+      </c>
+      <c r="B20" t="str">
+        <v>I – นักคิดวิเคราะห์</v>
+      </c>
+      <c r="C20" t="str">
+        <v>ฉันชอบค้นหาสาเหตุของปัญหาต่าง ๆ</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <f>IF(COUNT(E20:G20)=0,"",AVERAGE(E20:G20))</f>
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>I10</v>
+      </c>
+      <c r="B21" t="str">
+        <v>I – นักคิดวิเคราะห์</v>
+      </c>
+      <c r="C21" t="str">
+        <v>ฉันสนุกกับการคิดหาวิธีแก้ปัญหาใหม่ๆ</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <f>IF(COUNT(E21:G21)=0,"",AVERAGE(E21:G21))</f>
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>A1</v>
+      </c>
+      <c r="B22" t="str">
+        <v>A – นักสร้างสรรค์</v>
+      </c>
+      <c r="C22" t="str">
+        <v>ฉันชอบคิดไอเดียใหม่ๆ ที่แตกต่างจากคนอื่น</v>
+      </c>
+      <c r="D22" t="str">
+        <v>1 = น้อยที่สุด • 2 = น้อย • 3 = ปานกลาง • 4 = มาก • 5 = ตรงกับฉันมากที่สุด</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <f>IF(COUNT(E22:G22)=0,"",AVERAGE(E22:G22))</f>
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>A2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>A – นักสร้างสรรค์</v>
+      </c>
+      <c r="C23" t="str">
+        <v>ฉันสนใจงานศิลปะ ดนตรี การออกแบบ หรือการแสดง</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <f>IF(COUNT(E23:G23)=0,"",AVERAGE(E23:G23))</f>
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>A3</v>
+      </c>
+      <c r="B24" t="str">
+        <v>A – นักสร้างสรรค์</v>
+      </c>
+      <c r="C24" t="str">
+        <v>ฉันชอบแสดงออกถึงความคิดและความรู้สึกของตนเอง</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <f>IF(COUNT(E24:G24)=0,"",AVERAGE(E24:G24))</f>
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>A4</v>
+      </c>
+      <c r="B25" t="str">
+        <v>A – นักสร้างสรรค์</v>
+      </c>
+      <c r="C25" t="str">
+        <v>ฉันชอบงานที่เปิดโอกาสให้ใช้จินตนาการ</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <f>IF(COUNT(E25:G25)=0,"",AVERAGE(E25:G25))</f>
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>A5</v>
+      </c>
+      <c r="B26" t="str">
+        <v>A – นักสร้างสรรค์</v>
+      </c>
+      <c r="C26" t="str">
+        <v>ฉันสนุกกับการสร้างสรรค์ผลงานใหม่ๆ</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <f>IF(COUNT(E26:G26)=0,"",AVERAGE(E26:G26))</f>
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>A6</v>
+      </c>
+      <c r="B27" t="str">
+        <v>A – นักสร้างสรรค์</v>
+      </c>
+      <c r="C27" t="str">
+        <v>ฉันชอบออกแบบหรือจัดตกแต่งสิ่งต่าง ๆ</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <f>IF(COUNT(E27:G27)=0,"",AVERAGE(E27:G27))</f>
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>A7</v>
+      </c>
+      <c r="B28" t="str">
+        <v>A – นักสร้างสรรค์</v>
+      </c>
+      <c r="C28" t="str">
+        <v>ฉันชอบเล่าเรื่องหรือสร้างเนื้อหาด้วยตนเอง</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <f>IF(COUNT(E28:G28)=0,"",AVERAGE(E28:G28))</f>
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>A8</v>
+      </c>
+      <c r="B29" t="str">
+        <v>A – นักสร้างสรรค์</v>
+      </c>
+      <c r="C29" t="str">
+        <v>ฉันชอบทดลองแนวคิดหรือวิธีการที่แปลกใหม่</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <f>IF(COUNT(E29:G29)=0,"",AVERAGE(E29:G29))</f>
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>A9</v>
+      </c>
+      <c r="B30" t="str">
+        <v>A – นักสร้างสรรค์</v>
+      </c>
+      <c r="C30" t="str">
+        <v>ฉันสนใจการสร้างสื่อ ภาพ วิดีโอ หรือผลงานสร้างสรรค์</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <f>IF(COUNT(E30:G30)=0,"",AVERAGE(E30:G30))</f>
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>A10</v>
+      </c>
+      <c r="B31" t="str">
+        <v>A – นักสร้างสรรค์</v>
+      </c>
+      <c r="C31" t="str">
+        <v>ฉันชอบกิจกรรมที่ไม่มีคำตอบตายตัว</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <f>IF(COUNT(E31:G31)=0,"",AVERAGE(E31:G31))</f>
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>S1</v>
+      </c>
+      <c r="B32" t="str">
+        <v>S – นักช่วยเหลือ</v>
+      </c>
+      <c r="C32" t="str">
+        <v>ฉันชอบช่วยอธิบายบทเรียนให้เพื่อนที่ไม่เข้าใจ</v>
+      </c>
+      <c r="D32" t="str">
+        <v>1 = น้อยที่สุด • 2 = น้อย • 3 = ปานกลาง • 4 = มาก • 5 = ตรงกับฉันมากที่สุด</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <f>IF(COUNT(E32:G32)=0,"",AVERAGE(E32:G32))</f>
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>S2</v>
+      </c>
+      <c r="B33" t="str">
+        <v>S – นักช่วยเหลือ</v>
+      </c>
+      <c r="C33" t="str">
+        <v>ฉันรู้สึกดีเมื่อได้ช่วยเหลือผู้อื่น</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <f>IF(COUNT(E33:G33)=0,"",AVERAGE(E33:G33))</f>
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>S3</v>
+      </c>
+      <c r="B34" t="str">
+        <v>S – นักช่วยเหลือ</v>
+      </c>
+      <c r="C34" t="str">
+        <v>ฉันชอบทำงานร่วมกับคนอื่น</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <f>IF(COUNT(E34:G34)=0,"",AVERAGE(E34:G34))</f>
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>S4</v>
+      </c>
+      <c r="B35" t="str">
+        <v>S – นักช่วยเหลือ</v>
+      </c>
+      <c r="C35" t="str">
+        <v>ฉันสนใจรับฟังปัญหาและความคิดเห็นของผู้อื่น</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <f>IF(COUNT(E35:G35)=0,"",AVERAGE(E35:G35))</f>
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>S5</v>
+      </c>
+      <c r="B36" t="str">
+        <v>S – นักช่วยเหลือ</v>
+      </c>
+      <c r="C36" t="str">
+        <v>ฉันชอบสอนหรือแบ่งปันความรู้ให้คนรอบตัว</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <f>IF(COUNT(E36:G36)=0,"",AVERAGE(E36:G36))</f>
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>S6</v>
+      </c>
+      <c r="B37" t="str">
+        <v>S – นักช่วยเหลือ</v>
+      </c>
+      <c r="C37" t="str">
+        <v>ฉันชอบเข้าร่วมกิจกรรมจิตอาสาหรือกิจกรรมเพื่อสังคม</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <f>IF(COUNT(E37:G37)=0,"",AVERAGE(E37:G37))</f>
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>S7</v>
+      </c>
+      <c r="B38" t="str">
+        <v>S – นักช่วยเหลือ</v>
+      </c>
+      <c r="C38" t="str">
+        <v>ฉันชอบให้คำแนะนำแก่เพื่อนเมื่อมีปัญหา</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <f>IF(COUNT(E38:G38)=0,"",AVERAGE(E38:G38))</f>
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>S8</v>
+      </c>
+      <c r="B39" t="str">
+        <v>S – นักช่วยเหลือ</v>
+      </c>
+      <c r="C39" t="str">
+        <v>ฉันสนใจอาชีพที่เกี่ยวข้องกับการดูแลหรือพัฒนาผู้คน</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <f>IF(COUNT(E39:G39)=0,"",AVERAGE(E39:G39))</f>
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>S9</v>
+      </c>
+      <c r="B40" t="str">
+        <v>S – นักช่วยเหลือ</v>
+      </c>
+      <c r="C40" t="str">
+        <v>ฉันมีความสุขเมื่อเห็นคนอื่นได้รับประโยชน์จากสิ่งที่ฉันทำ</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <f>IF(COUNT(E40:G40)=0,"",AVERAGE(E40:G40))</f>
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>S10</v>
+      </c>
+      <c r="B41" t="str">
+        <v>S – นักช่วยเหลือ</v>
+      </c>
+      <c r="C41" t="str">
+        <v>ฉันชอบกิจกรรมที่ได้พบปะและทำความรู้จักผู้คนใหม่ๆ</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <f>IF(COUNT(E41:G41)=0,"",AVERAGE(E41:G41))</f>
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>E1</v>
+      </c>
+      <c r="B42" t="str">
+        <v>E – ผู้นำ</v>
+      </c>
+      <c r="C42" t="str">
+        <v>ฉันชอบเป็นผู้นำในการทำงานกลุ่ม</v>
+      </c>
+      <c r="D42" t="str">
+        <v>1 = น้อยที่สุด • 2 = น้อย • 3 = ปานกลาง • 4 = มาก • 5 = ตรงกับฉันมากที่สุด</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <f>IF(COUNT(E42:G42)=0,"",AVERAGE(E42:G42))</f>
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>E2</v>
+      </c>
+      <c r="B43" t="str">
+        <v>E – ผู้นำ</v>
+      </c>
+      <c r="C43" t="str">
+        <v>ฉันกล้าแสดงความคิดเห็นต่อหน้าผู้อื่น</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <f>IF(COUNT(E43:G43)=0,"",AVERAGE(E43:G43))</f>
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>E3</v>
+      </c>
+      <c r="B44" t="str">
+        <v>E – ผู้นำ</v>
+      </c>
+      <c r="C44" t="str">
+        <v>ฉันชอบวางแผนและจัดการกิจกรรมต่าง ๆ</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <f>IF(COUNT(E44:G44)=0,"",AVERAGE(E44:G44))</f>
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>E4</v>
+      </c>
+      <c r="B45" t="str">
+        <v>E – ผู้นำ</v>
+      </c>
+      <c r="C45" t="str">
+        <v>ฉันสนุกกับการนำเสนอหรือโน้มน้าวความคิดเห็นของตนเอง</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <f>IF(COUNT(E45:G45)=0,"",AVERAGE(E45:G45))</f>
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>E5</v>
+      </c>
+      <c r="B46" t="str">
+        <v>E – ผู้นำ</v>
+      </c>
+      <c r="C46" t="str">
+        <v>ฉันชอบการแข่งขันและความท้าทาย</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <f>IF(COUNT(E46:G46)=0,"",AVERAGE(E46:G46))</f>
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>E6</v>
+      </c>
+      <c r="B47" t="str">
+        <v>E – ผู้นำ</v>
+      </c>
+      <c r="C47" t="str">
+        <v>ฉันสนใจเรื่องธุรกิจ การลงทุน หรือการสร้างรายได้</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <f>IF(COUNT(E47:G47)=0,"",AVERAGE(E47:G47))</f>
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>E7</v>
+      </c>
+      <c r="B48" t="str">
+        <v>E – ผู้นำ</v>
+      </c>
+      <c r="C48" t="str">
+        <v>ฉันกล้าตัดสินใจในสถานการณ์สำคัญ</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <f>IF(COUNT(E48:G48)=0,"",AVERAGE(E48:G48))</f>
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>E8</v>
+      </c>
+      <c r="B49" t="str">
+        <v>E – ผู้นำ</v>
+      </c>
+      <c r="C49" t="str">
+        <v>ฉันชอบคิดโครงการหรือกิจกรรมใหม่ๆ</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <f>IF(COUNT(E49:G49)=0,"",AVERAGE(E49:G49))</f>
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>E9</v>
+      </c>
+      <c r="B50" t="str">
+        <v>E – ผู้นำ</v>
+      </c>
+      <c r="C50" t="str">
+        <v>ฉันชอบรับผิดชอบงานที่มีผลต่อคนจำนวนมาก</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <f>IF(COUNT(E50:G50)=0,"",AVERAGE(E50:G50))</f>
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>E10</v>
+      </c>
+      <c r="B51" t="str">
+        <v>E – ผู้นำ</v>
+      </c>
+      <c r="C51" t="str">
+        <v>ฉันสนใจบทบาทหัวหน้าหรือผู้บริหารในอนาคต</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <f>IF(COUNT(E51:G51)=0,"",AVERAGE(E51:G51))</f>
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>C1</v>
+      </c>
+      <c r="B52" t="str">
+        <v>C – นักจัดระเบียบ</v>
+      </c>
+      <c r="C52" t="str">
+        <v>ฉันชอบวางแผนก่อนเริ่มทำงาน</v>
+      </c>
+      <c r="D52" t="str">
+        <v>1 = น้อยที่สุด • 2 = น้อย • 3 = ปานกลาง • 4 = มาก • 5 = ตรงกับฉันมากที่สุด</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <f>IF(COUNT(E52:G52)=0,"",AVERAGE(E52:G52))</f>
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>C2</v>
+      </c>
+      <c r="B53" t="str">
+        <v>C – นักจัดระเบียบ</v>
+      </c>
+      <c r="C53" t="str">
+        <v>ฉันชอบจัดระเบียบเอกสารหรือข้อมูลให้เรียบร้อย</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <f>IF(COUNT(E53:G53)=0,"",AVERAGE(E53:G53))</f>
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>C3</v>
+      </c>
+      <c r="B54" t="str">
+        <v>C – นักจัดระเบียบ</v>
+      </c>
+      <c r="C54" t="str">
+        <v>ฉันใส่ใจรายละเอียดของงาน</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <f>IF(COUNT(E54:G54)=0,"",AVERAGE(E54:G54))</f>
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>C4</v>
+      </c>
+      <c r="B55" t="str">
+        <v>C – นักจัดระเบียบ</v>
+      </c>
+      <c r="C55" t="str">
+        <v>ฉันชอบทำงานตามขั้นตอนที่กำหนดไว้</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <f>IF(COUNT(E55:G55)=0,"",AVERAGE(E55:G55))</f>
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>C5</v>
+      </c>
+      <c r="B56" t="str">
+        <v>C – นักจัดระเบียบ</v>
+      </c>
+      <c r="C56" t="str">
+        <v>ฉันมักตรวจสอบความถูกต้องของงานก่อนส่ง</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <f>IF(COUNT(E56:G56)=0,"",AVERAGE(E56:G56))</f>
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>C6</v>
+      </c>
+      <c r="B57" t="str">
+        <v>C – นักจัดระเบียบ</v>
+      </c>
+      <c r="C57" t="str">
+        <v>ฉันชอบจัดตารางเวลาให้กับตนเอง</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <f>IF(COUNT(E57:G57)=0,"",AVERAGE(E57:G57))</f>
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>C7</v>
+      </c>
+      <c r="B58" t="str">
+        <v>C – นักจัดระเบียบ</v>
+      </c>
+      <c r="C58" t="str">
+        <v>ฉันชอบงานที่มีกฎเกณฑ์และระบบชัดเจน</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <f>IF(COUNT(E58:G58)=0,"",AVERAGE(E58:G58))</f>
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>C8</v>
+      </c>
+      <c r="B59" t="str">
+        <v>C – นักจัดระเบียบ</v>
+      </c>
+      <c r="C59" t="str">
+        <v>ฉันสามารถทำงานที่ต้องใช้ความละเอียดได้ดี</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <f>IF(COUNT(E59:G59)=0,"",AVERAGE(E59:G59))</f>
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>C9</v>
+      </c>
+      <c r="B60" t="str">
+        <v>C – นักจัดระเบียบ</v>
+      </c>
+      <c r="C60" t="str">
+        <v>ฉันชอบบันทึกหรือจัดเก็บข้อมูลอย่างเป็นระเบียบ</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <f>IF(COUNT(E60:G60)=0,"",AVERAGE(E60:G60))</f>
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>C10</v>
+      </c>
+      <c r="B61" t="str">
+        <v>C – นักจัดระเบียบ</v>
+      </c>
+      <c r="C61" t="str">
+        <v>ฉันรู้สึกสบายใจกับงานที่มีเป้าหมายและขั้นตอนชัดเจน</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <f>IF(COUNT(E61:G61)=0,"",AVERAGE(E61:G61))</f>
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J61"/>
   </ignoredErrors>
 </worksheet>
 </file>
